--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G30">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G42">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G30">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G30">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G49">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N56">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU59"/>
+  <dimension ref="A1:AU60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>8.1</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-20 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-20 12:10:00</t>
+          <t>2026-10-20 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-20 13:45:00</t>
+          <t>2026-10-20 12:10:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-20 14:00:00</t>
+          <t>2026-10-20 13:45:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.51</v>
+        <v>6.47</v>
       </c>
       <c r="O15">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
       <c r="P15">
-        <v>5.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-20 15:45:00</t>
+          <t>2026-10-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>2.44</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G42">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-20 16:00:00</t>
+          <t>2026-10-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-20 19:30:00</t>
+          <t>2026-10-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G52">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:00:00</t>
+          <t>2026-10-20 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,141 +9894,304 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>Zarzis</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ben Guerdane</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>CS Sfaxien</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-      <c r="V59">
-        <v>0</v>
-      </c>
-      <c r="W59">
-        <v>0</v>
-      </c>
-      <c r="X59">
-        <v>0</v>
-      </c>
-      <c r="Y59">
-        <v>0</v>
-      </c>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-      <c r="AA59">
-        <v>0</v>
-      </c>
-      <c r="AB59">
-        <v>0</v>
-      </c>
-      <c r="AC59">
-        <v>0</v>
-      </c>
-      <c r="AD59">
-        <v>0</v>
-      </c>
-      <c r="AE59">
-        <v>0</v>
-      </c>
-      <c r="AF59">
-        <v>0</v>
-      </c>
-      <c r="AG59">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>0</v>
-      </c>
-      <c r="AK59">
-        <v>0</v>
-      </c>
-      <c r="AL59">
-        <v>0</v>
-      </c>
-      <c r="AM59">
-        <v>-1</v>
-      </c>
-      <c r="AN59">
-        <v>-1</v>
-      </c>
-      <c r="AO59">
-        <v>-1</v>
-      </c>
-      <c r="AP59">
-        <v>-1</v>
-      </c>
-      <c r="AQ59">
-        <v>0</v>
-      </c>
-      <c r="AR59">
-        <v>0</v>
-      </c>
-      <c r="AS59">
-        <v>0</v>
-      </c>
-      <c r="AT59">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-1</v>
+      </c>
+      <c r="AN60">
+        <v>-1</v>
+      </c>
+      <c r="AO60">
+        <v>-1</v>
+      </c>
+      <c r="AP60">
+        <v>-1</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>2026-10-20 21:00:00</t>
         </is>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G31">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G43">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8178,10 +8178,10 @@
         <v>0</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="Q50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G60">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.01</v>
+        <v>1.64</v>
       </c>
       <c r="O45">
-        <v>3.96</v>
+        <v>4.67</v>
       </c>
       <c r="P45">
-        <v>2.32</v>
+        <v>5.18</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="O46">
-        <v>4.67</v>
+        <v>4.41</v>
       </c>
       <c r="P46">
-        <v>5.18</v>
+        <v>4.51</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="O47">
-        <v>11.1</v>
+        <v>4.88</v>
       </c>
       <c r="P47">
-        <v>25</v>
+        <v>6.36</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.76</v>
+        <v>3.01</v>
       </c>
       <c r="O49">
-        <v>4.41</v>
+        <v>3.96</v>
       </c>
       <c r="P49">
-        <v>4.51</v>
+        <v>2.32</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="O50">
-        <v>4.88</v>
+        <v>11.1</v>
       </c>
       <c r="P50">
-        <v>6.36</v>
+        <v>25</v>
       </c>
       <c r="Q50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.61</v>
+        <v>3.01</v>
       </c>
       <c r="O48">
-        <v>4.42</v>
+        <v>3.96</v>
       </c>
       <c r="P48">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8178,10 +8178,10 @@
         <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.01</v>
+        <v>1.13</v>
       </c>
       <c r="O49">
-        <v>3.96</v>
+        <v>11.1</v>
       </c>
       <c r="P49">
-        <v>2.32</v>
+        <v>25</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.13</v>
+        <v>2.61</v>
       </c>
       <c r="O50">
-        <v>11.1</v>
+        <v>4.42</v>
       </c>
       <c r="P50">
-        <v>25</v>
+        <v>2.47</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8504,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>8.1</v>
+        <v>2.33</v>
       </c>
       <c r="O8">
-        <v>3.95</v>
+        <v>2.72</v>
       </c>
       <c r="P8">
-        <v>1.37</v>
+        <v>3.12</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.300000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
-        <v>5.76</v>
+        <v>4.42</v>
       </c>
       <c r="P13">
-        <v>1.39</v>
+        <v>5.13</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O14">
-        <v>4.42</v>
+        <v>5.76</v>
       </c>
       <c r="P14">
-        <v>5.13</v>
+        <v>1.39</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA14">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AB14">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>1.48</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3415,55 +3415,55 @@
         <v>3.95</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>37</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>5.18</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>4.51</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,55 +7979,55 @@
         <v>6.36</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>2.32</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>25</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,40 +8468,40 @@
         <v>2.47</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC50">
         <v>1.93</v>
@@ -8510,13 +8510,13 @@
         <v>1.87</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>2.54</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O13">
-        <v>4.42</v>
+        <v>5.76</v>
       </c>
       <c r="P13">
-        <v>5.13</v>
+        <v>1.39</v>
       </c>
       <c r="Q13">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T13">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="U13">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>4.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA13">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="AD13">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>3.29</v>
       </c>
       <c r="AK13">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>8.300000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="O14">
-        <v>5.76</v>
+        <v>4.42</v>
       </c>
       <c r="P14">
-        <v>1.39</v>
+        <v>5.13</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="R14">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="S14">
+        <v>1.3</v>
+      </c>
+      <c r="T14">
+        <v>3.64</v>
+      </c>
+      <c r="U14">
+        <v>2.27</v>
+      </c>
+      <c r="V14">
+        <v>1.61</v>
+      </c>
+      <c r="W14">
+        <v>1.14</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
         <v>1.17</v>
       </c>
-      <c r="T14">
-        <v>3.55</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14">
-        <v>1.73</v>
-      </c>
-      <c r="W14">
-        <v>1.17</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.07</v>
-      </c>
       <c r="Z14">
-        <v>6.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA14">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB14">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC14">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="AD14">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE14">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>3.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>5.36</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.08</v>
+        <v>1.76</v>
       </c>
       <c r="O44">
-        <v>15</v>
+        <v>4.41</v>
       </c>
       <c r="P44">
-        <v>37</v>
+        <v>4.51</v>
       </c>
       <c r="Q44">
+        <v>2.19</v>
+      </c>
+      <c r="R44">
+        <v>2.45</v>
+      </c>
+      <c r="S44">
         <v>1.25</v>
       </c>
-      <c r="R44">
-        <v>3.62</v>
-      </c>
-      <c r="S44">
+      <c r="T44">
+        <v>3.84</v>
+      </c>
+      <c r="U44">
+        <v>2.25</v>
+      </c>
+      <c r="V44">
+        <v>1.62</v>
+      </c>
+      <c r="W44">
         <v>1.13</v>
       </c>
-      <c r="T44">
-        <v>5.25</v>
-      </c>
-      <c r="U44">
-        <v>1.85</v>
-      </c>
-      <c r="V44">
-        <v>2.01</v>
-      </c>
-      <c r="W44">
-        <v>1.25</v>
-      </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z44">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AA44">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AB44">
-        <v>3.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC44">
-        <v>1.68</v>
+        <v>2.41</v>
       </c>
       <c r="AD44">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AE44">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AF44">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="AG44">
-        <v>1.47</v>
+        <v>2.32</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>9.699999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="O45">
-        <v>4.67</v>
+        <v>11.1</v>
       </c>
       <c r="P45">
-        <v>5.18</v>
+        <v>25</v>
       </c>
       <c r="Q45">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="R45">
-        <v>2.34</v>
+        <v>3.49</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U45">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="V45">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="W45">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z45">
-        <v>4.95</v>
+        <v>7.1</v>
       </c>
       <c r="AA45">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB45">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AC45">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AD45">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AE45">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK45">
-        <v>2.28</v>
+        <v>5.5</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.76</v>
+        <v>3.01</v>
       </c>
       <c r="O46">
-        <v>4.41</v>
+        <v>3.96</v>
       </c>
       <c r="P46">
-        <v>4.51</v>
+        <v>2.32</v>
       </c>
       <c r="Q46">
-        <v>2.19</v>
+        <v>3.05</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V46">
         <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AA46">
+        <v>1.53</v>
+      </c>
+      <c r="AB46">
+        <v>2.34</v>
+      </c>
+      <c r="AC46">
+        <v>2.33</v>
+      </c>
+      <c r="AD46">
         <v>1.57</v>
-      </c>
-      <c r="AB46">
-        <v>2.37</v>
-      </c>
-      <c r="AC46">
-        <v>2.41</v>
-      </c>
-      <c r="AD46">
-        <v>1.64</v>
       </c>
       <c r="AE46">
         <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>1.64</v>
+      </c>
+      <c r="O47">
+        <v>4.67</v>
+      </c>
+      <c r="P47">
+        <v>5.18</v>
+      </c>
+      <c r="Q47">
+        <v>2.06</v>
+      </c>
+      <c r="R47">
+        <v>2.34</v>
+      </c>
+      <c r="S47">
+        <v>1.22</v>
+      </c>
+      <c r="T47">
+        <v>4</v>
+      </c>
+      <c r="U47">
+        <v>2.31</v>
+      </c>
+      <c r="V47">
+        <v>1.62</v>
+      </c>
+      <c r="W47">
+        <v>1.15</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.11</v>
+      </c>
+      <c r="Z47">
+        <v>4.95</v>
+      </c>
+      <c r="AA47">
+        <v>1.5</v>
+      </c>
+      <c r="AB47">
+        <v>2.62</v>
+      </c>
+      <c r="AC47">
+        <v>2.3</v>
+      </c>
+      <c r="AD47">
+        <v>1.72</v>
+      </c>
+      <c r="AE47">
+        <v>1.24</v>
+      </c>
+      <c r="AF47">
         <v>1.53</v>
       </c>
-      <c r="O47">
-        <v>4.88</v>
-      </c>
-      <c r="P47">
-        <v>6.36</v>
-      </c>
-      <c r="Q47">
-        <v>1.96</v>
-      </c>
-      <c r="R47">
-        <v>2.35</v>
-      </c>
-      <c r="S47">
-        <v>1.27</v>
-      </c>
-      <c r="T47">
-        <v>3.8</v>
-      </c>
-      <c r="U47">
-        <v>2.38</v>
-      </c>
-      <c r="V47">
-        <v>1.64</v>
-      </c>
-      <c r="W47">
-        <v>1.14</v>
-      </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.12</v>
-      </c>
-      <c r="Z47">
-        <v>5.25</v>
-      </c>
-      <c r="AA47">
-        <v>1.53</v>
-      </c>
-      <c r="AB47">
-        <v>2.5</v>
-      </c>
-      <c r="AC47">
-        <v>2.42</v>
-      </c>
-      <c r="AD47">
-        <v>1.56</v>
-      </c>
-      <c r="AE47">
-        <v>1.21</v>
-      </c>
-      <c r="AF47">
-        <v>1.62</v>
-      </c>
       <c r="AG47">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK47">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.01</v>
+        <v>1.53</v>
       </c>
       <c r="O48">
-        <v>3.96</v>
+        <v>4.88</v>
       </c>
       <c r="P48">
-        <v>2.32</v>
+        <v>6.36</v>
       </c>
       <c r="Q48">
-        <v>3.05</v>
+        <v>1.96</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S48">
         <v>1.27</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U48">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="V48">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z48">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="AA48">
         <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AC48">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AD48">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE48">
         <v>1.21</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG48">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>2.56</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
+        <v>1.08</v>
+      </c>
+      <c r="O49">
+        <v>15</v>
+      </c>
+      <c r="P49">
+        <v>37</v>
+      </c>
+      <c r="Q49">
+        <v>1.25</v>
+      </c>
+      <c r="R49">
+        <v>3.62</v>
+      </c>
+      <c r="S49">
         <v>1.13</v>
       </c>
-      <c r="O49">
-        <v>11.1</v>
-      </c>
-      <c r="P49">
-        <v>25</v>
-      </c>
-      <c r="Q49">
-        <v>1.4</v>
-      </c>
-      <c r="R49">
-        <v>3.49</v>
-      </c>
-      <c r="S49">
-        <v>1.17</v>
-      </c>
       <c r="T49">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="U49">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V49">
         <v>2.01</v>
       </c>
       <c r="W49">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,28 +8332,28 @@
         <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="AA49">
         <v>1.28</v>
       </c>
       <c r="AB49">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AC49">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AD49">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AE49">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF49">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AG49">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK49">
-        <v>5.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.300000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
-        <v>5.76</v>
+        <v>4.42</v>
       </c>
       <c r="P13">
-        <v>1.39</v>
+        <v>5.13</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="R13">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="S13">
+        <v>1.3</v>
+      </c>
+      <c r="T13">
+        <v>3.64</v>
+      </c>
+      <c r="U13">
+        <v>2.27</v>
+      </c>
+      <c r="V13">
+        <v>1.61</v>
+      </c>
+      <c r="W13">
+        <v>1.14</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
         <v>1.17</v>
       </c>
-      <c r="T13">
-        <v>3.55</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>1.73</v>
-      </c>
-      <c r="W13">
-        <v>1.17</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.07</v>
-      </c>
       <c r="Z13">
-        <v>6.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB13">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="AD13">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE13">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O14">
-        <v>4.42</v>
+        <v>5.76</v>
       </c>
       <c r="P14">
-        <v>5.13</v>
+        <v>1.39</v>
       </c>
       <c r="Q14">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T14">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="U14">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>4.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA14">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AB14">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="AD14">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.16</v>
+        <v>3.29</v>
       </c>
       <c r="AK14">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.01</v>
+        <v>1.53</v>
       </c>
       <c r="O46">
-        <v>3.96</v>
+        <v>4.88</v>
       </c>
       <c r="P46">
-        <v>2.32</v>
+        <v>6.36</v>
       </c>
       <c r="Q46">
-        <v>3.05</v>
+        <v>1.96</v>
       </c>
       <c r="R46">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S46">
         <v>1.27</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z46">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="AA46">
         <v>1.53</v>
       </c>
       <c r="AB46">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AC46">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AD46">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE46">
         <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK46">
-        <v>1.4</v>
+        <v>2.56</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="O48">
-        <v>4.88</v>
+        <v>15</v>
       </c>
       <c r="P48">
-        <v>6.36</v>
+        <v>37</v>
       </c>
       <c r="Q48">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="R48">
-        <v>2.35</v>
+        <v>3.62</v>
       </c>
       <c r="S48">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="T48">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="U48">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="V48">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="AA48">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AB48">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AC48">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="AD48">
-        <v>1.56</v>
+        <v>2.14</v>
       </c>
       <c r="AE48">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AF48">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="AG48">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK48">
-        <v>2.56</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.08</v>
+        <v>3.01</v>
       </c>
       <c r="O49">
-        <v>15</v>
+        <v>3.96</v>
       </c>
       <c r="P49">
-        <v>37</v>
+        <v>2.32</v>
       </c>
       <c r="Q49">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="R49">
-        <v>3.62</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="V49">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AA49">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>3.75</v>
+        <v>2.34</v>
       </c>
       <c r="AC49">
-        <v>1.68</v>
+        <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AE49">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG49">
-        <v>1.47</v>
+        <v>2.62</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>9.699999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O13">
-        <v>4.42</v>
+        <v>5.76</v>
       </c>
       <c r="P13">
-        <v>5.13</v>
+        <v>1.39</v>
       </c>
       <c r="Q13">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T13">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="U13">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>4.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA13">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="AD13">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>3.29</v>
       </c>
       <c r="AK13">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>8.300000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="O14">
-        <v>5.76</v>
+        <v>4.42</v>
       </c>
       <c r="P14">
-        <v>1.39</v>
+        <v>5.13</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="R14">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="S14">
+        <v>1.3</v>
+      </c>
+      <c r="T14">
+        <v>3.64</v>
+      </c>
+      <c r="U14">
+        <v>2.27</v>
+      </c>
+      <c r="V14">
+        <v>1.61</v>
+      </c>
+      <c r="W14">
+        <v>1.14</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
         <v>1.17</v>
       </c>
-      <c r="T14">
-        <v>3.55</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14">
-        <v>1.73</v>
-      </c>
-      <c r="W14">
-        <v>1.17</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.07</v>
-      </c>
       <c r="Z14">
-        <v>6.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA14">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB14">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC14">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="AD14">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE14">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>3.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
+        <v>1.64</v>
+      </c>
+      <c r="O46">
+        <v>4.67</v>
+      </c>
+      <c r="P46">
+        <v>5.18</v>
+      </c>
+      <c r="Q46">
+        <v>2.06</v>
+      </c>
+      <c r="R46">
+        <v>2.34</v>
+      </c>
+      <c r="S46">
+        <v>1.22</v>
+      </c>
+      <c r="T46">
+        <v>4</v>
+      </c>
+      <c r="U46">
+        <v>2.31</v>
+      </c>
+      <c r="V46">
+        <v>1.62</v>
+      </c>
+      <c r="W46">
+        <v>1.15</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.11</v>
+      </c>
+      <c r="Z46">
+        <v>4.95</v>
+      </c>
+      <c r="AA46">
+        <v>1.5</v>
+      </c>
+      <c r="AB46">
+        <v>2.62</v>
+      </c>
+      <c r="AC46">
+        <v>2.3</v>
+      </c>
+      <c r="AD46">
+        <v>1.72</v>
+      </c>
+      <c r="AE46">
+        <v>1.24</v>
+      </c>
+      <c r="AF46">
         <v>1.53</v>
       </c>
-      <c r="O46">
-        <v>4.88</v>
-      </c>
-      <c r="P46">
-        <v>6.36</v>
-      </c>
-      <c r="Q46">
-        <v>1.96</v>
-      </c>
-      <c r="R46">
-        <v>2.35</v>
-      </c>
-      <c r="S46">
-        <v>1.27</v>
-      </c>
-      <c r="T46">
-        <v>3.8</v>
-      </c>
-      <c r="U46">
-        <v>2.38</v>
-      </c>
-      <c r="V46">
-        <v>1.64</v>
-      </c>
-      <c r="W46">
-        <v>1.14</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.12</v>
-      </c>
-      <c r="Z46">
-        <v>5.25</v>
-      </c>
-      <c r="AA46">
-        <v>1.53</v>
-      </c>
-      <c r="AB46">
-        <v>2.5</v>
-      </c>
-      <c r="AC46">
-        <v>2.42</v>
-      </c>
-      <c r="AD46">
-        <v>1.56</v>
-      </c>
-      <c r="AE46">
-        <v>1.21</v>
-      </c>
-      <c r="AF46">
-        <v>1.62</v>
-      </c>
       <c r="AG46">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.64</v>
+        <v>3.01</v>
       </c>
       <c r="O47">
-        <v>4.67</v>
+        <v>3.96</v>
       </c>
       <c r="P47">
-        <v>5.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q47">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="R47">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="V47">
         <v>1.62</v>
       </c>
       <c r="W47">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,44 +8006,44 @@
         <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA47">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
+        <v>2.34</v>
+      </c>
+      <c r="AC47">
+        <v>2.33</v>
+      </c>
+      <c r="AD47">
+        <v>1.57</v>
+      </c>
+      <c r="AE47">
+        <v>1.21</v>
+      </c>
+      <c r="AF47">
+        <v>1.44</v>
+      </c>
+      <c r="AG47">
         <v>2.62</v>
       </c>
-      <c r="AC47">
-        <v>2.3</v>
-      </c>
-      <c r="AD47">
-        <v>1.72</v>
-      </c>
-      <c r="AE47">
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.24</v>
       </c>
-      <c r="AF47">
-        <v>1.53</v>
-      </c>
-      <c r="AG47">
-        <v>2.37</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.13</v>
-      </c>
       <c r="AK47">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.01</v>
+        <v>2.61</v>
       </c>
       <c r="O49">
-        <v>3.96</v>
+        <v>4.42</v>
       </c>
       <c r="P49">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q49">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="S49">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="U49">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="W49">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Z49">
-        <v>4.9</v>
+        <v>9.5</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AB49">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="AC49">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AD49">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AE49">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="AF49">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AG49">
-        <v>2.62</v>
+        <v>4.33</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK49">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.61</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
-        <v>4.42</v>
+        <v>4.88</v>
       </c>
       <c r="P50">
-        <v>2.47</v>
+        <v>6.36</v>
       </c>
       <c r="Q50">
-        <v>2.64</v>
+        <v>1.96</v>
       </c>
       <c r="R50">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="S50">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="T50">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="V50">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="W50">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>9.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA50">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AB50">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC50">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AD50">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AE50">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK50">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>4.52</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>5.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q43">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>7.88</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>36</v>
       </c>
       <c r="Q7">
         <v>4.2</v>
@@ -1465,7 +1465,7 @@
         <v>1.89</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
         <v>2.39</v>
@@ -1489,10 +1489,10 @@
         <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AB7">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC7">
         <v>4.15</v>
@@ -1501,7 +1501,7 @@
         <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
         <v>1.91</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="O28">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>4.52</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.39</v>
+        <v>1.81</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>2.65</v>
+        <v>3.84</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>3.84</v>
+        <v>3.15</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>3.15</v>
+        <v>4.52</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.61</v>
+        <v>1.53</v>
       </c>
       <c r="O49">
-        <v>4.42</v>
+        <v>4.88</v>
       </c>
       <c r="P49">
-        <v>2.47</v>
+        <v>6.36</v>
       </c>
       <c r="Q49">
-        <v>2.64</v>
+        <v>1.96</v>
       </c>
       <c r="R49">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="S49">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="V49">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="W49">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>9.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA49">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC49">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AD49">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AE49">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AG49">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>2.61</v>
       </c>
       <c r="O50">
-        <v>4.88</v>
+        <v>4.42</v>
       </c>
       <c r="P50">
-        <v>6.36</v>
+        <v>2.47</v>
       </c>
       <c r="Q50">
-        <v>1.96</v>
+        <v>2.64</v>
       </c>
       <c r="R50">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="S50">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="U50">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="V50">
+        <v>2.01</v>
+      </c>
+      <c r="W50">
+        <v>1.33</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.01</v>
+      </c>
+      <c r="Z50">
+        <v>9.5</v>
+      </c>
+      <c r="AA50">
+        <v>1.22</v>
+      </c>
+      <c r="AB50">
+        <v>4.5</v>
+      </c>
+      <c r="AC50">
+        <v>1.93</v>
+      </c>
+      <c r="AD50">
+        <v>1.87</v>
+      </c>
+      <c r="AE50">
         <v>1.64</v>
       </c>
-      <c r="W50">
-        <v>1.14</v>
-      </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
-        <v>1.12</v>
-      </c>
-      <c r="Z50">
-        <v>5.25</v>
-      </c>
-      <c r="AA50">
-        <v>1.53</v>
-      </c>
-      <c r="AB50">
-        <v>2.5</v>
-      </c>
-      <c r="AC50">
-        <v>2.42</v>
-      </c>
-      <c r="AD50">
-        <v>1.56</v>
-      </c>
-      <c r="AE50">
-        <v>1.21</v>
-      </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>2.56</v>
+        <v>1.51</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="O6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>2.27</v>
       </c>
       <c r="R16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
         <v>1.25</v>
@@ -2950,7 +2950,7 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
         <v>4.25</v>
@@ -2959,7 +2959,7 @@
         <v>1.56</v>
       </c>
       <c r="AB16">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
         <v>2.46</v>
@@ -2974,7 +2974,7 @@
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>3.95</v>
       </c>
       <c r="Q19">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
         <v>1.36</v>
@@ -3430,10 +3430,10 @@
         <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.06</v>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P21">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
-        <v>4.52</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S31">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="U31">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
         <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
         <v>1.59</v>
@@ -5416,10 +5416,10 @@
         <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.55</v>
       </c>
       <c r="O32">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P32">
-        <v>5.33</v>
+        <v>5.44</v>
       </c>
       <c r="Q32">
         <v>2.02</v>
@@ -6349,55 +6349,55 @@
         <v>3.05</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.26</v>
+        <v>1.58</v>
       </c>
       <c r="O41">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P41">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O43">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P43">
-        <v>4.78</v>
+        <v>5.46</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="O52">
         <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S52">
         <v>1.44</v>
@@ -8818,16 +8818,16 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z52">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA52">
         <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC52">
         <v>4.4</v>
@@ -8836,7 +8836,7 @@
         <v>1.18</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF52">
         <v>1.87</v>
@@ -8858,7 +8858,7 @@
         <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>2</v>
+        <v>3.54</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>2.22</v>
+      </c>
+      <c r="R6">
+        <v>2.12</v>
+      </c>
+      <c r="S6">
+        <v>1.31</v>
+      </c>
+      <c r="T6">
+        <v>2.94</v>
+      </c>
+      <c r="U6">
+        <v>2.38</v>
+      </c>
+      <c r="V6">
+        <v>1.47</v>
+      </c>
+      <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
+        <v>1.02</v>
+      </c>
+      <c r="Y6">
+        <v>1.15</v>
+      </c>
+      <c r="Z6">
+        <v>4.3</v>
+      </c>
+      <c r="AA6">
+        <v>1.6</v>
+      </c>
+      <c r="AB6">
+        <v>2.15</v>
+      </c>
+      <c r="AC6">
+        <v>2.43</v>
+      </c>
+      <c r="AD6">
+        <v>1.44</v>
+      </c>
+      <c r="AE6">
+        <v>1.14</v>
+      </c>
+      <c r="AF6">
+        <v>1.59</v>
+      </c>
+      <c r="AG6">
+        <v>2.17</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.2</v>
       </c>
-      <c r="O6">
-        <v>5.5</v>
-      </c>
-      <c r="P6">
-        <v>9.6</v>
-      </c>
-      <c r="Q6">
-        <v>1.62</v>
-      </c>
-      <c r="R6">
-        <v>2.72</v>
-      </c>
-      <c r="S6">
-        <v>1.21</v>
-      </c>
-      <c r="T6">
-        <v>3.58</v>
-      </c>
-      <c r="U6">
-        <v>2.06</v>
-      </c>
-      <c r="V6">
-        <v>1.65</v>
-      </c>
-      <c r="W6">
-        <v>1.15</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.1</v>
-      </c>
-      <c r="Z6">
-        <v>5.2</v>
-      </c>
-      <c r="AA6">
-        <v>1.4</v>
-      </c>
-      <c r="AB6">
-        <v>2.56</v>
-      </c>
-      <c r="AC6">
-        <v>2.05</v>
-      </c>
-      <c r="AD6">
-        <v>1.66</v>
-      </c>
-      <c r="AE6">
-        <v>1.26</v>
-      </c>
-      <c r="AF6">
-        <v>1.75</v>
-      </c>
-      <c r="AG6">
-        <v>1.91</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.06</v>
-      </c>
       <c r="AK6">
-        <v>3.54</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>7.88</v>
       </c>
       <c r="P7">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="Q7">
         <v>4.2</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.33</v>
+        <v>6.5</v>
       </c>
       <c r="O8">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>3.12</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
-        <v>3.32</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
+        <v>2.48</v>
+      </c>
+      <c r="U8">
+        <v>3.1</v>
+      </c>
+      <c r="V8">
+        <v>1.33</v>
+      </c>
+      <c r="W8">
+        <v>1.02</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.35</v>
+      </c>
+      <c r="Z8">
+        <v>2.88</v>
+      </c>
+      <c r="AA8">
+        <v>2.2</v>
+      </c>
+      <c r="AB8">
+        <v>1.6</v>
+      </c>
+      <c r="AC8">
+        <v>3.96</v>
+      </c>
+      <c r="AD8">
+        <v>1.17</v>
+      </c>
+      <c r="AE8">
+        <v>1.02</v>
+      </c>
+      <c r="AF8">
         <v>2.4</v>
       </c>
-      <c r="U8">
-        <v>3.5</v>
-      </c>
-      <c r="V8">
-        <v>1.22</v>
-      </c>
-      <c r="W8">
-        <v>1.04</v>
-      </c>
-      <c r="X8">
-        <v>1.12</v>
-      </c>
-      <c r="Y8">
-        <v>1.54</v>
-      </c>
-      <c r="Z8">
-        <v>2.36</v>
-      </c>
-      <c r="AA8">
-        <v>2.71</v>
-      </c>
-      <c r="AB8">
-        <v>1.44</v>
-      </c>
-      <c r="AC8">
-        <v>4.95</v>
-      </c>
-      <c r="AD8">
-        <v>1.15</v>
-      </c>
-      <c r="AE8">
-        <v>1.01</v>
-      </c>
-      <c r="AF8">
-        <v>2.1</v>
-      </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AK8">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>8.1</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="P9">
-        <v>1.37</v>
+        <v>3.26</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="R9">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T9">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U9">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="Z9">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="AA9">
-        <v>2.17</v>
+        <v>2.52</v>
       </c>
       <c r="AB9">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AC9">
-        <v>3.96</v>
+        <v>4.95</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AG9">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="O11">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q11">
         <v>3.5</v>
@@ -2117,13 +2117,13 @@
         <v>1.92</v>
       </c>
       <c r="S11">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V11">
         <v>1.3</v>
@@ -2132,19 +2132,19 @@
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
         <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB11">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
         <v>3.98</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
         <v>1.33</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O13">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="P13">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -2446,7 +2446,7 @@
         <v>1.17</v>
       </c>
       <c r="T13">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2464,13 +2464,13 @@
         <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC13">
         <v>2.12</v>
@@ -2479,10 +2479,10 @@
         <v>1.75</v>
       </c>
       <c r="AE13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
         <v>2.05</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="AK13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>5.13</v>
+        <v>4.5</v>
       </c>
       <c r="Q14">
         <v>2.14</v>
@@ -2627,13 +2627,13 @@
         <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA14">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AB14">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AC14">
         <v>2.46</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,13 +2757,13 @@
         <v>6.47</v>
       </c>
       <c r="O15">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
         <v>1.48</v>
       </c>
       <c r="Q15">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>2.1</v>
@@ -2775,16 +2775,16 @@
         <v>2.62</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
         <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.32</v>
@@ -2793,7 +2793,7 @@
         <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB15">
         <v>1.63</v>
@@ -2805,10 +2805,10 @@
         <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG15">
         <v>1.6</v>
@@ -2947,7 +2947,7 @@
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.15</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="Q31">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
         <v>1.5</v>
@@ -6370,7 +6370,7 @@
         <v>1.09</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.17</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.26</v>
+      </c>
+      <c r="O41">
+        <v>3.55</v>
+      </c>
+      <c r="P41">
+        <v>2.89</v>
+      </c>
+      <c r="Q41">
+        <v>2.8</v>
+      </c>
+      <c r="R41">
+        <v>2.25</v>
+      </c>
+      <c r="S41">
+        <v>1.3</v>
+      </c>
+      <c r="T41">
+        <v>3.3</v>
+      </c>
+      <c r="U41">
+        <v>2.35</v>
+      </c>
+      <c r="V41">
+        <v>1.5</v>
+      </c>
+      <c r="W41">
+        <v>1.09</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>1.18</v>
+      </c>
+      <c r="Z41">
+        <v>3.92</v>
+      </c>
+      <c r="AA41">
+        <v>1.72</v>
+      </c>
+      <c r="AB41">
+        <v>2.05</v>
+      </c>
+      <c r="AC41">
+        <v>2.74</v>
+      </c>
+      <c r="AD41">
+        <v>1.35</v>
+      </c>
+      <c r="AE41">
+        <v>1.1</v>
+      </c>
+      <c r="AF41">
         <v>1.58</v>
       </c>
-      <c r="O41">
-        <v>4.5</v>
-      </c>
-      <c r="P41">
-        <v>5</v>
-      </c>
-      <c r="Q41">
-        <v>2.05</v>
-      </c>
-      <c r="R41">
-        <v>2.5</v>
-      </c>
-      <c r="S41">
-        <v>1.18</v>
-      </c>
-      <c r="T41">
-        <v>4</v>
-      </c>
-      <c r="U41">
-        <v>2.02</v>
-      </c>
-      <c r="V41">
-        <v>1.68</v>
-      </c>
-      <c r="W41">
-        <v>1.17</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.09</v>
-      </c>
-      <c r="Z41">
-        <v>5.25</v>
-      </c>
-      <c r="AA41">
-        <v>1.4</v>
-      </c>
-      <c r="AB41">
-        <v>2.56</v>
-      </c>
-      <c r="AC41">
-        <v>2.09</v>
-      </c>
-      <c r="AD41">
-        <v>1.69</v>
-      </c>
-      <c r="AE41">
-        <v>1.25</v>
-      </c>
-      <c r="AF41">
-        <v>1.5</v>
-      </c>
       <c r="AG41">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O43">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P43">
-        <v>5.46</v>
+        <v>5.25</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -7339,7 +7339,7 @@
         <v>4.2</v>
       </c>
       <c r="U43">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="V43">
         <v>1.73</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O44">
-        <v>4.41</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>4.51</v>
+        <v>4.34</v>
       </c>
       <c r="Q44">
         <v>2.19</v>
@@ -7505,10 +7505,10 @@
         <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
         <v>1.03</v>
@@ -7520,13 +7520,13 @@
         <v>4.6</v>
       </c>
       <c r="AA44">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB44">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AC44">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AD44">
         <v>1.64</v>
@@ -7535,10 +7535,10 @@
         <v>1.21</v>
       </c>
       <c r="AF44">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK44">
         <v>2.18</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="O45">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="P45">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Q45">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R45">
-        <v>3.49</v>
+        <v>3.15</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T45">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="U45">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V45">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="W45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z45">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA45">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB45">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AC45">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AD45">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AE45">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG45">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK45">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="O46">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="P46">
-        <v>5.18</v>
+        <v>4.45</v>
       </c>
       <c r="Q46">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R46">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
         <v>1.22</v>
@@ -7834,7 +7834,7 @@
         <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7846,25 +7846,25 @@
         <v>4.95</v>
       </c>
       <c r="AA46">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB46">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AC46">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD46">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AE46">
         <v>1.24</v>
       </c>
       <c r="AF46">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O47">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q47">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="S47">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="U47">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W47">
         <v>1.17</v>
@@ -8003,7 +8003,7 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
         <v>4.9</v>
@@ -8012,13 +8012,13 @@
         <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AC47">
         <v>2.33</v>
       </c>
       <c r="AD47">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE47">
         <v>1.21</v>
@@ -8136,16 +8136,16 @@
         <v>1.08</v>
       </c>
       <c r="O48">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="P48">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R48">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="S48">
         <v>1.13</v>
@@ -8160,7 +8160,7 @@
         <v>2.01</v>
       </c>
       <c r="W48">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,28 +8169,28 @@
         <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="AA48">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB48">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AC48">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AD48">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AE48">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF48">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AG48">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK48">
         <v>9.699999999999999</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O49">
-        <v>4.88</v>
+        <v>4.6</v>
       </c>
       <c r="P49">
-        <v>6.36</v>
+        <v>5.3</v>
       </c>
       <c r="Q49">
         <v>1.96</v>
@@ -8317,13 +8317,13 @@
         <v>3.8</v>
       </c>
       <c r="U49">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8335,25 +8335,25 @@
         <v>5.25</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC49">
         <v>2.42</v>
       </c>
       <c r="AD49">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE49">
         <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="O50">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="P50">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q50">
         <v>2.64</v>
@@ -8474,7 +8474,7 @@
         <v>2.62</v>
       </c>
       <c r="S50">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T50">
         <v>5.4</v>
@@ -8483,13 +8483,13 @@
         <v>1.71</v>
       </c>
       <c r="V50">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="W50">
         <v>1.33</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y50">
         <v>1.01</v>
@@ -8498,25 +8498,25 @@
         <v>9.5</v>
       </c>
       <c r="AA50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AB50">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AC50">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AD50">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AE50">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF50">
         <v>1.2</v>
       </c>
       <c r="AG50">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>3.35</v>
       </c>
       <c r="P51">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1456,7 +1456,7 @@
         <v>7.88</v>
       </c>
       <c r="P7">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="Q7">
         <v>4.2</v>
@@ -2947,7 +2947,7 @@
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.15</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P27">
-        <v>5.95</v>
+        <v>6.2</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
         <v>4.2</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="O38">
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P39">
+        <v>5</v>
+      </c>
+      <c r="Q39">
         <v>2.05</v>
       </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>2.26</v>
+      </c>
+      <c r="O40">
+        <v>3.55</v>
+      </c>
+      <c r="P40">
+        <v>2.89</v>
+      </c>
+      <c r="Q40">
+        <v>2.8</v>
+      </c>
+      <c r="R40">
+        <v>2.25</v>
+      </c>
+      <c r="S40">
+        <v>1.28</v>
+      </c>
+      <c r="T40">
+        <v>3.26</v>
+      </c>
+      <c r="U40">
+        <v>2.35</v>
+      </c>
+      <c r="V40">
+        <v>1.5</v>
+      </c>
+      <c r="W40">
+        <v>1.08</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.18</v>
+      </c>
+      <c r="Z40">
+        <v>3.92</v>
+      </c>
+      <c r="AA40">
+        <v>1.72</v>
+      </c>
+      <c r="AB40">
+        <v>2.05</v>
+      </c>
+      <c r="AC40">
+        <v>2.74</v>
+      </c>
+      <c r="AD40">
+        <v>1.35</v>
+      </c>
+      <c r="AE40">
+        <v>1.1</v>
+      </c>
+      <c r="AF40">
         <v>1.58</v>
       </c>
-      <c r="O40">
-        <v>4.5</v>
-      </c>
-      <c r="P40">
-        <v>5</v>
-      </c>
-      <c r="Q40">
-        <v>2.05</v>
-      </c>
-      <c r="R40">
-        <v>2.5</v>
-      </c>
-      <c r="S40">
-        <v>1.18</v>
-      </c>
-      <c r="T40">
-        <v>4</v>
-      </c>
-      <c r="U40">
-        <v>2.02</v>
-      </c>
-      <c r="V40">
-        <v>1.68</v>
-      </c>
-      <c r="W40">
-        <v>1.17</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.09</v>
-      </c>
-      <c r="Z40">
-        <v>5.25</v>
-      </c>
-      <c r="AA40">
-        <v>1.4</v>
-      </c>
-      <c r="AB40">
-        <v>2.56</v>
-      </c>
-      <c r="AC40">
-        <v>2.09</v>
-      </c>
-      <c r="AD40">
-        <v>1.69</v>
-      </c>
-      <c r="AE40">
-        <v>1.25</v>
-      </c>
-      <c r="AF40">
-        <v>1.5</v>
-      </c>
       <c r="AG40">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>2.15</v>
+      </c>
+      <c r="O43">
+        <v>3.6</v>
+      </c>
+      <c r="P43">
+        <v>3.05</v>
+      </c>
+      <c r="Q43">
+        <v>2.75</v>
+      </c>
+      <c r="R43">
+        <v>2.25</v>
+      </c>
+      <c r="S43">
+        <v>1.3</v>
+      </c>
+      <c r="T43">
+        <v>3.3</v>
+      </c>
+      <c r="U43">
+        <v>2.45</v>
+      </c>
+      <c r="V43">
         <v>1.5</v>
       </c>
-      <c r="O43">
-        <v>4.75</v>
-      </c>
-      <c r="P43">
-        <v>5.25</v>
-      </c>
-      <c r="Q43">
-        <v>1.95</v>
-      </c>
-      <c r="R43">
-        <v>2.6</v>
-      </c>
-      <c r="S43">
-        <v>1.2</v>
-      </c>
-      <c r="T43">
-        <v>4.2</v>
-      </c>
-      <c r="U43">
-        <v>1.95</v>
-      </c>
-      <c r="V43">
-        <v>1.73</v>
-      </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>5.45</v>
+        <v>3.98</v>
       </c>
       <c r="AA43">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AB43">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="AC43">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AD43">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>2.51</v>
+        <v>1.66</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1148,7 +1148,7 @@
         <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W5">
         <v>1.15</v>
@@ -1314,7 +1314,7 @@
         <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>1.02</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1181,7 +1181,7 @@
         <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
         <v>1.07</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
+        <v>2.26</v>
+      </c>
+      <c r="O39">
+        <v>3.55</v>
+      </c>
+      <c r="P39">
+        <v>2.89</v>
+      </c>
+      <c r="Q39">
+        <v>2.8</v>
+      </c>
+      <c r="R39">
+        <v>2.25</v>
+      </c>
+      <c r="S39">
+        <v>1.28</v>
+      </c>
+      <c r="T39">
+        <v>3.26</v>
+      </c>
+      <c r="U39">
+        <v>2.35</v>
+      </c>
+      <c r="V39">
+        <v>1.5</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>3.92</v>
+      </c>
+      <c r="AA39">
+        <v>1.72</v>
+      </c>
+      <c r="AB39">
+        <v>2.05</v>
+      </c>
+      <c r="AC39">
+        <v>2.74</v>
+      </c>
+      <c r="AD39">
+        <v>1.35</v>
+      </c>
+      <c r="AE39">
+        <v>1.1</v>
+      </c>
+      <c r="AF39">
         <v>1.58</v>
       </c>
-      <c r="O39">
-        <v>4.5</v>
-      </c>
-      <c r="P39">
-        <v>5</v>
-      </c>
-      <c r="Q39">
-        <v>2.05</v>
-      </c>
-      <c r="R39">
-        <v>2.5</v>
-      </c>
-      <c r="S39">
-        <v>1.18</v>
-      </c>
-      <c r="T39">
-        <v>4</v>
-      </c>
-      <c r="U39">
-        <v>2.02</v>
-      </c>
-      <c r="V39">
-        <v>1.68</v>
-      </c>
-      <c r="W39">
-        <v>1.18</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.09</v>
-      </c>
-      <c r="Z39">
-        <v>5.25</v>
-      </c>
-      <c r="AA39">
-        <v>1.4</v>
-      </c>
-      <c r="AB39">
-        <v>2.56</v>
-      </c>
-      <c r="AC39">
-        <v>2.09</v>
-      </c>
-      <c r="AD39">
-        <v>1.69</v>
-      </c>
-      <c r="AE39">
-        <v>1.25</v>
-      </c>
-      <c r="AF39">
-        <v>1.5</v>
-      </c>
       <c r="AG39">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>2.15</v>
+      </c>
+      <c r="O42">
+        <v>3.6</v>
+      </c>
+      <c r="P42">
+        <v>3.05</v>
+      </c>
+      <c r="Q42">
+        <v>2.75</v>
+      </c>
+      <c r="R42">
+        <v>2.25</v>
+      </c>
+      <c r="S42">
+        <v>1.3</v>
+      </c>
+      <c r="T42">
+        <v>3.3</v>
+      </c>
+      <c r="U42">
+        <v>2.45</v>
+      </c>
+      <c r="V42">
         <v>1.5</v>
       </c>
-      <c r="O42">
-        <v>4.75</v>
-      </c>
-      <c r="P42">
-        <v>5.25</v>
-      </c>
-      <c r="Q42">
-        <v>1.95</v>
-      </c>
-      <c r="R42">
-        <v>2.6</v>
-      </c>
-      <c r="S42">
-        <v>1.2</v>
-      </c>
-      <c r="T42">
-        <v>4.2</v>
-      </c>
-      <c r="U42">
-        <v>1.95</v>
-      </c>
-      <c r="V42">
-        <v>1.74</v>
-      </c>
       <c r="W42">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>5.45</v>
+        <v>3.98</v>
       </c>
       <c r="AA42">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="AC42">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AD42">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>2.51</v>
+        <v>1.66</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="Q43">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T43">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="V43">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W43">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>3.98</v>
+        <v>5.25</v>
       </c>
       <c r="AA43">
+        <v>1.4</v>
+      </c>
+      <c r="AB43">
+        <v>2.56</v>
+      </c>
+      <c r="AC43">
+        <v>2.09</v>
+      </c>
+      <c r="AD43">
         <v>1.69</v>
       </c>
-      <c r="AB43">
-        <v>2.09</v>
-      </c>
-      <c r="AC43">
-        <v>2.62</v>
-      </c>
-      <c r="AD43">
-        <v>1.38</v>
-      </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>2.85</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
         <v>2.4</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1616,22 +1616,22 @@
         <v>6.5</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U8">
         <v>3.1</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="O9">
         <v>2.8</v>
       </c>
       <c r="P9">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
@@ -1800,7 +1800,7 @@
         <v>3.5</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
         <v>3.1</v>
@@ -2159,7 +2159,7 @@
         <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="P14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
         <v>2.14</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>6.47</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
         <v>3.7</v>
       </c>
       <c r="P15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q15">
         <v>6</v>
@@ -2775,10 +2775,10 @@
         <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2793,7 +2793,7 @@
         <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AB15">
         <v>1.63</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O30">
         <v>4.2</v>
       </c>
       <c r="P30">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
         <v>2.12</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P42">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z42">
-        <v>3.98</v>
+        <v>5.25</v>
       </c>
       <c r="AA42">
+        <v>1.4</v>
+      </c>
+      <c r="AB42">
+        <v>2.56</v>
+      </c>
+      <c r="AC42">
+        <v>2.09</v>
+      </c>
+      <c r="AD42">
         <v>1.69</v>
       </c>
-      <c r="AB42">
-        <v>2.09</v>
-      </c>
-      <c r="AC42">
-        <v>2.62</v>
-      </c>
-      <c r="AD42">
-        <v>1.38</v>
-      </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="Q43">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U43">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="V43">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>5.25</v>
+        <v>3.98</v>
       </c>
       <c r="AA43">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AB43">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="AC43">
-        <v>2.09</v>
+        <v>2.62</v>
       </c>
       <c r="AD43">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7535,10 +7535,10 @@
         <v>1.21</v>
       </c>
       <c r="AF44">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG44">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>12</v>
       </c>
       <c r="Q45">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="R45">
         <v>3.15</v>
@@ -7683,7 +7683,7 @@
         <v>6.5</v>
       </c>
       <c r="AA45">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB45">
         <v>3.08</v>
@@ -7698,7 +7698,7 @@
         <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
         <v>1.85</v>
@@ -7849,7 +7849,7 @@
         <v>1.46</v>
       </c>
       <c r="AB46">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AC46">
         <v>2.1</v>
@@ -8012,7 +8012,7 @@
         <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC47">
         <v>2.33</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="O48">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="P48">
         <v>34</v>
@@ -8163,7 +8163,7 @@
         <v>1.31</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48">
         <v>1.04</v>
@@ -8175,7 +8175,7 @@
         <v>1.25</v>
       </c>
       <c r="AB48">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="AC48">
         <v>1.78</v>
@@ -8299,10 +8299,10 @@
         <v>1.51</v>
       </c>
       <c r="O49">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P49">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q49">
         <v>1.96</v>
@@ -8314,7 +8314,7 @@
         <v>1.27</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="U49">
         <v>2.25</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
         <v>4.2</v>
@@ -8498,10 +8498,10 @@
         <v>9.5</v>
       </c>
       <c r="AA50">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AB50">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AC50">
         <v>1.54</v>
@@ -8510,7 +8510,7 @@
         <v>2.29</v>
       </c>
       <c r="AE50">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF50">
         <v>1.2</v>
@@ -8797,7 +8797,7 @@
         <v>3.4</v>
       </c>
       <c r="R52">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S52">
         <v>1.44</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="O19">
+        <v>3.25</v>
+      </c>
+      <c r="P19">
         <v>3.3</v>
       </c>
-      <c r="P19">
-        <v>3.95</v>
-      </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z19">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA19">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="O21">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
         <v>2.45</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.19</v>
+        <v>2.14</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4716,58 +4716,58 @@
         <v>4.5</v>
       </c>
       <c r="P27">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P28">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="O30">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q30">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="U30">
+        <v>2.29</v>
+      </c>
+      <c r="V30">
+        <v>1.53</v>
+      </c>
+      <c r="W30">
+        <v>1.12</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.17</v>
+      </c>
+      <c r="Z30">
+        <v>3.95</v>
+      </c>
+      <c r="AA30">
+        <v>1.66</v>
+      </c>
+      <c r="AB30">
         <v>2.19</v>
       </c>
-      <c r="V30">
-        <v>1.58</v>
-      </c>
-      <c r="W30">
+      <c r="AC30">
+        <v>2.52</v>
+      </c>
+      <c r="AD30">
+        <v>1.41</v>
+      </c>
+      <c r="AE30">
         <v>1.13</v>
       </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.15</v>
-      </c>
-      <c r="Z30">
-        <v>4.25</v>
-      </c>
-      <c r="AA30">
-        <v>1.59</v>
-      </c>
-      <c r="AB30">
-        <v>2.25</v>
-      </c>
-      <c r="AC30">
-        <v>2.38</v>
-      </c>
-      <c r="AD30">
-        <v>1.46</v>
-      </c>
-      <c r="AE30">
-        <v>1.16</v>
-      </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AG30">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>3.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O32">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>5.44</v>
+        <v>5.07</v>
       </c>
       <c r="Q32">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R32">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="U32">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
+        <v>1.24</v>
+      </c>
+      <c r="Z32">
+        <v>3.82</v>
+      </c>
+      <c r="AA32">
+        <v>1.77</v>
+      </c>
+      <c r="AB32">
+        <v>2.08</v>
+      </c>
+      <c r="AC32">
+        <v>2.91</v>
+      </c>
+      <c r="AD32">
+        <v>1.4</v>
+      </c>
+      <c r="AE32">
         <v>1.15</v>
       </c>
-      <c r="Z32">
-        <v>4.3</v>
-      </c>
-      <c r="AA32">
-        <v>1.61</v>
-      </c>
-      <c r="AB32">
-        <v>2.23</v>
-      </c>
-      <c r="AC32">
-        <v>2.43</v>
-      </c>
-      <c r="AD32">
-        <v>1.44</v>
-      </c>
-      <c r="AE32">
-        <v>1.14</v>
-      </c>
       <c r="AF32">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="O33">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.26</v>
+        <v>3.9</v>
       </c>
       <c r="O36">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="O39">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
+        <v>2.4</v>
+      </c>
+      <c r="S39">
+        <v>1.25</v>
+      </c>
+      <c r="T39">
+        <v>3.6</v>
+      </c>
+      <c r="U39">
         <v>2.25</v>
       </c>
-      <c r="S39">
-        <v>1.28</v>
-      </c>
-      <c r="T39">
-        <v>3.26</v>
-      </c>
-      <c r="U39">
-        <v>2.35</v>
-      </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>3.92</v>
+        <v>5.13</v>
       </c>
       <c r="AA39">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AC39">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AD39">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF39">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P40">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O41">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="P41">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q41">
         <v>1.95</v>
       </c>
       <c r="R41">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T41">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U41">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V41">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W41">
         <v>1.18</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z41">
-        <v>5.45</v>
+        <v>5.57</v>
       </c>
       <c r="AA41">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AB41">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AC41">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AD41">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="O42">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q42">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T42">
         <v>4</v>
       </c>
       <c r="U42">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V42">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
-        <v>5.25</v>
+        <v>6.06</v>
       </c>
       <c r="AA42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB42">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC42">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AD42">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF42">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P43">
         <v>3.05</v>
       </c>
       <c r="Q43">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
         <v>2.25</v>
@@ -7336,46 +7336,46 @@
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.98</v>
+        <v>3.87</v>
       </c>
       <c r="AA43">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB43">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="AD43">
         <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>2.85</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P51">
         <v>2.4</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>5.36</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
+        <v>2.38</v>
+      </c>
+      <c r="R16">
+        <v>2.38</v>
+      </c>
+      <c r="S16">
+        <v>1.29</v>
+      </c>
+      <c r="T16">
+        <v>3.4</v>
+      </c>
+      <c r="U16">
         <v>2.27</v>
       </c>
-      <c r="R16">
-        <v>2.3</v>
-      </c>
-      <c r="S16">
-        <v>1.25</v>
-      </c>
-      <c r="T16">
-        <v>3.24</v>
-      </c>
-      <c r="U16">
-        <v>2.32</v>
-      </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -2950,31 +2950,31 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA16">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC16">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>3.25</v>
       </c>
       <c r="P19">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
         <v>2.68</v>
@@ -3460,7 +3460,7 @@
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG19">
         <v>1.78</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="U20">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
         <v>1.02</v>
@@ -3608,25 +3608,25 @@
         <v>3.23</v>
       </c>
       <c r="AA20">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AB20">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
         <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG20">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="O22">
         <v>3.15</v>
       </c>
       <c r="P22">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U22">
         <v>2.82</v>
@@ -3922,7 +3922,7 @@
         <v>1.42</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3934,25 +3934,25 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB22">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="AD22">
         <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
         <v>2.85</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P24">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="O25">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S25">
+        <v>1.38</v>
+      </c>
+      <c r="T25">
+        <v>2.74</v>
+      </c>
+      <c r="U25">
+        <v>2.8</v>
+      </c>
+      <c r="V25">
         <v>1.4</v>
       </c>
-      <c r="T25">
-        <v>2.67</v>
-      </c>
-      <c r="U25">
-        <v>2.82</v>
-      </c>
-      <c r="V25">
-        <v>1.36</v>
-      </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="AA25">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB25">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC25">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG25">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="P26">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>2.86</v>
+        <v>1.85</v>
       </c>
       <c r="R26">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>2.74</v>
+        <v>3.78</v>
       </c>
       <c r="U26">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="Z26">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA26">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="AB26">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="AC26">
-        <v>3.34</v>
+        <v>2.16</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AF26">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="O27">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>5</v>
+        <v>2.43</v>
       </c>
       <c r="Q27">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.26</v>
       </c>
       <c r="U27">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
+        <v>1.11</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
         <v>1.17</v>
       </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.12</v>
-      </c>
       <c r="Z27">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA27">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AB27">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AC27">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AD27">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="AE27">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
+        <v>3.25</v>
+      </c>
+      <c r="O28">
+        <v>3.45</v>
+      </c>
+      <c r="P28">
+        <v>1.9</v>
+      </c>
+      <c r="Q28">
+        <v>3.88</v>
+      </c>
+      <c r="R28">
+        <v>2.25</v>
+      </c>
+      <c r="S28">
+        <v>1.29</v>
+      </c>
+      <c r="T28">
+        <v>3.4</v>
+      </c>
+      <c r="U28">
+        <v>2.56</v>
+      </c>
+      <c r="V28">
+        <v>1.48</v>
+      </c>
+      <c r="W28">
+        <v>1.1</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>1.21</v>
+      </c>
+      <c r="Z28">
+        <v>4.16</v>
+      </c>
+      <c r="AA28">
+        <v>1.66</v>
+      </c>
+      <c r="AB28">
+        <v>2.11</v>
+      </c>
+      <c r="AC28">
+        <v>2.79</v>
+      </c>
+      <c r="AD28">
+        <v>1.42</v>
+      </c>
+      <c r="AE28">
+        <v>1.12</v>
+      </c>
+      <c r="AF28">
         <v>1.57</v>
       </c>
-      <c r="O28">
-        <v>3.85</v>
-      </c>
-      <c r="P28">
-        <v>4.5</v>
-      </c>
-      <c r="Q28">
-        <v>2.05</v>
-      </c>
-      <c r="R28">
-        <v>2.54</v>
-      </c>
-      <c r="S28">
-        <v>1.25</v>
-      </c>
-      <c r="T28">
-        <v>3.32</v>
-      </c>
-      <c r="U28">
-        <v>2.31</v>
-      </c>
-      <c r="V28">
-        <v>1.55</v>
-      </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.15</v>
-      </c>
-      <c r="Z28">
-        <v>4.25</v>
-      </c>
-      <c r="AA28">
-        <v>1.59</v>
-      </c>
-      <c r="AB28">
-        <v>2.33</v>
-      </c>
-      <c r="AC28">
-        <v>2.38</v>
-      </c>
-      <c r="AD28">
-        <v>1.46</v>
-      </c>
-      <c r="AE28">
-        <v>1.16</v>
-      </c>
-      <c r="AF28">
-        <v>1.64</v>
-      </c>
       <c r="AG28">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="Q29">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U29">
         <v>2.64</v>
@@ -5069,16 +5069,16 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z29">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA29">
         <v>1.77</v>
       </c>
       <c r="AB29">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC29">
         <v>2.83</v>
@@ -5087,13 +5087,13 @@
         <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AK29">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R30">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>3.26</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.29</v>
+        <v>2.82</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>3.95</v>
+        <v>3.39</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>2.52</v>
+        <v>3.45</v>
       </c>
       <c r="AD30">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AG30">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q31">
-        <v>4.03</v>
+        <v>2.05</v>
       </c>
       <c r="R31">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>2.86</v>
+        <v>3.32</v>
       </c>
       <c r="U31">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AB31">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG31">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
         <v>3.22</v>
@@ -5552,10 +5552,10 @@
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.24</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>2.43</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.9</v>
+        <v>2.57</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>1.66</v>
+        <v>2.49</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.44</v>
+        <v>3.46</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P37">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.46</v>
+        <v>2.37</v>
       </c>
       <c r="O38">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>2.07</v>
+        <v>2.57</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P39">
-        <v>2.57</v>
+        <v>1.97</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>5.13</v>
+        <v>4.1</v>
       </c>
       <c r="AA39">
+        <v>1.64</v>
+      </c>
+      <c r="AB39">
+        <v>2.17</v>
+      </c>
+      <c r="AC39">
+        <v>2.49</v>
+      </c>
+      <c r="AD39">
+        <v>1.42</v>
+      </c>
+      <c r="AE39">
+        <v>1.14</v>
+      </c>
+      <c r="AF39">
         <v>1.56</v>
       </c>
-      <c r="AB39">
-        <v>2.26</v>
-      </c>
-      <c r="AC39">
-        <v>2.44</v>
-      </c>
-      <c r="AD39">
-        <v>1.55</v>
-      </c>
-      <c r="AE39">
-        <v>1.21</v>
-      </c>
-      <c r="AF39">
-        <v>1.44</v>
-      </c>
       <c r="AG39">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.38</v>
+        <v>1.57</v>
       </c>
       <c r="O40">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.97</v>
+        <v>5.5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41">
@@ -6995,61 +6995,61 @@
         <v>1.51</v>
       </c>
       <c r="O41">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P41">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="Q41">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R41">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="S41">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U41">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z41">
-        <v>5.57</v>
+        <v>6.08</v>
       </c>
       <c r="AA41">
         <v>1.41</v>
       </c>
       <c r="AB41">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="AC41">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AD41">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.54</v>
+        <v>3.65</v>
       </c>
       <c r="O42">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="Q42">
-        <v>1.85</v>
+        <v>4.33</v>
       </c>
       <c r="R42">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="V42">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>6.06</v>
+        <v>4.9</v>
       </c>
       <c r="AA42">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB42">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="AD42">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AE42">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.38</v>
+        <v>1.21</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O43">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="Q43">
         <v>2.5</v>
@@ -7354,16 +7354,16 @@
         <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="AA43">
         <v>1.83</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC43">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="AD43">
         <v>1.38</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="O45">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
-        <v>12</v>
+        <v>4.45</v>
       </c>
       <c r="Q45">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="R45">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="V45">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="W45">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA45">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AB45">
-        <v>3.08</v>
+        <v>2.46</v>
       </c>
       <c r="AC45">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AE45">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AF45">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>4.65</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="O46">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>4.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="U46">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA46">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC46">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD46">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AE46">
+        <v>1.21</v>
+      </c>
+      <c r="AF46">
+        <v>1.44</v>
+      </c>
+      <c r="AG46">
+        <v>2.62</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.24</v>
       </c>
-      <c r="AF46">
-        <v>1.6</v>
-      </c>
-      <c r="AG46">
-        <v>2.3</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.14</v>
-      </c>
       <c r="AK46">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.8</v>
+        <v>1.05</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="P47">
-        <v>2.3</v>
+        <v>34</v>
       </c>
       <c r="Q47">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="R47">
+        <v>3.9</v>
+      </c>
+      <c r="S47">
+        <v>1.13</v>
+      </c>
+      <c r="T47">
+        <v>5.25</v>
+      </c>
+      <c r="U47">
+        <v>1.85</v>
+      </c>
+      <c r="V47">
+        <v>2.01</v>
+      </c>
+      <c r="W47">
+        <v>1.31</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>1.04</v>
+      </c>
+      <c r="Z47">
+        <v>7.1</v>
+      </c>
+      <c r="AA47">
+        <v>1.25</v>
+      </c>
+      <c r="AB47">
+        <v>3.75</v>
+      </c>
+      <c r="AC47">
+        <v>1.78</v>
+      </c>
+      <c r="AD47">
+        <v>2.2</v>
+      </c>
+      <c r="AE47">
+        <v>1.47</v>
+      </c>
+      <c r="AF47">
         <v>2.52</v>
       </c>
-      <c r="S47">
-        <v>1.25</v>
-      </c>
-      <c r="T47">
-        <v>3.84</v>
-      </c>
-      <c r="U47">
-        <v>2.25</v>
-      </c>
-      <c r="V47">
-        <v>1.7</v>
-      </c>
-      <c r="W47">
-        <v>1.17</v>
-      </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.13</v>
-      </c>
-      <c r="Z47">
-        <v>4.9</v>
-      </c>
-      <c r="AA47">
-        <v>1.53</v>
-      </c>
-      <c r="AB47">
-        <v>2.4</v>
-      </c>
-      <c r="AC47">
-        <v>2.33</v>
-      </c>
-      <c r="AD47">
-        <v>1.61</v>
-      </c>
-      <c r="AE47">
-        <v>1.21</v>
-      </c>
-      <c r="AF47">
-        <v>1.44</v>
-      </c>
       <c r="AG47">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AK47">
-        <v>1.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="O48">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="P48">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="Q48">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="R48">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="S48">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="T48">
+        <v>3.65</v>
+      </c>
+      <c r="U48">
+        <v>2.25</v>
+      </c>
+      <c r="V48">
+        <v>1.65</v>
+      </c>
+      <c r="W48">
+        <v>1.15</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.12</v>
+      </c>
+      <c r="Z48">
         <v>5.25</v>
       </c>
-      <c r="U48">
-        <v>1.85</v>
-      </c>
-      <c r="V48">
-        <v>2.01</v>
-      </c>
-      <c r="W48">
-        <v>1.31</v>
-      </c>
-      <c r="X48">
-        <v>1</v>
-      </c>
-      <c r="Y48">
-        <v>1.04</v>
-      </c>
-      <c r="Z48">
-        <v>7.1</v>
-      </c>
       <c r="AA48">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="AD48">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AE48">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AF48">
-        <v>2.52</v>
+        <v>1.65</v>
       </c>
       <c r="AG48">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AK48">
-        <v>9.699999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
+        <v>2.4</v>
+      </c>
+      <c r="O49">
+        <v>4.2</v>
+      </c>
+      <c r="P49">
+        <v>2.45</v>
+      </c>
+      <c r="Q49">
+        <v>2.64</v>
+      </c>
+      <c r="R49">
+        <v>2.62</v>
+      </c>
+      <c r="S49">
+        <v>1.15</v>
+      </c>
+      <c r="T49">
+        <v>5.4</v>
+      </c>
+      <c r="U49">
+        <v>1.71</v>
+      </c>
+      <c r="V49">
+        <v>2.15</v>
+      </c>
+      <c r="W49">
+        <v>1.33</v>
+      </c>
+      <c r="X49">
+        <v>1</v>
+      </c>
+      <c r="Y49">
+        <v>1.01</v>
+      </c>
+      <c r="Z49">
+        <v>9.5</v>
+      </c>
+      <c r="AA49">
+        <v>1.22</v>
+      </c>
+      <c r="AB49">
+        <v>4.25</v>
+      </c>
+      <c r="AC49">
+        <v>1.54</v>
+      </c>
+      <c r="AD49">
+        <v>2.29</v>
+      </c>
+      <c r="AE49">
+        <v>1.66</v>
+      </c>
+      <c r="AF49">
+        <v>1.2</v>
+      </c>
+      <c r="AG49">
+        <v>4.14</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.18</v>
+      </c>
+      <c r="AK49">
         <v>1.51</v>
-      </c>
-      <c r="O49">
-        <v>4.5</v>
-      </c>
-      <c r="P49">
-        <v>5.2</v>
-      </c>
-      <c r="Q49">
-        <v>1.96</v>
-      </c>
-      <c r="R49">
-        <v>2.35</v>
-      </c>
-      <c r="S49">
-        <v>1.27</v>
-      </c>
-      <c r="T49">
-        <v>3.65</v>
-      </c>
-      <c r="U49">
-        <v>2.25</v>
-      </c>
-      <c r="V49">
-        <v>1.65</v>
-      </c>
-      <c r="W49">
-        <v>1.15</v>
-      </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>1.12</v>
-      </c>
-      <c r="Z49">
-        <v>5.25</v>
-      </c>
-      <c r="AA49">
-        <v>1.5</v>
-      </c>
-      <c r="AB49">
-        <v>2.38</v>
-      </c>
-      <c r="AC49">
-        <v>2.42</v>
-      </c>
-      <c r="AD49">
-        <v>1.61</v>
-      </c>
-      <c r="AE49">
-        <v>1.21</v>
-      </c>
-      <c r="AF49">
-        <v>1.65</v>
-      </c>
-      <c r="AG49">
-        <v>2.19</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.16</v>
-      </c>
-      <c r="AK49">
-        <v>2.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="O50">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="P50">
-        <v>2.45</v>
+        <v>12</v>
       </c>
       <c r="Q50">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="R50">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="S50">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="U50">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="V50">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="W50">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z50">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AB50">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="AC50">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AD50">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="AE50">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AF50">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>4.14</v>
+        <v>1.85</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK50">
-        <v>1.51</v>
+        <v>4.65</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         <v>2.74</v>
       </c>
       <c r="AA52">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB52">
         <v>1.63</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="P5">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="Q5">
         <v>1.62</v>
@@ -1145,13 +1145,13 @@
         <v>3.58</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>1.73</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1178,7 +1178,7 @@
         <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG5">
         <v>1.85</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1344,7 +1344,7 @@
         <v>1.59</v>
       </c>
       <c r="AG6">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P8">
         <v>1.39</v>
@@ -1625,10 +1625,10 @@
         <v>7.8</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T8">
         <v>2.47</v>
@@ -1655,7 +1655,7 @@
         <v>2.2</v>
       </c>
       <c r="AB8">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
         <v>3.96</v>
@@ -1818,7 +1818,7 @@
         <v>2.52</v>
       </c>
       <c r="AB9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC9">
         <v>4.95</v>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O10">
         <v>4.54</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O11">
         <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
         <v>3.5</v>
@@ -2123,7 +2123,7 @@
         <v>2.51</v>
       </c>
       <c r="U11">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="V11">
         <v>1.3</v>
@@ -2135,16 +2135,16 @@
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z11">
         <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
         <v>3.98</v>
@@ -2159,7 +2159,7 @@
         <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>4.2</v>
       </c>
       <c r="P12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2754,22 +2754,22 @@
         </is>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q15">
         <v>6</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
         <v>2.62</v>
@@ -2778,7 +2778,7 @@
         <v>3</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2808,7 +2808,7 @@
         <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG15">
         <v>1.6</v>
@@ -3098,16 +3098,16 @@
         <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3137,7 +3137,7 @@
         <v>1.39</v>
       </c>
       <c r="AG17">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3258,19 +3258,19 @@
         <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q19">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
         <v>2.12</v>
@@ -3442,16 +3442,16 @@
         <v>1.37</v>
       </c>
       <c r="Z19">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA19">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
         <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="AD19">
         <v>1.23</v>
@@ -3572,7 +3572,7 @@
         <v>2.75</v>
       </c>
       <c r="O20">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
         <v>2.45</v>
@@ -3741,55 +3741,55 @@
         <v>3.05</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.72</v>
+        <v>1.69</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="Q22">
-        <v>3.34</v>
+        <v>2.15</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="S22">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="U22">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA22">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AB22">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC22">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="AD22">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG22">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G23">
@@ -4061,61 +4061,61 @@
         <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P23">
         <v>2.85</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="O24">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="P24">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="Q25">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="R25">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>2.74</v>
+        <v>3.26</v>
       </c>
       <c r="U25">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AA25">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AB25">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AC25">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="AD25">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AG25">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.49</v>
+        <v>2.79</v>
       </c>
       <c r="O26">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>2.18</v>
       </c>
       <c r="Q26">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.78</v>
+        <v>2.96</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AB26">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
+        <v>2.83</v>
+      </c>
+      <c r="AD26">
+        <v>1.33</v>
+      </c>
+      <c r="AE26">
+        <v>1.09</v>
+      </c>
+      <c r="AF26">
+        <v>1.6</v>
+      </c>
+      <c r="AG26">
         <v>2.16</v>
       </c>
-      <c r="AD26">
-        <v>1.59</v>
-      </c>
-      <c r="AE26">
-        <v>1.24</v>
-      </c>
-      <c r="AF26">
-        <v>1.57</v>
-      </c>
-      <c r="AG26">
-        <v>2.25</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AK26">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.95</v>
+        <v>4.16</v>
       </c>
       <c r="AA27">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC27">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="AD27">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
+        <v>1.29</v>
+      </c>
+      <c r="AK27">
         <v>1.27</v>
-      </c>
-      <c r="AK27">
-        <v>1.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P28">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="Q28">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U28">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
         <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="AC28">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,37 +5036,37 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="Q29">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="R29">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T29">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U29">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="V29">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.19</v>
@@ -5075,25 +5075,25 @@
         <v>3.74</v>
       </c>
       <c r="AA29">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG29">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
+        <v>1.27</v>
+      </c>
+      <c r="AK29">
         <v>1.52</v>
-      </c>
-      <c r="AK29">
-        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="Q30">
         <v>3.12</v>
@@ -5223,7 +5223,7 @@
         <v>2.82</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5235,16 +5235,16 @@
         <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
         <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AD30">
         <v>1.25</v>
@@ -5401,7 +5401,7 @@
         <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
         <v>2.33</v>
@@ -5567,7 +5567,7 @@
         <v>1.77</v>
       </c>
       <c r="AB32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>2.91</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P33">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="Q33">
-        <v>3.49</v>
+        <v>3.26</v>
       </c>
       <c r="R33">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U33">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AA33">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.68</v>
+        <v>1.88</v>
       </c>
       <c r="O34">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>2.43</v>
+        <v>4</v>
       </c>
       <c r="Q34">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.88</v>
+        <v>2.57</v>
       </c>
       <c r="O35">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.37</v>
+      </c>
+      <c r="O36">
+        <v>3.4</v>
+      </c>
+      <c r="P36">
         <v>2.57</v>
       </c>
-      <c r="O36">
-        <v>3.25</v>
-      </c>
-      <c r="P36">
-        <v>2.49</v>
-      </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.46</v>
+        <v>1.57</v>
       </c>
       <c r="O37">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="P37">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="Q37">
-        <v>4.27</v>
+        <v>1.95</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="T37">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="V37">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>3.04</v>
+        <v>5.65</v>
       </c>
       <c r="AA37">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="AB37">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="AC37">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.28</v>
+        <v>2.46</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,58 +6503,58 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.37</v>
+        <v>1.51</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P38">
-        <v>2.57</v>
+        <v>4.55</v>
       </c>
       <c r="Q38">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>5.13</v>
+        <v>6.08</v>
       </c>
       <c r="AA38">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AB38">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="AC38">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="AD38">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AE38">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AF38">
         <v>1.44</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="O39">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Q39">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="R39">
+        <v>2.5</v>
+      </c>
+      <c r="S39">
+        <v>1.23</v>
+      </c>
+      <c r="T39">
+        <v>3.48</v>
+      </c>
+      <c r="U39">
+        <v>2.15</v>
+      </c>
+      <c r="V39">
+        <v>1.62</v>
+      </c>
+      <c r="W39">
+        <v>1.13</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
+        <v>4.9</v>
+      </c>
+      <c r="AA39">
+        <v>1.5</v>
+      </c>
+      <c r="AB39">
+        <v>2.38</v>
+      </c>
+      <c r="AC39">
         <v>2.31</v>
       </c>
-      <c r="S39">
-        <v>1.28</v>
-      </c>
-      <c r="T39">
-        <v>3.24</v>
-      </c>
-      <c r="U39">
-        <v>2.38</v>
-      </c>
-      <c r="V39">
-        <v>1.5</v>
-      </c>
-      <c r="W39">
-        <v>1.09</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.16</v>
-      </c>
-      <c r="Z39">
-        <v>4.1</v>
-      </c>
-      <c r="AA39">
-        <v>1.64</v>
-      </c>
-      <c r="AB39">
-        <v>2.17</v>
-      </c>
-      <c r="AC39">
-        <v>2.49</v>
-      </c>
       <c r="AD39">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AG39">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>5.5</v>
+        <v>3.13</v>
       </c>
       <c r="Q40">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="R40">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U40">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>5.65</v>
+        <v>3.85</v>
       </c>
       <c r="AA40">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AB40">
-        <v>2.52</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>2.11</v>
+        <v>3.01</v>
       </c>
       <c r="AD40">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.51</v>
+        <v>3.46</v>
       </c>
       <c r="O41">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>4.55</v>
+        <v>1.91</v>
       </c>
       <c r="Q41">
-        <v>1.85</v>
+        <v>4.27</v>
       </c>
       <c r="R41">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>6.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA41">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="AB41">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC41">
-        <v>1.97</v>
+        <v>3.34</v>
       </c>
       <c r="AD41">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="AE41">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>2.38</v>
+        <v>1.28</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="P42">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="Q42">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S42">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="U42">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
+        <v>1.16</v>
+      </c>
+      <c r="Z42">
+        <v>4.1</v>
+      </c>
+      <c r="AA42">
+        <v>1.64</v>
+      </c>
+      <c r="AB42">
+        <v>2.17</v>
+      </c>
+      <c r="AC42">
+        <v>2.49</v>
+      </c>
+      <c r="AD42">
+        <v>1.42</v>
+      </c>
+      <c r="AE42">
         <v>1.14</v>
       </c>
-      <c r="Z42">
-        <v>4.9</v>
-      </c>
-      <c r="AA42">
-        <v>1.5</v>
-      </c>
-      <c r="AB42">
-        <v>2.38</v>
-      </c>
-      <c r="AC42">
-        <v>2.31</v>
-      </c>
-      <c r="AD42">
-        <v>1.61</v>
-      </c>
-      <c r="AE42">
-        <v>1.23</v>
-      </c>
       <c r="AF42">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>3.49</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB43">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="O49">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="P49">
-        <v>2.45</v>
+        <v>12</v>
       </c>
       <c r="Q49">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="R49">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="S49">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="T49">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="U49">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="V49">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="W49">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z49">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA49">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="AC49">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AD49">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="AE49">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AF49">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AG49">
-        <v>4.14</v>
+        <v>1.85</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>1.51</v>
+        <v>4.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.4</v>
+      </c>
+      <c r="O50">
+        <v>4.2</v>
+      </c>
+      <c r="P50">
+        <v>2.45</v>
+      </c>
+      <c r="Q50">
+        <v>2.64</v>
+      </c>
+      <c r="R50">
+        <v>2.62</v>
+      </c>
+      <c r="S50">
+        <v>1.15</v>
+      </c>
+      <c r="T50">
+        <v>5.4</v>
+      </c>
+      <c r="U50">
+        <v>1.71</v>
+      </c>
+      <c r="V50">
+        <v>2.15</v>
+      </c>
+      <c r="W50">
+        <v>1.33</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
+        <v>1.01</v>
+      </c>
+      <c r="Z50">
+        <v>9.5</v>
+      </c>
+      <c r="AA50">
+        <v>1.22</v>
+      </c>
+      <c r="AB50">
+        <v>4.25</v>
+      </c>
+      <c r="AC50">
+        <v>1.54</v>
+      </c>
+      <c r="AD50">
+        <v>2.29</v>
+      </c>
+      <c r="AE50">
+        <v>1.66</v>
+      </c>
+      <c r="AF50">
+        <v>1.2</v>
+      </c>
+      <c r="AG50">
+        <v>4.14</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.18</v>
       </c>
-      <c r="O50">
-        <v>6.7</v>
-      </c>
-      <c r="P50">
-        <v>12</v>
-      </c>
-      <c r="Q50">
-        <v>1.4</v>
-      </c>
-      <c r="R50">
-        <v>3.15</v>
-      </c>
-      <c r="S50">
-        <v>1.23</v>
-      </c>
-      <c r="T50">
-        <v>5.2</v>
-      </c>
-      <c r="U50">
-        <v>1.91</v>
-      </c>
-      <c r="V50">
-        <v>1.86</v>
-      </c>
-      <c r="W50">
-        <v>1.25</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.05</v>
-      </c>
-      <c r="Z50">
-        <v>6.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.3</v>
-      </c>
-      <c r="AB50">
-        <v>3.08</v>
-      </c>
-      <c r="AC50">
-        <v>1.79</v>
-      </c>
-      <c r="AD50">
-        <v>2.01</v>
-      </c>
-      <c r="AE50">
-        <v>1.4</v>
-      </c>
-      <c r="AF50">
-        <v>1.83</v>
-      </c>
-      <c r="AG50">
-        <v>1.85</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.13</v>
-      </c>
       <c r="AK50">
-        <v>4.65</v>
+        <v>1.51</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8625,61 +8625,61 @@
         <v>2.85</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P51">
         <v>2.4</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2446,7 +2446,7 @@
         <v>1.17</v>
       </c>
       <c r="T13">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2467,7 +2467,7 @@
         <v>5.95</v>
       </c>
       <c r="AA13">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB13">
         <v>2.8</v>
@@ -2597,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q14">
         <v>2.14</v>
@@ -2606,7 +2606,7 @@
         <v>2.41</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
         <v>3.64</v>
@@ -2633,7 +2633,7 @@
         <v>1.61</v>
       </c>
       <c r="AB14">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AC14">
         <v>2.46</v>
@@ -2648,7 +2648,7 @@
         <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>1.75</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
         <v>3.9</v>
@@ -2953,7 +2953,7 @@
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="AA16">
         <v>1.59</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="P23">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>2.86</v>
+        <v>1.85</v>
       </c>
       <c r="R23">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>2.74</v>
+        <v>3.78</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA23">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="AB23">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="AC23">
-        <v>3.34</v>
+        <v>2.16</v>
       </c>
       <c r="AD23">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AF23">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="O24">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>2.43</v>
       </c>
       <c r="Q24">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
-        <v>3.78</v>
+        <v>3.26</v>
       </c>
       <c r="U24">
+        <v>2.45</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.11</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.17</v>
+      </c>
+      <c r="Z24">
+        <v>3.95</v>
+      </c>
+      <c r="AA24">
+        <v>1.66</v>
+      </c>
+      <c r="AB24">
         <v>2.15</v>
       </c>
-      <c r="V24">
-        <v>1.67</v>
-      </c>
-      <c r="W24">
-        <v>1.17</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.12</v>
-      </c>
-      <c r="Z24">
-        <v>4.8</v>
-      </c>
-      <c r="AA24">
-        <v>1.48</v>
-      </c>
-      <c r="AB24">
-        <v>2.5</v>
-      </c>
       <c r="AC24">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AD24">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="AE24">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="R25">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U25">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>3.95</v>
+        <v>4.16</v>
       </c>
       <c r="AA25">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="AD25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
+        <v>1.29</v>
+      </c>
+      <c r="AK25">
         <v>1.27</v>
-      </c>
-      <c r="AK25">
-        <v>1.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="R26">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z26">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA26">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AC26">
-        <v>2.83</v>
+        <v>3.48</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG26">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q27">
-        <v>3.88</v>
+        <v>2.87</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="V27">
         <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z27">
-        <v>4.16</v>
+        <v>3.74</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG27">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O28">
         <v>3.15</v>
       </c>
       <c r="P28">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="Q28">
-        <v>3.34</v>
+        <v>2.86</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="U28">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V28">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB28">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P29">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="Q29">
-        <v>2.87</v>
+        <v>3.34</v>
       </c>
       <c r="R29">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA29">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC29">
-        <v>2.69</v>
+        <v>3.26</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
-        <v>2.73</v>
+        <v>4.5</v>
       </c>
       <c r="Q30">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="U30">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="AC30">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG30">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.57</v>
+        <v>2.79</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="R31">
-        <v>2.54</v>
+        <v>2.11</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA31">
+        <v>1.77</v>
+      </c>
+      <c r="AB31">
+        <v>1.92</v>
+      </c>
+      <c r="AC31">
+        <v>2.83</v>
+      </c>
+      <c r="AD31">
+        <v>1.33</v>
+      </c>
+      <c r="AE31">
+        <v>1.09</v>
+      </c>
+      <c r="AF31">
         <v>1.6</v>
       </c>
-      <c r="AB31">
-        <v>2.33</v>
-      </c>
-      <c r="AC31">
-        <v>2.38</v>
-      </c>
-      <c r="AD31">
-        <v>1.46</v>
-      </c>
-      <c r="AE31">
-        <v>1.16</v>
-      </c>
-      <c r="AF31">
-        <v>1.64</v>
-      </c>
       <c r="AG31">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="AK31">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.68</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
+        <v>4</v>
+      </c>
+      <c r="Q33">
         <v>2.43</v>
       </c>
-      <c r="Q33">
-        <v>3.26</v>
-      </c>
       <c r="R33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U33">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>1.21</v>
+      </c>
+      <c r="Z33">
+        <v>3.58</v>
+      </c>
+      <c r="AA33">
+        <v>1.9</v>
+      </c>
+      <c r="AB33">
+        <v>1.9</v>
+      </c>
+      <c r="AC33">
+        <v>2.83</v>
+      </c>
+      <c r="AD33">
+        <v>1.33</v>
+      </c>
+      <c r="AE33">
         <v>1.09</v>
       </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
-      <c r="Y33">
-        <v>1.18</v>
-      </c>
-      <c r="Z33">
-        <v>3.85</v>
-      </c>
-      <c r="AA33">
-        <v>1.72</v>
-      </c>
-      <c r="AB33">
-        <v>2.05</v>
-      </c>
-      <c r="AC33">
-        <v>2.66</v>
-      </c>
-      <c r="AD33">
-        <v>1.37</v>
-      </c>
-      <c r="AE33">
-        <v>1.11</v>
-      </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>2.49</v>
+        <v>5.5</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,58 +6177,58 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.37</v>
+        <v>1.51</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P36">
-        <v>2.57</v>
+        <v>4.55</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W36">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>5.13</v>
+        <v>6.08</v>
       </c>
       <c r="AA36">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="AC36">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="AD36">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AE36">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AF36">
         <v>1.44</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="O37">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>5.5</v>
+        <v>1.72</v>
       </c>
       <c r="Q37">
-        <v>1.95</v>
+        <v>4.33</v>
       </c>
       <c r="R37">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="U37">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>5.65</v>
+        <v>4.9</v>
       </c>
       <c r="AA37">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AD37">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>2.46</v>
+        <v>1.21</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="O38">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>4.55</v>
+        <v>3.13</v>
       </c>
       <c r="Q38">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V38">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>6.08</v>
+        <v>3.85</v>
       </c>
       <c r="AA38">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="AC38">
-        <v>1.97</v>
+        <v>3.01</v>
       </c>
       <c r="AD38">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AE38">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P39">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Q39">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S39">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB39">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AC39">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="AD39">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>3.13</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="AA40">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="AD40">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.46</v>
+        <v>2.94</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P41">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="Q41">
-        <v>4.27</v>
+        <v>3.62</v>
       </c>
       <c r="R41">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V41">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AB41">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AD41">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AG41">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="Q42">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R42">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
+        <v>1.31</v>
+      </c>
+      <c r="T42">
+        <v>3.08</v>
+      </c>
+      <c r="U42">
+        <v>2.48</v>
+      </c>
+      <c r="V42">
+        <v>1.46</v>
+      </c>
+      <c r="W42">
+        <v>1.07</v>
+      </c>
+      <c r="X42">
+        <v>1.02</v>
+      </c>
+      <c r="Y42">
+        <v>1.2</v>
+      </c>
+      <c r="Z42">
+        <v>3.7</v>
+      </c>
+      <c r="AA42">
+        <v>1.79</v>
+      </c>
+      <c r="AB42">
+        <v>1.95</v>
+      </c>
+      <c r="AC42">
+        <v>2.88</v>
+      </c>
+      <c r="AD42">
+        <v>1.32</v>
+      </c>
+      <c r="AE42">
+        <v>1.08</v>
+      </c>
+      <c r="AF42">
+        <v>1.61</v>
+      </c>
+      <c r="AG42">
+        <v>2.18</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.28</v>
       </c>
-      <c r="T42">
-        <v>3.24</v>
-      </c>
-      <c r="U42">
-        <v>2.38</v>
-      </c>
-      <c r="V42">
-        <v>1.5</v>
-      </c>
-      <c r="W42">
-        <v>1.09</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.16</v>
-      </c>
-      <c r="Z42">
-        <v>4.1</v>
-      </c>
-      <c r="AA42">
-        <v>1.64</v>
-      </c>
-      <c r="AB42">
-        <v>2.17</v>
-      </c>
-      <c r="AC42">
-        <v>2.49</v>
-      </c>
-      <c r="AD42">
-        <v>1.42</v>
-      </c>
-      <c r="AE42">
-        <v>1.14</v>
-      </c>
-      <c r="AF42">
-        <v>1.56</v>
-      </c>
-      <c r="AG42">
-        <v>2.28</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.24</v>
-      </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.62</v>
+        <v>3.46</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P43">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="Q43">
-        <v>3.49</v>
+        <v>4.27</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="S43">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U43">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="AA43">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD43">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG43">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
+        <v>1.29</v>
+      </c>
+      <c r="AK43">
         <v>1.28</v>
-      </c>
-      <c r="AK43">
-        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P44">
-        <v>4.34</v>
+        <v>4.54</v>
       </c>
       <c r="Q44">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="R44">
         <v>2.45</v>
@@ -7499,7 +7499,7 @@
         <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="U44">
         <v>2.25</v>
@@ -7508,37 +7508,37 @@
         <v>1.57</v>
       </c>
       <c r="W44">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z44">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA44">
+        <v>1.52</v>
+      </c>
+      <c r="AB44">
+        <v>2.33</v>
+      </c>
+      <c r="AC44">
+        <v>2.4</v>
+      </c>
+      <c r="AD44">
         <v>1.56</v>
-      </c>
-      <c r="AB44">
-        <v>2.29</v>
-      </c>
-      <c r="AC44">
-        <v>2.42</v>
-      </c>
-      <c r="AD44">
-        <v>1.64</v>
       </c>
       <c r="AE44">
         <v>1.21</v>
       </c>
       <c r="AF44">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.18</v>
       </c>
       <c r="AK44">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="Q45">
         <v>2.05</v>
@@ -7686,7 +7686,7 @@
         <v>1.46</v>
       </c>
       <c r="AB45">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC45">
         <v>2.1</v>
@@ -7698,10 +7698,10 @@
         <v>1.24</v>
       </c>
       <c r="AF45">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.8</v>
+        <v>1.05</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>29</v>
       </c>
       <c r="Q46">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="R46">
-        <v>2.52</v>
+        <v>3.62</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T46">
-        <v>3.84</v>
+        <v>5.25</v>
       </c>
       <c r="U46">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z46">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AB46">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="AC46">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AD46">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AE46">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AF46">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AG46">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AK46">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="O47">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="P47">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="Q47">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="R47">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="S47">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="U47">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="V47">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="W47">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z47">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA47">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AD47">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AE47">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AF47">
-        <v>2.52</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>9.699999999999999</v>
+        <v>2.69</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.4</v>
+      </c>
+      <c r="O48">
+        <v>4.2</v>
+      </c>
+      <c r="P48">
+        <v>2.45</v>
+      </c>
+      <c r="Q48">
+        <v>2.64</v>
+      </c>
+      <c r="R48">
+        <v>2.62</v>
+      </c>
+      <c r="S48">
+        <v>1.14</v>
+      </c>
+      <c r="T48">
+        <v>5.4</v>
+      </c>
+      <c r="U48">
+        <v>1.71</v>
+      </c>
+      <c r="V48">
+        <v>2.21</v>
+      </c>
+      <c r="W48">
+        <v>1.33</v>
+      </c>
+      <c r="X48">
+        <v>1.01</v>
+      </c>
+      <c r="Y48">
+        <v>1.01</v>
+      </c>
+      <c r="Z48">
+        <v>9.5</v>
+      </c>
+      <c r="AA48">
+        <v>1.2</v>
+      </c>
+      <c r="AB48">
+        <v>4.4</v>
+      </c>
+      <c r="AC48">
+        <v>1.53</v>
+      </c>
+      <c r="AD48">
+        <v>2.29</v>
+      </c>
+      <c r="AE48">
+        <v>1.7</v>
+      </c>
+      <c r="AF48">
+        <v>1.2</v>
+      </c>
+      <c r="AG48">
+        <v>4.14</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.18</v>
+      </c>
+      <c r="AK48">
         <v>1.51</v>
-      </c>
-      <c r="O48">
-        <v>4.5</v>
-      </c>
-      <c r="P48">
-        <v>5.2</v>
-      </c>
-      <c r="Q48">
-        <v>1.96</v>
-      </c>
-      <c r="R48">
-        <v>2.35</v>
-      </c>
-      <c r="S48">
-        <v>1.27</v>
-      </c>
-      <c r="T48">
-        <v>3.65</v>
-      </c>
-      <c r="U48">
-        <v>2.25</v>
-      </c>
-      <c r="V48">
-        <v>1.65</v>
-      </c>
-      <c r="W48">
-        <v>1.15</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.12</v>
-      </c>
-      <c r="Z48">
-        <v>5.25</v>
-      </c>
-      <c r="AA48">
-        <v>1.5</v>
-      </c>
-      <c r="AB48">
-        <v>2.38</v>
-      </c>
-      <c r="AC48">
-        <v>2.42</v>
-      </c>
-      <c r="AD48">
-        <v>1.61</v>
-      </c>
-      <c r="AE48">
-        <v>1.21</v>
-      </c>
-      <c r="AF48">
-        <v>1.65</v>
-      </c>
-      <c r="AG48">
-        <v>2.19</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.16</v>
-      </c>
-      <c r="AK48">
-        <v>2.57</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,10 +8299,10 @@
         <v>1.18</v>
       </c>
       <c r="O49">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="P49">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Q49">
         <v>1.4</v>
@@ -8311,16 +8311,16 @@
         <v>3.15</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T49">
         <v>5.2</v>
       </c>
       <c r="U49">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V49">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="W49">
         <v>1.25</v>
@@ -8329,31 +8329,31 @@
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA49">
         <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AC49">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD49">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AE49">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF49">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK49">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
+        <v>3.1</v>
+      </c>
+      <c r="O50">
+        <v>3.8</v>
+      </c>
+      <c r="P50">
+        <v>2.1</v>
+      </c>
+      <c r="Q50">
+        <v>3.3</v>
+      </c>
+      <c r="R50">
         <v>2.4</v>
       </c>
-      <c r="O50">
-        <v>4.2</v>
-      </c>
-      <c r="P50">
-        <v>2.45</v>
-      </c>
-      <c r="Q50">
-        <v>2.64</v>
-      </c>
-      <c r="R50">
+      <c r="S50">
+        <v>1.25</v>
+      </c>
+      <c r="T50">
+        <v>3.84</v>
+      </c>
+      <c r="U50">
+        <v>2.2</v>
+      </c>
+      <c r="V50">
+        <v>1.64</v>
+      </c>
+      <c r="W50">
+        <v>1.13</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.13</v>
+      </c>
+      <c r="Z50">
+        <v>4.9</v>
+      </c>
+      <c r="AA50">
+        <v>1.48</v>
+      </c>
+      <c r="AB50">
+        <v>2.43</v>
+      </c>
+      <c r="AC50">
+        <v>2.35</v>
+      </c>
+      <c r="AD50">
+        <v>1.63</v>
+      </c>
+      <c r="AE50">
+        <v>1.22</v>
+      </c>
+      <c r="AF50">
+        <v>1.44</v>
+      </c>
+      <c r="AG50">
         <v>2.62</v>
       </c>
-      <c r="S50">
-        <v>1.15</v>
-      </c>
-      <c r="T50">
-        <v>5.4</v>
-      </c>
-      <c r="U50">
-        <v>1.71</v>
-      </c>
-      <c r="V50">
-        <v>2.15</v>
-      </c>
-      <c r="W50">
-        <v>1.33</v>
-      </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
-      <c r="Y50">
-        <v>1.01</v>
-      </c>
-      <c r="Z50">
-        <v>9.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.22</v>
-      </c>
-      <c r="AB50">
-        <v>4.25</v>
-      </c>
-      <c r="AC50">
-        <v>1.54</v>
-      </c>
-      <c r="AD50">
-        <v>2.29</v>
-      </c>
-      <c r="AE50">
-        <v>1.66</v>
-      </c>
-      <c r="AF50">
-        <v>1.2</v>
-      </c>
-      <c r="AG50">
-        <v>4.14</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
+        <v>2.38</v>
+      </c>
+      <c r="V5">
+        <v>1.47</v>
+      </c>
+      <c r="W5">
+        <v>1.12</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.15</v>
+      </c>
+      <c r="Z5">
+        <v>4.3</v>
+      </c>
+      <c r="AA5">
+        <v>1.6</v>
+      </c>
+      <c r="AB5">
+        <v>2.15</v>
+      </c>
+      <c r="AC5">
+        <v>2.43</v>
+      </c>
+      <c r="AD5">
+        <v>1.44</v>
+      </c>
+      <c r="AE5">
+        <v>1.14</v>
+      </c>
+      <c r="AF5">
+        <v>1.59</v>
+      </c>
+      <c r="AG5">
+        <v>2.15</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.2</v>
+      </c>
+      <c r="AK5">
         <v>2</v>
-      </c>
-      <c r="V5">
-        <v>1.73</v>
-      </c>
-      <c r="W5">
-        <v>1.18</v>
-      </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.1</v>
-      </c>
-      <c r="Z5">
-        <v>5.2</v>
-      </c>
-      <c r="AA5">
-        <v>1.4</v>
-      </c>
-      <c r="AB5">
-        <v>2.56</v>
-      </c>
-      <c r="AC5">
-        <v>2.05</v>
-      </c>
-      <c r="AD5">
-        <v>1.66</v>
-      </c>
-      <c r="AE5">
-        <v>1.26</v>
-      </c>
-      <c r="AF5">
-        <v>1.82</v>
-      </c>
-      <c r="AG5">
-        <v>1.85</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.14</v>
-      </c>
-      <c r="AK5">
-        <v>3.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>1.62</v>
       </c>
       <c r="R6">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="T6">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z6">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC6">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AE6">
+        <v>1.26</v>
+      </c>
+      <c r="AF6">
+        <v>1.75</v>
+      </c>
+      <c r="AG6">
+        <v>1.85</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.14</v>
       </c>
-      <c r="AF6">
-        <v>1.59</v>
-      </c>
-      <c r="AG6">
-        <v>2.15</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.2</v>
-      </c>
       <c r="AK6">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>4.8</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="P12">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
         <v>3.67</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q21">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="R21">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T21">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="U21">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>3.42</v>
+        <v>4.45</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>3.08</v>
+        <v>2.43</v>
       </c>
       <c r="AD21">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG21">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="O22">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="P22">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="Q22">
+        <v>1.85</v>
+      </c>
+      <c r="R22">
+        <v>2.5</v>
+      </c>
+      <c r="S22">
+        <v>1.2</v>
+      </c>
+      <c r="T22">
+        <v>3.78</v>
+      </c>
+      <c r="U22">
         <v>2.15</v>
       </c>
-      <c r="R22">
-        <v>2.35</v>
-      </c>
-      <c r="S22">
-        <v>1.26</v>
-      </c>
-      <c r="T22">
-        <v>3.38</v>
-      </c>
-      <c r="U22">
-        <v>2.32</v>
-      </c>
       <c r="V22">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z22">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA22">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AB22">
+        <v>2.5</v>
+      </c>
+      <c r="AC22">
+        <v>2.15</v>
+      </c>
+      <c r="AD22">
+        <v>1.6</v>
+      </c>
+      <c r="AE22">
+        <v>1.24</v>
+      </c>
+      <c r="AF22">
+        <v>1.57</v>
+      </c>
+      <c r="AG22">
         <v>2.25</v>
       </c>
-      <c r="AC22">
-        <v>2.43</v>
-      </c>
-      <c r="AD22">
-        <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.14</v>
-      </c>
-      <c r="AF22">
-        <v>1.61</v>
-      </c>
-      <c r="AG22">
-        <v>2.18</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="Q23">
-        <v>1.85</v>
+        <v>3.12</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="U23">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="V23">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA23">
+        <v>1.93</v>
+      </c>
+      <c r="AB23">
+        <v>1.8</v>
+      </c>
+      <c r="AC23">
+        <v>3.48</v>
+      </c>
+      <c r="AD23">
+        <v>1.25</v>
+      </c>
+      <c r="AE23">
+        <v>1.1</v>
+      </c>
+      <c r="AF23">
+        <v>1.72</v>
+      </c>
+      <c r="AG23">
+        <v>1.98</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.31</v>
+      </c>
+      <c r="AK23">
         <v>1.48</v>
-      </c>
-      <c r="AB23">
-        <v>2.5</v>
-      </c>
-      <c r="AC23">
-        <v>2.16</v>
-      </c>
-      <c r="AD23">
-        <v>1.59</v>
-      </c>
-      <c r="AE23">
-        <v>1.24</v>
-      </c>
-      <c r="AF23">
-        <v>1.57</v>
-      </c>
-      <c r="AG23">
-        <v>2.25</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.2</v>
-      </c>
-      <c r="AK23">
-        <v>2.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="Q24">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="R24">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="S24">
+        <v>1.38</v>
+      </c>
+      <c r="T24">
+        <v>2.74</v>
+      </c>
+      <c r="U24">
+        <v>2.8</v>
+      </c>
+      <c r="V24">
+        <v>1.4</v>
+      </c>
+      <c r="W24">
+        <v>1.04</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.31</v>
+      </c>
+      <c r="Z24">
+        <v>3.3</v>
+      </c>
+      <c r="AA24">
+        <v>2.02</v>
+      </c>
+      <c r="AB24">
+        <v>1.8</v>
+      </c>
+      <c r="AC24">
+        <v>3.34</v>
+      </c>
+      <c r="AD24">
         <v>1.28</v>
       </c>
-      <c r="T24">
-        <v>3.26</v>
-      </c>
-      <c r="U24">
-        <v>2.45</v>
-      </c>
-      <c r="V24">
-        <v>1.44</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1.17</v>
-      </c>
-      <c r="Z24">
-        <v>3.95</v>
-      </c>
-      <c r="AA24">
-        <v>1.66</v>
-      </c>
-      <c r="AB24">
-        <v>2.15</v>
-      </c>
-      <c r="AC24">
-        <v>2.52</v>
-      </c>
-      <c r="AD24">
-        <v>1.41</v>
-      </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="AG24">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="Q25">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
       <c r="AD25">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE25">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.29</v>
       </c>
       <c r="AK25">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P26">
-        <v>2.73</v>
+        <v>4.5</v>
       </c>
       <c r="Q26">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="U26">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA26">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB26">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="AC26">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AK26">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
-        <v>2.87</v>
+        <v>3.88</v>
       </c>
       <c r="R27">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
         <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.74</v>
+        <v>4.16</v>
       </c>
       <c r="AA27">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC27">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
+        <v>1.29</v>
+      </c>
+      <c r="AK27">
         <v>1.27</v>
-      </c>
-      <c r="AK27">
-        <v>1.52</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O28">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
         <v>2.85</v>
       </c>
       <c r="Q28">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="R28">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="U28">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA28">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>2.69</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AG28">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.72</v>
+        <v>2.07</v>
       </c>
       <c r="O29">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>2.31</v>
+        <v>3.05</v>
       </c>
       <c r="Q29">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U29">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V29">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.57</v>
+        <v>2.79</v>
       </c>
       <c r="O30">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q30">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="R30">
-        <v>2.54</v>
+        <v>2.11</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V30">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA30">
+        <v>1.77</v>
+      </c>
+      <c r="AB30">
+        <v>1.92</v>
+      </c>
+      <c r="AC30">
+        <v>2.83</v>
+      </c>
+      <c r="AD30">
+        <v>1.33</v>
+      </c>
+      <c r="AE30">
+        <v>1.09</v>
+      </c>
+      <c r="AF30">
         <v>1.6</v>
       </c>
-      <c r="AB30">
-        <v>2.33</v>
-      </c>
-      <c r="AC30">
-        <v>2.38</v>
-      </c>
-      <c r="AD30">
-        <v>1.46</v>
-      </c>
-      <c r="AE30">
-        <v>1.16</v>
-      </c>
-      <c r="AF30">
-        <v>1.64</v>
-      </c>
       <c r="AG30">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="AK30">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="Q31">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>2.96</v>
+        <v>3.26</v>
       </c>
       <c r="U31">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="AA31">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG31">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5564,7 +5564,7 @@
         <v>3.82</v>
       </c>
       <c r="AA32">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB32">
         <v>2.1</v>
@@ -5694,7 +5694,7 @@
         <v>3.35</v>
       </c>
       <c r="P33">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="Q33">
         <v>2.43</v>
@@ -5727,10 +5727,10 @@
         <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>2.83</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>5.51</v>
       </c>
       <c r="AA35">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AC35">
         <v>2.19</v>
@@ -6216,7 +6216,7 @@
         <v>6.08</v>
       </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
         <v>2.84</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -6536,31 +6536,31 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z38">
-        <v>3.85</v>
+        <v>4.34</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>3.01</v>
+        <v>2.72</v>
       </c>
       <c r="AD38">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.57</v>
+        <v>2.63</v>
       </c>
       <c r="O39">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R39">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="U39">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V39">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="AD39">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.44</v>
+        <v>3.46</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="Q40">
-        <v>3.14</v>
+        <v>4.27</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W40">
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
+        <v>1.29</v>
+      </c>
+      <c r="Z40">
+        <v>3.04</v>
+      </c>
+      <c r="AA40">
+        <v>2.01</v>
+      </c>
+      <c r="AB40">
+        <v>1.75</v>
+      </c>
+      <c r="AC40">
+        <v>3.34</v>
+      </c>
+      <c r="AD40">
         <v>1.24</v>
       </c>
-      <c r="Z40">
-        <v>3.34</v>
-      </c>
-      <c r="AA40">
-        <v>1.85</v>
-      </c>
-      <c r="AB40">
-        <v>1.95</v>
-      </c>
-      <c r="AC40">
-        <v>2.92</v>
-      </c>
-      <c r="AD40">
-        <v>1.31</v>
-      </c>
       <c r="AE40">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="O41">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="P41">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="Q41">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA41">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AC41">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="AD41">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG41">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
+        <v>1.24</v>
+      </c>
+      <c r="AK41">
         <v>1.29</v>
-      </c>
-      <c r="AK41">
-        <v>1.37</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         <v>3.5</v>
       </c>
       <c r="P42">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="Q42">
         <v>3.3</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.46</v>
+        <v>2.94</v>
       </c>
       <c r="O43">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P43">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="Q43">
-        <v>4.27</v>
+        <v>3.62</v>
       </c>
       <c r="R43">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U43">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V43">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AA43">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AB43">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AD43">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8661,7 +8661,7 @@
         <v>2.97</v>
       </c>
       <c r="AA51">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB51">
         <v>1.8</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O10">
         <v>4.54</v>
       </c>
       <c r="P10">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>5.53</v>
       </c>
       <c r="O12">
         <v>4.65</v>
@@ -2274,55 +2274,55 @@
         <v>1.47</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.6</v>
       </c>
       <c r="P16">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q20">
         <v>3.67</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="O21">
+        <v>4.6</v>
+      </c>
+      <c r="P21">
+        <v>5.5</v>
+      </c>
+      <c r="Q21">
+        <v>1.85</v>
+      </c>
+      <c r="R21">
+        <v>2.5</v>
+      </c>
+      <c r="S21">
+        <v>1.2</v>
+      </c>
+      <c r="T21">
         <v>3.8</v>
       </c>
-      <c r="P21">
-        <v>3.7</v>
-      </c>
-      <c r="Q21">
+      <c r="U21">
         <v>2.15</v>
       </c>
-      <c r="R21">
-        <v>2.35</v>
-      </c>
-      <c r="S21">
-        <v>1.26</v>
-      </c>
-      <c r="T21">
-        <v>3.38</v>
-      </c>
-      <c r="U21">
-        <v>2.32</v>
-      </c>
       <c r="V21">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="W21">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z21">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
+        <v>2.38</v>
+      </c>
+      <c r="AC21">
+        <v>2.15</v>
+      </c>
+      <c r="AD21">
+        <v>1.6</v>
+      </c>
+      <c r="AE21">
+        <v>1.24</v>
+      </c>
+      <c r="AF21">
+        <v>1.57</v>
+      </c>
+      <c r="AG21">
         <v>2.25</v>
       </c>
-      <c r="AC21">
-        <v>2.43</v>
-      </c>
-      <c r="AD21">
-        <v>1.44</v>
-      </c>
-      <c r="AE21">
-        <v>1.14</v>
-      </c>
-      <c r="AF21">
-        <v>1.61</v>
-      </c>
-      <c r="AG21">
-        <v>2.18</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="Q22">
-        <v>1.85</v>
+        <v>3.12</v>
       </c>
       <c r="R22">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="U22">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
+        <v>1.93</v>
+      </c>
+      <c r="AB22">
+        <v>1.8</v>
+      </c>
+      <c r="AC22">
+        <v>3.48</v>
+      </c>
+      <c r="AD22">
+        <v>1.25</v>
+      </c>
+      <c r="AE22">
+        <v>1.1</v>
+      </c>
+      <c r="AF22">
+        <v>1.72</v>
+      </c>
+      <c r="AG22">
+        <v>1.98</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.31</v>
+      </c>
+      <c r="AK22">
         <v>1.48</v>
-      </c>
-      <c r="AB22">
-        <v>2.5</v>
-      </c>
-      <c r="AC22">
-        <v>2.15</v>
-      </c>
-      <c r="AD22">
-        <v>1.6</v>
-      </c>
-      <c r="AE22">
-        <v>1.24</v>
-      </c>
-      <c r="AF22">
-        <v>1.57</v>
-      </c>
-      <c r="AG22">
-        <v>2.25</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.2</v>
-      </c>
-      <c r="AK22">
-        <v>2.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="Q23">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="U23">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA23">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB23">
         <v>1.8</v>
       </c>
       <c r="AC23">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD23">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG23">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="Q24">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="U24">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
+        <v>1.06</v>
+      </c>
+      <c r="X24">
         <v>1.04</v>
       </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA24">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>3.26</v>
+        <v>2.69</v>
       </c>
       <c r="AD25">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>2.48</v>
       </c>
       <c r="O26">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q26">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
+        <v>2.45</v>
+      </c>
+      <c r="V26">
+        <v>1.44</v>
+      </c>
+      <c r="W26">
+        <v>1.11</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1.17</v>
+      </c>
+      <c r="Z26">
+        <v>3.95</v>
+      </c>
+      <c r="AA26">
+        <v>1.7</v>
+      </c>
+      <c r="AB26">
+        <v>2.1</v>
+      </c>
+      <c r="AC26">
+        <v>2.52</v>
+      </c>
+      <c r="AD26">
+        <v>1.41</v>
+      </c>
+      <c r="AE26">
+        <v>1.13</v>
+      </c>
+      <c r="AF26">
+        <v>1.55</v>
+      </c>
+      <c r="AG26">
         <v>2.3</v>
       </c>
-      <c r="V26">
-        <v>1.57</v>
-      </c>
-      <c r="W26">
-        <v>1.15</v>
-      </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>1.15</v>
-      </c>
-      <c r="Z26">
-        <v>4.25</v>
-      </c>
-      <c r="AA26">
-        <v>1.6</v>
-      </c>
-      <c r="AB26">
-        <v>2.33</v>
-      </c>
-      <c r="AC26">
-        <v>2.38</v>
-      </c>
-      <c r="AD26">
-        <v>1.46</v>
-      </c>
-      <c r="AE26">
-        <v>1.16</v>
-      </c>
-      <c r="AF26">
-        <v>1.64</v>
-      </c>
-      <c r="AG26">
-        <v>2.13</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>3.88</v>
+        <v>2.15</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S27">
         <v>1.29</v>
@@ -4731,43 +4731,43 @@
         <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>4.16</v>
+        <v>4.45</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC27">
-        <v>2.79</v>
+        <v>2.43</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.27</v>
+        <v>2.14</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>2.87</v>
+        <v>3.88</v>
       </c>
       <c r="R28">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V28">
         <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>3.74</v>
+        <v>4.16</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC28">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
+        <v>1.29</v>
+      </c>
+      <c r="AK28">
         <v>1.27</v>
-      </c>
-      <c r="AK28">
-        <v>1.52</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -5051,19 +5051,19 @@
         <v>2.07</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5075,7 +5075,7 @@
         <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB29">
         <v>1.9</v>
@@ -5090,10 +5090,10 @@
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.79</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P30">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="Q30">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="R30">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="U30">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG30">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
+        <v>3</v>
+      </c>
+      <c r="U31">
+        <v>2.82</v>
+      </c>
+      <c r="V31">
+        <v>1.4</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
+        <v>3.5</v>
+      </c>
+      <c r="AA31">
+        <v>1.85</v>
+      </c>
+      <c r="AB31">
+        <v>1.92</v>
+      </c>
+      <c r="AC31">
         <v>3.26</v>
       </c>
-      <c r="U31">
-        <v>2.45</v>
-      </c>
-      <c r="V31">
-        <v>1.44</v>
-      </c>
-      <c r="W31">
-        <v>1.11</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1.17</v>
-      </c>
-      <c r="Z31">
-        <v>3.95</v>
-      </c>
-      <c r="AA31">
-        <v>1.7</v>
-      </c>
-      <c r="AB31">
-        <v>2.1</v>
-      </c>
-      <c r="AC31">
-        <v>2.52</v>
-      </c>
       <c r="AD31">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.83</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="Q33">
         <v>2.43</v>
@@ -5703,13 +5703,13 @@
         <v>2.18</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U33">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
         <v>1.46</v>
@@ -5727,10 +5727,10 @@
         <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC33">
         <v>2.83</v>
@@ -5745,7 +5745,7 @@
         <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
         <v>2.7</v>
@@ -5893,7 +5893,7 @@
         <v>1.56</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC34">
         <v>2.44</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
-        <v>5.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.65</v>
+        <v>4.07</v>
       </c>
       <c r="O37">
         <v>3.7</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q38">
         <v>2.5</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK38">
         <v>1.67</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>3.14</v>
+        <v>4.27</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S39">
         <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
+        <v>1.29</v>
+      </c>
+      <c r="Z39">
+        <v>3.04</v>
+      </c>
+      <c r="AA39">
+        <v>2.01</v>
+      </c>
+      <c r="AB39">
+        <v>1.75</v>
+      </c>
+      <c r="AC39">
+        <v>3.34</v>
+      </c>
+      <c r="AD39">
         <v>1.24</v>
       </c>
-      <c r="Z39">
-        <v>3.34</v>
-      </c>
-      <c r="AA39">
-        <v>1.85</v>
-      </c>
-      <c r="AB39">
-        <v>1.95</v>
-      </c>
-      <c r="AC39">
-        <v>2.92</v>
-      </c>
-      <c r="AD39">
-        <v>1.31</v>
-      </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="O40">
-        <v>3.35</v>
+        <v>3.78</v>
       </c>
       <c r="P40">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q40">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
+        <v>1.2</v>
+      </c>
+      <c r="Z40">
+        <v>4.4</v>
+      </c>
+      <c r="AA40">
+        <v>1.64</v>
+      </c>
+      <c r="AB40">
+        <v>2.26</v>
+      </c>
+      <c r="AC40">
+        <v>2.64</v>
+      </c>
+      <c r="AD40">
+        <v>1.47</v>
+      </c>
+      <c r="AE40">
+        <v>1.18</v>
+      </c>
+      <c r="AF40">
+        <v>1.56</v>
+      </c>
+      <c r="AG40">
+        <v>2.28</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.24</v>
+      </c>
+      <c r="AK40">
         <v>1.29</v>
-      </c>
-      <c r="Z40">
-        <v>3.04</v>
-      </c>
-      <c r="AA40">
-        <v>2.01</v>
-      </c>
-      <c r="AB40">
-        <v>1.75</v>
-      </c>
-      <c r="AC40">
-        <v>3.34</v>
-      </c>
-      <c r="AD40">
-        <v>1.24</v>
-      </c>
-      <c r="AE40">
-        <v>1.05</v>
-      </c>
-      <c r="AF40">
-        <v>1.8</v>
-      </c>
-      <c r="AG40">
-        <v>1.9</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.29</v>
-      </c>
-      <c r="AK40">
-        <v>1.28</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="O41">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R41">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V41">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA41">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="AD41">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,22 +7155,22 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
         <v>2.38</v>
       </c>
       <c r="Q42">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="R42">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
         <v>3.08</v>
@@ -7191,7 +7191,7 @@
         <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AA42">
         <v>1.79</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
         <v>1.4</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O43">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
         <v>2.29</v>
@@ -8625,7 +8625,7 @@
         <v>2.85</v>
       </c>
       <c r="O51">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
         <v>2.4</v>
@@ -8637,19 +8637,19 @@
         <v>2.06</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U51">
         <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8664,7 +8664,7 @@
         <v>1.96</v>
       </c>
       <c r="AB51">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC51">
         <v>3.42</v>
@@ -8679,7 +8679,7 @@
         <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1197,7 +1197,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="O6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P6">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -1616,10 +1616,10 @@
         <v>7.2</v>
       </c>
       <c r="O8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
         <v>7.8</v>
@@ -1640,7 +1640,7 @@
         <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="O9">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
@@ -1812,10 +1812,10 @@
         <v>1.54</v>
       </c>
       <c r="Z9">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AA9">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AB9">
         <v>1.44</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O10">
-        <v>4.54</v>
+        <v>4.05</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>1.9</v>
@@ -1969,7 +1969,7 @@
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>1.17</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="O11">
         <v>3.1</v>
@@ -2111,16 +2111,16 @@
         <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
         <v>1.92</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="U11">
         <v>2.92</v>
@@ -2268,16 +2268,16 @@
         <v>5.53</v>
       </c>
       <c r="O12">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="P12">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q12">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="R12">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="S12">
         <v>1.18</v>
@@ -2434,7 +2434,7 @@
         <v>5.75</v>
       </c>
       <c r="P13">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -2479,7 +2479,7 @@
         <v>1.75</v>
       </c>
       <c r="AE13">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
         <v>1.67</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O14">
         <v>4</v>
@@ -2757,7 +2757,7 @@
         <v>5.8</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
         <v>1.52</v>
@@ -2793,7 +2793,7 @@
         <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
         <v>1.63</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.38</v>
+        <v>1.75</v>
       </c>
       <c r="R17">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AC17">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AD17">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF17">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AG17">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="R18">
         <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
         <v>3.67</v>
@@ -3584,16 +3584,16 @@
         <v>1.96</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="V20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3602,10 +3602,10 @@
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="AA20">
         <v>1.99</v>
@@ -3735,7 +3735,7 @@
         <v>1.53</v>
       </c>
       <c r="O21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
         <v>5.5</v>
@@ -3904,16 +3904,16 @@
         <v>2.73</v>
       </c>
       <c r="Q22">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
         <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="U22">
         <v>2.82</v>
@@ -4061,10 +4061,10 @@
         <v>2.14</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
         <v>2.86</v>
@@ -4076,7 +4076,7 @@
         <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
         <v>2.8</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="R24">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="U24">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA24">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC24">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q25">
-        <v>2.87</v>
+        <v>3.34</v>
       </c>
       <c r="R25">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
-        <v>2.69</v>
+        <v>3.26</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK25">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="O26">
+        <v>3.3</v>
+      </c>
+      <c r="P26">
+        <v>2.18</v>
+      </c>
+      <c r="Q26">
         <v>3.4</v>
       </c>
-      <c r="P26">
-        <v>2.55</v>
-      </c>
-      <c r="Q26">
-        <v>3.1</v>
-      </c>
       <c r="R26">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="AD26">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AK26">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O27">
         <v>4.2</v>
       </c>
       <c r="P27">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q27">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R27">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
         <v>1.29</v>
@@ -4731,10 +4731,10 @@
         <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V27">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W27">
         <v>1.12</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>3.88</v>
+        <v>2.8</v>
       </c>
       <c r="R28">
         <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="V28">
         <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>4.16</v>
+        <v>3.74</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="O29">
         <v>3.4</v>
       </c>
       <c r="P29">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q29">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="S29">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="AA29">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>2.52</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O30">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="R30">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>3.32</v>
+        <v>2.73</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC30">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AD30">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.72</v>
+        <v>1.61</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>2.31</v>
+        <v>4.5</v>
       </c>
       <c r="Q31">
-        <v>3.34</v>
+        <v>2.05</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AC31">
-        <v>3.26</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG31">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O32">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="P32">
-        <v>5.07</v>
+        <v>4.97</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -5564,13 +5564,13 @@
         <v>3.82</v>
       </c>
       <c r="AA32">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC32">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
         <v>1.4</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P33">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="Q33">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
         <v>1.3</v>
@@ -5709,13 +5709,13 @@
         <v>3.1</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5727,16 +5727,16 @@
         <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB33">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AC33">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
         <v>1.09</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
         <v>2.7</v>
@@ -5887,7 +5887,7 @@
         <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="AA34">
         <v>1.56</v>
@@ -5896,7 +5896,7 @@
         <v>2.26</v>
       </c>
       <c r="AC34">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AD34">
         <v>1.55</v>
@@ -6017,25 +6017,25 @@
         <v>1.5</v>
       </c>
       <c r="O35">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
-        <v>4.92</v>
+        <v>5.5</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
         <v>1.18</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U35">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V35">
         <v>1.67</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="O36">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="P36">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="Q36">
         <v>1.85</v>
@@ -6216,16 +6216,16 @@
         <v>6.08</v>
       </c>
       <c r="AA36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AC36">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD36">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE36">
         <v>1.31</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.07</v>
+        <v>3.76</v>
       </c>
       <c r="O37">
         <v>3.7</v>
       </c>
       <c r="P37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q37">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="R37">
         <v>2.5</v>
@@ -6385,13 +6385,13 @@
         <v>2.38</v>
       </c>
       <c r="AC37">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AD37">
         <v>1.61</v>
       </c>
       <c r="AE37">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
         <v>1.47</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
         <v>3.7</v>
@@ -6542,7 +6542,7 @@
         <v>4.34</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB38">
         <v>2.1</v>
@@ -6557,7 +6557,7 @@
         <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG38">
         <v>2.3</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.6</v>
+        <v>2.41</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P39">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>4.27</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AD39">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="O40">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q40">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V40">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA40">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AB40">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG40">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G41">
@@ -6995,61 +6995,61 @@
         <v>2.63</v>
       </c>
       <c r="O41">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P41">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="Q41">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="U41">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD41">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q42">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="R42">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T42">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="AA42">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AB42">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC42">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD42">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="P43">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="Q43">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U43">
+        <v>2.47</v>
+      </c>
+      <c r="V43">
+        <v>1.52</v>
+      </c>
+      <c r="W43">
+        <v>1.11</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.21</v>
+      </c>
+      <c r="Z43">
+        <v>4.34</v>
+      </c>
+      <c r="AA43">
+        <v>1.66</v>
+      </c>
+      <c r="AB43">
+        <v>2.23</v>
+      </c>
+      <c r="AC43">
         <v>2.66</v>
       </c>
-      <c r="V43">
-        <v>1.47</v>
-      </c>
-      <c r="W43">
-        <v>1.08</v>
-      </c>
-      <c r="X43">
-        <v>1.02</v>
-      </c>
-      <c r="Y43">
-        <v>1.2</v>
-      </c>
-      <c r="Z43">
-        <v>3.4</v>
-      </c>
-      <c r="AA43">
-        <v>1.76</v>
-      </c>
-      <c r="AB43">
-        <v>1.95</v>
-      </c>
-      <c r="AC43">
-        <v>2.78</v>
-      </c>
       <c r="AD43">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
+        <v>1.24</v>
+      </c>
+      <c r="AK43">
         <v>1.29</v>
-      </c>
-      <c r="AK43">
-        <v>1.37</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,7 +7484,7 @@
         <v>1.65</v>
       </c>
       <c r="O44">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P44">
         <v>4.54</v>
@@ -7520,7 +7520,7 @@
         <v>4.65</v>
       </c>
       <c r="AA44">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB44">
         <v>2.33</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
         <v>2.27</v>
@@ -7665,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="V45">
         <v>1.62</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="O46">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="P46">
-        <v>29</v>
+        <v>5.75</v>
       </c>
       <c r="Q46">
+        <v>1.96</v>
+      </c>
+      <c r="R46">
+        <v>2.35</v>
+      </c>
+      <c r="S46">
         <v>1.25</v>
       </c>
-      <c r="R46">
-        <v>3.62</v>
-      </c>
-      <c r="S46">
-        <v>1.13</v>
-      </c>
       <c r="T46">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="V46">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="W46">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA46">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB46">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC46">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AD46">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AE46">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AF46">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AG46">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AK46">
-        <v>9</v>
+        <v>2.69</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O47">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P47">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q47">
-        <v>1.96</v>
+        <v>2.64</v>
       </c>
       <c r="R47">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T47">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="U47">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="V47">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
         <v>1.01</v>
       </c>
-      <c r="Y47">
-        <v>1.1</v>
-      </c>
       <c r="Z47">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AA47">
+        <v>1.2</v>
+      </c>
+      <c r="AB47">
+        <v>4.4</v>
+      </c>
+      <c r="AC47">
         <v>1.5</v>
       </c>
-      <c r="AB47">
-        <v>2.55</v>
-      </c>
-      <c r="AC47">
-        <v>2.12</v>
-      </c>
       <c r="AD47">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AE47">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AF47">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>4.35</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>2.69</v>
+        <v>1.51</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="O48">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="P48">
-        <v>2.45</v>
+        <v>14.5</v>
       </c>
       <c r="Q48">
-        <v>2.64</v>
+        <v>1.5</v>
       </c>
       <c r="R48">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="S48">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="T48">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="U48">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="V48">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="W48">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AB48">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC48">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AD48">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="AE48">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AF48">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG48">
-        <v>4.14</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AK48">
-        <v>1.51</v>
+        <v>5.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,40 +8296,40 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="O49">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P49">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="Q49">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="R49">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="S49">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="T49">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="U49">
+        <v>1.85</v>
+      </c>
+      <c r="V49">
         <v>1.9</v>
       </c>
-      <c r="V49">
-        <v>1.92</v>
-      </c>
       <c r="W49">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z49">
         <v>7.1</v>
@@ -8338,22 +8338,22 @@
         <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AC49">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AD49">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AE49">
         <v>1.41</v>
       </c>
       <c r="AF49">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG49">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK49">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,16 +8462,16 @@
         <v>3.1</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
         <v>2.1</v>
       </c>
       <c r="Q50">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S50">
         <v>1.25</v>
@@ -8486,28 +8486,28 @@
         <v>1.64</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
         <v>4.9</v>
       </c>
       <c r="AA50">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB50">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC50">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AD50">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE50">
         <v>1.22</v>
@@ -8516,7 +8516,7 @@
         <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="O51">
+        <v>3.15</v>
+      </c>
+      <c r="P51">
+        <v>2.27</v>
+      </c>
+      <c r="Q51">
         <v>3.3</v>
       </c>
-      <c r="P51">
-        <v>2.4</v>
-      </c>
-      <c r="Q51">
-        <v>3.61</v>
-      </c>
       <c r="R51">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.41</v>
@@ -8649,7 +8649,7 @@
         <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8664,7 +8664,7 @@
         <v>1.96</v>
       </c>
       <c r="AB51">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
         <v>3.42</v>
@@ -8794,7 +8794,7 @@
         <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R52">
         <v>2</v>
@@ -8824,7 +8824,7 @@
         <v>2.74</v>
       </c>
       <c r="AA52">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
         <v>1.63</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O6">
         <v>5.5</v>
       </c>
       <c r="P6">
-        <v>7.3</v>
+        <v>7.04</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -1360,7 +1360,7 @@
         <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.5</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>1.19</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="R13">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="S13">
+        <v>1.29</v>
+      </c>
+      <c r="T13">
+        <v>3.64</v>
+      </c>
+      <c r="U13">
+        <v>2.27</v>
+      </c>
+      <c r="V13">
+        <v>1.61</v>
+      </c>
+      <c r="W13">
+        <v>1.14</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
         <v>1.17</v>
       </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>1.73</v>
-      </c>
-      <c r="W13">
-        <v>1.17</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.07</v>
-      </c>
       <c r="Z13">
-        <v>5.95</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="AC13">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="AD13">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE13">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.68</v>
+        <v>8.5</v>
       </c>
       <c r="O14">
+        <v>5.75</v>
+      </c>
+      <c r="P14">
+        <v>1.19</v>
+      </c>
+      <c r="Q14">
+        <v>7</v>
+      </c>
+      <c r="R14">
+        <v>2.75</v>
+      </c>
+      <c r="S14">
+        <v>1.17</v>
+      </c>
+      <c r="T14">
         <v>4</v>
       </c>
-      <c r="P14">
-        <v>4.2</v>
-      </c>
-      <c r="Q14">
-        <v>2.14</v>
-      </c>
-      <c r="R14">
-        <v>2.41</v>
-      </c>
-      <c r="S14">
-        <v>1.29</v>
-      </c>
-      <c r="T14">
-        <v>3.64</v>
-      </c>
       <c r="U14">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>4.6</v>
+        <v>5.95</v>
       </c>
       <c r="AA14">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AB14">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="AC14">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="AD14">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="AK14">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AA16">
         <v>1.59</v>
@@ -3119,10 +3119,10 @@
         <v>5.05</v>
       </c>
       <c r="AA17">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC17">
         <v>2.21</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
         <v>2.8</v>
@@ -3282,10 +3282,10 @@
         <v>5.25</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
         <v>2.09</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q25">
-        <v>3.34</v>
+        <v>2.05</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U25">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AC25">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="AD25">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
+        <v>2.15</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.19</v>
+      </c>
+      <c r="AK25">
         <v>2.14</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.29</v>
-      </c>
-      <c r="AK25">
-        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.79</v>
+        <v>2.1</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R26">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="U26">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
+        <v>1.07</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.23</v>
+      </c>
+      <c r="Z26">
+        <v>3.42</v>
+      </c>
+      <c r="AA26">
+        <v>1.9</v>
+      </c>
+      <c r="AB26">
+        <v>1.9</v>
+      </c>
+      <c r="AC26">
+        <v>3.08</v>
+      </c>
+      <c r="AD26">
+        <v>1.28</v>
+      </c>
+      <c r="AE26">
         <v>1.06</v>
       </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
-      <c r="Y26">
-        <v>1.19</v>
-      </c>
-      <c r="Z26">
-        <v>3.74</v>
-      </c>
-      <c r="AA26">
-        <v>1.8</v>
-      </c>
-      <c r="AB26">
-        <v>1.97</v>
-      </c>
-      <c r="AC26">
-        <v>2.83</v>
-      </c>
-      <c r="AD26">
-        <v>1.33</v>
-      </c>
-      <c r="AE26">
-        <v>1.09</v>
-      </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.67</v>
+        <v>2.72</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="P27">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
-        <v>2.05</v>
+        <v>3.34</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="V27">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="AD27">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,37 +4873,37 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q28">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U28">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
         <v>1.19</v>
@@ -4912,41 +4912,41 @@
         <v>3.74</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC28">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD28">
+        <v>1.33</v>
+      </c>
+      <c r="AE28">
+        <v>1.09</v>
+      </c>
+      <c r="AF28">
+        <v>1.6</v>
+      </c>
+      <c r="AG28">
+        <v>2.16</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.52</v>
+      </c>
+      <c r="AK28">
         <v>1.36</v>
-      </c>
-      <c r="AE28">
-        <v>1.11</v>
-      </c>
-      <c r="AF28">
-        <v>1.62</v>
-      </c>
-      <c r="AG28">
-        <v>2.2</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.27</v>
-      </c>
-      <c r="AK28">
-        <v>1.52</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P29">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R29">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="AA29">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF29">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q30">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA30">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC30">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,65 +5362,65 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.61</v>
+        <v>2.48</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
+        <v>2.45</v>
+      </c>
+      <c r="V31">
+        <v>1.44</v>
+      </c>
+      <c r="W31">
+        <v>1.11</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1.17</v>
+      </c>
+      <c r="Z31">
+        <v>3.95</v>
+      </c>
+      <c r="AA31">
+        <v>1.7</v>
+      </c>
+      <c r="AB31">
+        <v>2.1</v>
+      </c>
+      <c r="AC31">
+        <v>2.52</v>
+      </c>
+      <c r="AD31">
+        <v>1.41</v>
+      </c>
+      <c r="AE31">
+        <v>1.13</v>
+      </c>
+      <c r="AF31">
+        <v>1.55</v>
+      </c>
+      <c r="AG31">
         <v>2.3</v>
       </c>
-      <c r="V31">
-        <v>1.57</v>
-      </c>
-      <c r="W31">
-        <v>1.15</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.15</v>
-      </c>
-      <c r="Z31">
-        <v>4.25</v>
-      </c>
-      <c r="AA31">
-        <v>1.6</v>
-      </c>
-      <c r="AB31">
-        <v>2.3</v>
-      </c>
-      <c r="AC31">
-        <v>2.38</v>
-      </c>
-      <c r="AD31">
-        <v>1.46</v>
-      </c>
-      <c r="AE31">
-        <v>1.16</v>
-      </c>
-      <c r="AF31">
-        <v>1.64</v>
-      </c>
-      <c r="AG31">
-        <v>2.13</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O44">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>4.54</v>
+        <v>4.7</v>
       </c>
       <c r="Q44">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="R44">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="U44">
+        <v>2.06</v>
+      </c>
+      <c r="V44">
+        <v>1.62</v>
+      </c>
+      <c r="W44">
+        <v>1.19</v>
+      </c>
+      <c r="X44">
+        <v>1.01</v>
+      </c>
+      <c r="Y44">
+        <v>1.11</v>
+      </c>
+      <c r="Z44">
+        <v>4.95</v>
+      </c>
+      <c r="AA44">
+        <v>1.46</v>
+      </c>
+      <c r="AB44">
+        <v>2.62</v>
+      </c>
+      <c r="AC44">
+        <v>2.1</v>
+      </c>
+      <c r="AD44">
+        <v>1.63</v>
+      </c>
+      <c r="AE44">
+        <v>1.24</v>
+      </c>
+      <c r="AF44">
+        <v>1.53</v>
+      </c>
+      <c r="AG44">
+        <v>2.37</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.14</v>
+      </c>
+      <c r="AK44">
         <v>2.25</v>
-      </c>
-      <c r="V44">
-        <v>1.57</v>
-      </c>
-      <c r="W44">
-        <v>1.13</v>
-      </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>1.12</v>
-      </c>
-      <c r="Z44">
-        <v>4.65</v>
-      </c>
-      <c r="AA44">
-        <v>1.57</v>
-      </c>
-      <c r="AB44">
-        <v>2.33</v>
-      </c>
-      <c r="AC44">
-        <v>2.4</v>
-      </c>
-      <c r="AD44">
-        <v>1.56</v>
-      </c>
-      <c r="AE44">
-        <v>1.21</v>
-      </c>
-      <c r="AF44">
-        <v>1.56</v>
-      </c>
-      <c r="AG44">
-        <v>2.3</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.17</v>
-      </c>
-      <c r="AK44">
-        <v>2.27</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P45">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q45">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U45">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="V45">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W45">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="AA45">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB45">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD45">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE45">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O46">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P46">
+        <v>2.4</v>
+      </c>
+      <c r="Q46">
+        <v>2.64</v>
+      </c>
+      <c r="R46">
+        <v>2.62</v>
+      </c>
+      <c r="S46">
+        <v>1.14</v>
+      </c>
+      <c r="T46">
         <v>5.75</v>
       </c>
-      <c r="Q46">
-        <v>1.96</v>
-      </c>
-      <c r="R46">
-        <v>2.35</v>
-      </c>
-      <c r="S46">
-        <v>1.25</v>
-      </c>
-      <c r="T46">
-        <v>3.8</v>
-      </c>
       <c r="U46">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="V46">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46">
         <v>1.01</v>
       </c>
-      <c r="Y46">
-        <v>1.1</v>
-      </c>
       <c r="Z46">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AA46">
+        <v>1.2</v>
+      </c>
+      <c r="AB46">
+        <v>4.4</v>
+      </c>
+      <c r="AC46">
         <v>1.5</v>
       </c>
-      <c r="AB46">
-        <v>2.55</v>
-      </c>
-      <c r="AC46">
-        <v>2.12</v>
-      </c>
       <c r="AD46">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AE46">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AF46">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AG46">
-        <v>2.25</v>
+        <v>4.35</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>2.69</v>
+        <v>1.51</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.4</v>
+        <v>1.05</v>
       </c>
       <c r="O47">
-        <v>4.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P47">
-        <v>2.4</v>
+        <v>29</v>
       </c>
       <c r="Q47">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="R47">
-        <v>2.62</v>
+        <v>3.62</v>
       </c>
       <c r="S47">
         <v>1.14</v>
       </c>
       <c r="T47">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="W47">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="AA47">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AB47">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AC47">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AD47">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="AE47">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AF47">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AG47">
-        <v>4.35</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK47">
-        <v>1.51</v>
+        <v>9</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="O49">
-        <v>9.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>29</v>
+        <v>2.1</v>
       </c>
       <c r="Q49">
+        <v>3.5</v>
+      </c>
+      <c r="R49">
+        <v>2.58</v>
+      </c>
+      <c r="S49">
         <v>1.25</v>
       </c>
-      <c r="R49">
-        <v>3.62</v>
-      </c>
-      <c r="S49">
-        <v>1.14</v>
-      </c>
       <c r="T49">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="U49">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="W49">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA49">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AB49">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="AD49">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AE49">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG49">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>9</v>
+        <v>1.36</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>2.1</v>
+        <v>4.54</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="R50">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
+        <v>1.13</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.12</v>
+      </c>
+      <c r="Z50">
+        <v>4.65</v>
+      </c>
+      <c r="AA50">
+        <v>1.57</v>
+      </c>
+      <c r="AB50">
+        <v>2.33</v>
+      </c>
+      <c r="AC50">
+        <v>2.4</v>
+      </c>
+      <c r="AD50">
+        <v>1.56</v>
+      </c>
+      <c r="AE50">
+        <v>1.21</v>
+      </c>
+      <c r="AF50">
+        <v>1.56</v>
+      </c>
+      <c r="AG50">
+        <v>2.3</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.17</v>
       </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.11</v>
-      </c>
-      <c r="Z50">
-        <v>4.9</v>
-      </c>
-      <c r="AA50">
-        <v>1.49</v>
-      </c>
-      <c r="AB50">
-        <v>2.4</v>
-      </c>
-      <c r="AC50">
-        <v>2.34</v>
-      </c>
-      <c r="AD50">
-        <v>1.64</v>
-      </c>
-      <c r="AE50">
-        <v>1.22</v>
-      </c>
-      <c r="AF50">
-        <v>1.44</v>
-      </c>
-      <c r="AG50">
-        <v>2.59</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.24</v>
-      </c>
       <c r="AK50">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,43 +3080,43 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
         <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA17">
         <v>1.5</v>
@@ -3125,19 +3125,19 @@
         <v>2.5</v>
       </c>
       <c r="AC17">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AD17">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AE17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,43 +3243,43 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="R18">
         <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA18">
         <v>1.5</v>
@@ -3288,19 +3288,19 @@
         <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AG18">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3584,13 +3584,13 @@
         <v>1.96</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T20">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="U20">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -3605,7 +3605,7 @@
         <v>1.31</v>
       </c>
       <c r="Z20">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AA20">
         <v>1.99</v>
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3919,7 +3919,7 @@
         <v>2.82</v>
       </c>
       <c r="V22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
         <v>1.03</v>
@@ -3934,13 +3934,13 @@
         <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB22">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AD22">
         <v>1.25</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
+        <v>3.5</v>
+      </c>
+      <c r="P23">
         <v>3.4</v>
       </c>
-      <c r="P23">
-        <v>3.1</v>
-      </c>
       <c r="Q23">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
+        <v>3.42</v>
+      </c>
+      <c r="AA23">
+        <v>1.9</v>
+      </c>
+      <c r="AB23">
+        <v>1.9</v>
+      </c>
+      <c r="AC23">
         <v>3.3</v>
-      </c>
-      <c r="AA23">
-        <v>2</v>
-      </c>
-      <c r="AB23">
-        <v>1.8</v>
-      </c>
-      <c r="AC23">
-        <v>3.34</v>
       </c>
       <c r="AD23">
         <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>2.01</v>
+        <v>4.5</v>
       </c>
       <c r="Q24">
-        <v>3.79</v>
+        <v>2.05</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG24">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q25">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA25">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AB25">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
+        <v>2.72</v>
+      </c>
+      <c r="O26">
+        <v>3.15</v>
+      </c>
+      <c r="P26">
+        <v>2.45</v>
+      </c>
+      <c r="Q26">
+        <v>3.34</v>
+      </c>
+      <c r="R26">
         <v>2.1</v>
-      </c>
-      <c r="O26">
-        <v>3.5</v>
-      </c>
-      <c r="P26">
-        <v>3.4</v>
-      </c>
-      <c r="Q26">
-        <v>2.7</v>
-      </c>
-      <c r="R26">
-        <v>2.2</v>
       </c>
       <c r="S26">
         <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="V26">
         <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.72</v>
+        <v>1.62</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q27">
-        <v>3.34</v>
+        <v>2.05</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.82</v>
+        <v>2.27</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA27">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AB27">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AC27">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="AD27">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG27">
+        <v>2.18</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.19</v>
+      </c>
+      <c r="AK27">
         <v>2.14</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.29</v>
-      </c>
-      <c r="AK27">
-        <v>1.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="Q28">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="R28">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T28">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="U28">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC28">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG28">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.61</v>
+        <v>2.79</v>
       </c>
       <c r="O29">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q29">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U29">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V29">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z29">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA29">
+        <v>1.8</v>
+      </c>
+      <c r="AB29">
+        <v>1.97</v>
+      </c>
+      <c r="AC29">
+        <v>2.83</v>
+      </c>
+      <c r="AD29">
+        <v>1.33</v>
+      </c>
+      <c r="AE29">
+        <v>1.09</v>
+      </c>
+      <c r="AF29">
         <v>1.6</v>
       </c>
-      <c r="AB29">
-        <v>2.3</v>
-      </c>
-      <c r="AC29">
-        <v>2.38</v>
-      </c>
-      <c r="AD29">
-        <v>1.46</v>
-      </c>
-      <c r="AE29">
-        <v>1.16</v>
-      </c>
-      <c r="AF29">
-        <v>1.64</v>
-      </c>
       <c r="AG29">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="AK29">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q30">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="AA30">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AG30">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
+        <v>1.36</v>
+      </c>
+      <c r="T31">
+        <v>2.88</v>
+      </c>
+      <c r="U31">
+        <v>2.8</v>
+      </c>
+      <c r="V31">
+        <v>1.36</v>
+      </c>
+      <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.32</v>
+      </c>
+      <c r="Z31">
+        <v>3.24</v>
+      </c>
+      <c r="AA31">
+        <v>2</v>
+      </c>
+      <c r="AB31">
+        <v>1.76</v>
+      </c>
+      <c r="AC31">
+        <v>3.34</v>
+      </c>
+      <c r="AD31">
+        <v>1.24</v>
+      </c>
+      <c r="AE31">
+        <v>1.05</v>
+      </c>
+      <c r="AF31">
+        <v>1.76</v>
+      </c>
+      <c r="AG31">
+        <v>1.96</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.28</v>
       </c>
-      <c r="T31">
-        <v>3.25</v>
-      </c>
-      <c r="U31">
-        <v>2.45</v>
-      </c>
-      <c r="V31">
-        <v>1.44</v>
-      </c>
-      <c r="W31">
-        <v>1.11</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1.17</v>
-      </c>
-      <c r="Z31">
-        <v>3.95</v>
-      </c>
-      <c r="AA31">
-        <v>1.7</v>
-      </c>
-      <c r="AB31">
-        <v>2.1</v>
-      </c>
-      <c r="AC31">
-        <v>2.52</v>
-      </c>
-      <c r="AD31">
-        <v>1.41</v>
-      </c>
-      <c r="AE31">
-        <v>1.13</v>
-      </c>
-      <c r="AF31">
-        <v>1.55</v>
-      </c>
-      <c r="AG31">
-        <v>2.3</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.27</v>
-      </c>
       <c r="AK31">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>1.85</v>
@@ -6017,10 +6017,10 @@
         <v>1.5</v>
       </c>
       <c r="O35">
-        <v>4.4</v>
+        <v>3.89</v>
       </c>
       <c r="P35">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>1.95</v>
@@ -6053,10 +6053,10 @@
         <v>5.51</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB35">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC35">
         <v>2.19</v>
@@ -6835,7 +6835,7 @@
         <v>3.3</v>
       </c>
       <c r="P40">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O41">
         <v>3.42</v>
@@ -7034,7 +7034,7 @@
         <v>1.76</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
         <v>2.78</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P42">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Q42">
         <v>3.9</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O45">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P45">
+        <v>2.4</v>
+      </c>
+      <c r="Q45">
+        <v>2.64</v>
+      </c>
+      <c r="R45">
+        <v>2.62</v>
+      </c>
+      <c r="S45">
+        <v>1.14</v>
+      </c>
+      <c r="T45">
         <v>5.75</v>
       </c>
-      <c r="Q45">
-        <v>1.96</v>
-      </c>
-      <c r="R45">
-        <v>2.35</v>
-      </c>
-      <c r="S45">
-        <v>1.25</v>
-      </c>
-      <c r="T45">
-        <v>3.8</v>
-      </c>
       <c r="U45">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="V45">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="W45">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="Y45">
         <v>1.01</v>
       </c>
-      <c r="Y45">
-        <v>1.1</v>
-      </c>
       <c r="Z45">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AA45">
+        <v>1.2</v>
+      </c>
+      <c r="AB45">
+        <v>4.4</v>
+      </c>
+      <c r="AC45">
         <v>1.5</v>
       </c>
-      <c r="AB45">
-        <v>2.55</v>
-      </c>
-      <c r="AC45">
-        <v>2.12</v>
-      </c>
       <c r="AD45">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AE45">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AF45">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>4.35</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.69</v>
+        <v>1.51</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
+        <v>1.65</v>
+      </c>
+      <c r="O46">
+        <v>4.4</v>
+      </c>
+      <c r="P46">
+        <v>4.54</v>
+      </c>
+      <c r="Q46">
+        <v>2.12</v>
+      </c>
+      <c r="R46">
+        <v>2.45</v>
+      </c>
+      <c r="S46">
+        <v>1.25</v>
+      </c>
+      <c r="T46">
+        <v>3.94</v>
+      </c>
+      <c r="U46">
+        <v>2.25</v>
+      </c>
+      <c r="V46">
+        <v>1.57</v>
+      </c>
+      <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.12</v>
+      </c>
+      <c r="Z46">
+        <v>4.65</v>
+      </c>
+      <c r="AA46">
+        <v>1.57</v>
+      </c>
+      <c r="AB46">
+        <v>2.33</v>
+      </c>
+      <c r="AC46">
         <v>2.4</v>
       </c>
-      <c r="O46">
-        <v>4.33</v>
-      </c>
-      <c r="P46">
-        <v>2.4</v>
-      </c>
-      <c r="Q46">
-        <v>2.64</v>
-      </c>
-      <c r="R46">
-        <v>2.62</v>
-      </c>
-      <c r="S46">
-        <v>1.14</v>
-      </c>
-      <c r="T46">
-        <v>5.75</v>
-      </c>
-      <c r="U46">
-        <v>1.67</v>
-      </c>
-      <c r="V46">
-        <v>2.21</v>
-      </c>
-      <c r="W46">
-        <v>1.36</v>
-      </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
-      <c r="Y46">
-        <v>1.01</v>
-      </c>
-      <c r="Z46">
-        <v>10</v>
-      </c>
-      <c r="AA46">
-        <v>1.2</v>
-      </c>
-      <c r="AB46">
-        <v>4.4</v>
-      </c>
-      <c r="AC46">
-        <v>1.5</v>
-      </c>
       <c r="AD46">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AE46">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AG46">
-        <v>4.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>1.51</v>
+        <v>2.27</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="O47">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="P47">
-        <v>29</v>
+        <v>5.75</v>
       </c>
       <c r="Q47">
+        <v>1.96</v>
+      </c>
+      <c r="R47">
+        <v>2.35</v>
+      </c>
+      <c r="S47">
         <v>1.25</v>
       </c>
-      <c r="R47">
-        <v>3.62</v>
-      </c>
-      <c r="S47">
+      <c r="T47">
+        <v>3.8</v>
+      </c>
+      <c r="U47">
+        <v>2.19</v>
+      </c>
+      <c r="V47">
+        <v>1.66</v>
+      </c>
+      <c r="W47">
         <v>1.14</v>
-      </c>
-      <c r="T47">
-        <v>5</v>
-      </c>
-      <c r="U47">
-        <v>1.85</v>
-      </c>
-      <c r="V47">
-        <v>1.9</v>
-      </c>
-      <c r="W47">
-        <v>1.31</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z47">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA47">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AD47">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AE47">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AF47">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>9</v>
+        <v>2.69</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,40 +8133,40 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="O48">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P48">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="Q48">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="R48">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="S48">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="T48">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="U48">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V48">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W48">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z48">
         <v>7.1</v>
@@ -8175,22 +8175,22 @@
         <v>1.3</v>
       </c>
       <c r="AB48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC48">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AD48">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AE48">
         <v>1.41</v>
       </c>
       <c r="AF48">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK48">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="P50">
-        <v>4.54</v>
+        <v>14.5</v>
       </c>
       <c r="Q50">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="R50">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="S50">
+        <v>1.19</v>
+      </c>
+      <c r="T50">
+        <v>5.2</v>
+      </c>
+      <c r="U50">
+        <v>1.91</v>
+      </c>
+      <c r="V50">
+        <v>1.91</v>
+      </c>
+      <c r="W50">
         <v>1.25</v>
       </c>
-      <c r="T50">
-        <v>3.94</v>
-      </c>
-      <c r="U50">
-        <v>2.25</v>
-      </c>
-      <c r="V50">
-        <v>1.57</v>
-      </c>
-      <c r="W50">
-        <v>1.13</v>
-      </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Z50">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="AA50">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AB50">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="AC50">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="AD50">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="AE50">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>2.27</v>
+        <v>5.25</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1942,10 +1942,10 @@
         <v>1.48</v>
       </c>
       <c r="O10">
-        <v>4.05</v>
+        <v>4.54</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q10">
         <v>1.9</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>5.53</v>
+        <v>4.96</v>
       </c>
       <c r="O12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P12">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="Q12">
         <v>4.6</v>
@@ -2301,10 +2301,10 @@
         <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.6</v>
+        <v>6.04</v>
       </c>
       <c r="AA12">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AB12">
         <v>2.66</v>
@@ -2923,7 +2923,7 @@
         <v>3.6</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,43 +3080,43 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="R17">
         <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA17">
         <v>1.5</v>
@@ -3125,19 +3125,19 @@
         <v>2.5</v>
       </c>
       <c r="AC17">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AD17">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF17">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AG17">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>3.54</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.05</v>
+        <v>5.65</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>3.3</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
+        <v>1.03</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.25</v>
+      </c>
+      <c r="Z19">
+        <v>2.5</v>
+      </c>
+      <c r="AA19">
+        <v>1.77</v>
+      </c>
+      <c r="AB19">
+        <v>1.57</v>
+      </c>
+      <c r="AC19">
+        <v>2.8</v>
+      </c>
+      <c r="AD19">
+        <v>1.18</v>
+      </c>
+      <c r="AE19">
         <v>1.04</v>
       </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.37</v>
-      </c>
-      <c r="Z19">
-        <v>2.97</v>
-      </c>
-      <c r="AA19">
-        <v>2.15</v>
-      </c>
-      <c r="AB19">
-        <v>1.68</v>
-      </c>
-      <c r="AC19">
-        <v>3.87</v>
-      </c>
-      <c r="AD19">
-        <v>1.23</v>
-      </c>
-      <c r="AE19">
-        <v>1.03</v>
-      </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
         <v>1.67</v>
@@ -3575,7 +3575,7 @@
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
         <v>3.67</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>4.04</v>
       </c>
       <c r="P21">
-        <v>5.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -3753,7 +3753,7 @@
         <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="V21">
         <v>1.67</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="P22">
         <v>2.74</v>
@@ -3925,16 +3925,16 @@
         <v>1.03</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
         <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AA22">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB22">
         <v>1.75</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>2.7</v>
+      </c>
+      <c r="O23">
+        <v>3.15</v>
+      </c>
+      <c r="P23">
+        <v>2.24</v>
+      </c>
+      <c r="Q23">
+        <v>3.34</v>
+      </c>
+      <c r="R23">
         <v>2.1</v>
-      </c>
-      <c r="O23">
-        <v>3.5</v>
-      </c>
-      <c r="P23">
-        <v>3.4</v>
-      </c>
-      <c r="Q23">
-        <v>2.63</v>
-      </c>
-      <c r="R23">
-        <v>2.2</v>
       </c>
       <c r="S23">
         <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U23">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="V23">
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC23">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="AD23">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.61</v>
+        <v>2.79</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>4.5</v>
+        <v>2.23</v>
       </c>
       <c r="Q24">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V24">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA24">
+        <v>1.8</v>
+      </c>
+      <c r="AB24">
+        <v>1.97</v>
+      </c>
+      <c r="AC24">
+        <v>2.83</v>
+      </c>
+      <c r="AD24">
+        <v>1.33</v>
+      </c>
+      <c r="AE24">
+        <v>1.09</v>
+      </c>
+      <c r="AF24">
         <v>1.6</v>
       </c>
-      <c r="AB24">
-        <v>2.3</v>
-      </c>
-      <c r="AC24">
-        <v>2.38</v>
-      </c>
-      <c r="AD24">
-        <v>1.46</v>
-      </c>
-      <c r="AE24">
-        <v>1.16</v>
-      </c>
-      <c r="AF24">
-        <v>1.64</v>
-      </c>
       <c r="AG24">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="AK24">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="P25">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
         <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
         <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA25">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC25">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q26">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB26">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>3.26</v>
+        <v>2.69</v>
       </c>
       <c r="AD26">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
         <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>3.03</v>
       </c>
       <c r="P27">
-        <v>4.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q27">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>4.45</v>
+        <v>3.24</v>
       </c>
       <c r="AA27">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="AC27">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
+        <v>3.58</v>
+      </c>
+      <c r="P28">
+        <v>3.99</v>
+      </c>
+      <c r="Q28">
+        <v>2.2</v>
+      </c>
+      <c r="R28">
+        <v>2.3</v>
+      </c>
+      <c r="S28">
+        <v>1.29</v>
+      </c>
+      <c r="T28">
         <v>3.4</v>
       </c>
-      <c r="P28">
-        <v>2.01</v>
-      </c>
-      <c r="Q28">
-        <v>3.79</v>
-      </c>
-      <c r="R28">
-        <v>2.2</v>
-      </c>
-      <c r="S28">
-        <v>1.27</v>
-      </c>
-      <c r="T28">
-        <v>3.32</v>
-      </c>
       <c r="U28">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W28">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB28">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG28">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="P29">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="R29">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T29">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="U29">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="V29">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA29">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB29">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC29">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG29">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O30">
+        <v>3.13</v>
+      </c>
+      <c r="P30">
         <v>3.4</v>
       </c>
-      <c r="P30">
-        <v>2.55</v>
-      </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R30">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
+        <v>1.35</v>
+      </c>
+      <c r="T30">
+        <v>2.7</v>
+      </c>
+      <c r="U30">
+        <v>2.62</v>
+      </c>
+      <c r="V30">
+        <v>1.4</v>
+      </c>
+      <c r="W30">
+        <v>1.06</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.23</v>
+      </c>
+      <c r="Z30">
+        <v>3.42</v>
+      </c>
+      <c r="AA30">
+        <v>1.95</v>
+      </c>
+      <c r="AB30">
+        <v>1.85</v>
+      </c>
+      <c r="AC30">
+        <v>3.3</v>
+      </c>
+      <c r="AD30">
         <v>1.28</v>
       </c>
-      <c r="T30">
-        <v>3.25</v>
-      </c>
-      <c r="U30">
-        <v>2.45</v>
-      </c>
-      <c r="V30">
-        <v>1.44</v>
-      </c>
-      <c r="W30">
-        <v>1.11</v>
-      </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1.17</v>
-      </c>
-      <c r="Z30">
-        <v>3.95</v>
-      </c>
-      <c r="AA30">
-        <v>1.7</v>
-      </c>
-      <c r="AB30">
-        <v>2.1</v>
-      </c>
-      <c r="AC30">
-        <v>2.52</v>
-      </c>
-      <c r="AD30">
-        <v>1.41</v>
-      </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="O31">
+        <v>3.85</v>
+      </c>
+      <c r="P31">
+        <v>4.45</v>
+      </c>
+      <c r="Q31">
+        <v>2.05</v>
+      </c>
+      <c r="R31">
+        <v>2.4</v>
+      </c>
+      <c r="S31">
+        <v>1.29</v>
+      </c>
+      <c r="T31">
         <v>3.4</v>
       </c>
-      <c r="P31">
-        <v>3.1</v>
-      </c>
-      <c r="Q31">
-        <v>2.86</v>
-      </c>
-      <c r="R31">
-        <v>2.07</v>
-      </c>
-      <c r="S31">
-        <v>1.36</v>
-      </c>
-      <c r="T31">
-        <v>2.88</v>
-      </c>
       <c r="U31">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>3.24</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AC31">
-        <v>3.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AG31">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.53</v>
       </c>
       <c r="O32">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>4.97</v>
+        <v>5.25</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -5564,10 +5564,10 @@
         <v>3.82</v>
       </c>
       <c r="AA32">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O33">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
         <v>3.81</v>
@@ -5890,7 +5890,7 @@
         <v>5.09</v>
       </c>
       <c r="AA34">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
         <v>2.26</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O35">
-        <v>3.89</v>
+        <v>3.77</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="Q35">
         <v>1.95</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="O37">
         <v>3.7</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,65 +6503,65 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.03</v>
       </c>
       <c r="P38">
+        <v>2.65</v>
+      </c>
+      <c r="Q38">
+        <v>3.25</v>
+      </c>
+      <c r="R38">
+        <v>2.1</v>
+      </c>
+      <c r="S38">
+        <v>1.39</v>
+      </c>
+      <c r="T38">
         <v>3</v>
       </c>
-      <c r="Q38">
-        <v>2.5</v>
-      </c>
-      <c r="R38">
-        <v>2.25</v>
-      </c>
-      <c r="S38">
-        <v>1.33</v>
-      </c>
-      <c r="T38">
-        <v>3.16</v>
-      </c>
       <c r="U38">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>4.34</v>
+        <v>3.34</v>
       </c>
       <c r="AA38">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB38">
+        <v>1.9</v>
+      </c>
+      <c r="AC38">
+        <v>2.92</v>
+      </c>
+      <c r="AD38">
+        <v>1.31</v>
+      </c>
+      <c r="AE38">
+        <v>1.08</v>
+      </c>
+      <c r="AF38">
+        <v>1.67</v>
+      </c>
+      <c r="AG38">
         <v>2.1</v>
       </c>
-      <c r="AC38">
-        <v>2.72</v>
-      </c>
-      <c r="AD38">
-        <v>1.45</v>
-      </c>
-      <c r="AE38">
-        <v>1.17</v>
-      </c>
-      <c r="AF38">
-        <v>1.53</v>
-      </c>
-      <c r="AG38">
-        <v>2.3</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.41</v>
+        <v>2.71</v>
       </c>
       <c r="O39">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
+        <v>2.29</v>
+      </c>
+      <c r="Q39">
+        <v>3.62</v>
+      </c>
+      <c r="R39">
+        <v>2.31</v>
+      </c>
+      <c r="S39">
+        <v>1.31</v>
+      </c>
+      <c r="T39">
+        <v>3.19</v>
+      </c>
+      <c r="U39">
         <v>2.65</v>
       </c>
-      <c r="Q39">
-        <v>3.25</v>
-      </c>
-      <c r="R39">
-        <v>2.1</v>
-      </c>
-      <c r="S39">
-        <v>1.39</v>
-      </c>
-      <c r="T39">
-        <v>3</v>
-      </c>
-      <c r="U39">
-        <v>2.59</v>
-      </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="P40">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V40">
+        <v>1.52</v>
+      </c>
+      <c r="W40">
+        <v>1.11</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.21</v>
+      </c>
+      <c r="Z40">
+        <v>4.34</v>
+      </c>
+      <c r="AA40">
+        <v>1.65</v>
+      </c>
+      <c r="AB40">
+        <v>2.23</v>
+      </c>
+      <c r="AC40">
+        <v>2.66</v>
+      </c>
+      <c r="AD40">
         <v>1.46</v>
       </c>
-      <c r="W40">
-        <v>1.07</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.2</v>
-      </c>
-      <c r="Z40">
-        <v>3.3</v>
-      </c>
-      <c r="AA40">
-        <v>1.79</v>
-      </c>
-      <c r="AB40">
-        <v>1.95</v>
-      </c>
-      <c r="AC40">
-        <v>2.88</v>
-      </c>
-      <c r="AD40">
-        <v>1.32</v>
-      </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG40">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="O41">
-        <v>3.42</v>
+        <v>3.07</v>
       </c>
       <c r="P41">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="Q41">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="R41">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>3.19</v>
+        <v>2.75</v>
       </c>
       <c r="U41">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AA41">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC41">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="AD41">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="O42">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.01</v>
+        <v>2.95</v>
       </c>
       <c r="Q42">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.04</v>
+        <v>4.34</v>
       </c>
       <c r="AA42">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AB42">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>3.34</v>
+        <v>2.72</v>
       </c>
       <c r="AD42">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="O43">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="Q43">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V43">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB43">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG43">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK43">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="O47">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P47">
-        <v>5.75</v>
+        <v>29</v>
       </c>
       <c r="Q47">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="R47">
-        <v>2.35</v>
+        <v>3.62</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T47">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="AA47">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB47">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AC47">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AD47">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="AE47">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AF47">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK47">
-        <v>2.69</v>
+        <v>9</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="O48">
-        <v>9.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>29</v>
+        <v>2.1</v>
       </c>
       <c r="Q48">
+        <v>3.5</v>
+      </c>
+      <c r="R48">
+        <v>2.58</v>
+      </c>
+      <c r="S48">
         <v>1.25</v>
       </c>
-      <c r="R48">
-        <v>3.62</v>
-      </c>
-      <c r="S48">
-        <v>1.14</v>
-      </c>
       <c r="T48">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="U48">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="W48">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA48">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AB48">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC48">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="AD48">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AE48">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>9</v>
+        <v>1.36</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.1</v>
+        <v>1.17</v>
       </c>
       <c r="O49">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="P49">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="Q49">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="R49">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="S49">
+        <v>1.19</v>
+      </c>
+      <c r="T49">
+        <v>5.2</v>
+      </c>
+      <c r="U49">
+        <v>1.91</v>
+      </c>
+      <c r="V49">
+        <v>1.91</v>
+      </c>
+      <c r="W49">
         <v>1.25</v>
-      </c>
-      <c r="T49">
-        <v>3.84</v>
-      </c>
-      <c r="U49">
-        <v>2.2</v>
-      </c>
-      <c r="V49">
-        <v>1.64</v>
-      </c>
-      <c r="W49">
-        <v>1.17</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="AA49">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC49">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="AD49">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="AE49">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AF49">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>2.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AK49">
-        <v>1.36</v>
+        <v>5.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="O50">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="P50">
-        <v>14.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q50">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="R50">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="S50">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="V50">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="W50">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA50">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC50">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AD50">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="AE50">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AK50">
-        <v>5.25</v>
+        <v>2.69</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="O51">
         <v>3.15</v>
       </c>
       <c r="P51">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q51">
         <v>3.3</v>
@@ -8640,7 +8640,7 @@
         <v>1.41</v>
       </c>
       <c r="T51">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U51">
         <v>2.75</v>
@@ -8652,16 +8652,16 @@
         <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
         <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB51">
         <v>1.8</v>
@@ -8670,7 +8670,7 @@
         <v>3.42</v>
       </c>
       <c r="AD51">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
         <v>1.05</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
         <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="Q52">
         <v>3.1</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1178,7 +1178,7 @@
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
         <v>2.15</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O6">
         <v>5.5</v>
       </c>
       <c r="P6">
-        <v>7.04</v>
+        <v>7.3</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q8">
         <v>7.8</v>
@@ -1634,10 +1634,10 @@
         <v>2.47</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
         <v>1.04</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O9">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
@@ -1794,7 +1794,7 @@
         <v>1.57</v>
       </c>
       <c r="T9">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="U9">
         <v>3.5</v>
@@ -1815,10 +1815,10 @@
         <v>2.29</v>
       </c>
       <c r="AA9">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AB9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC9">
         <v>4.95</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O10">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="P10">
         <v>5.8</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S10">
         <v>1.26</v>
@@ -1972,31 +1972,31 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC10">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q11">
         <v>3.4</v>
@@ -2126,7 +2126,7 @@
         <v>2.92</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
         <v>1.04</v>
@@ -2144,7 +2144,7 @@
         <v>2.18</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC11">
         <v>3.98</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
         <v>3.7</v>
       </c>
       <c r="P15">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
         <v>1.45</v>
@@ -2778,7 +2778,7 @@
         <v>3</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2790,7 +2790,7 @@
         <v>1.32</v>
       </c>
       <c r="Z15">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AA15">
         <v>2.15</v>
@@ -2799,16 +2799,16 @@
         <v>1.63</v>
       </c>
       <c r="AC15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE15">
         <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
         <v>1.6</v>
@@ -2938,10 +2938,10 @@
         <v>3.4</v>
       </c>
       <c r="U16">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q17">
-        <v>1.75</v>
+        <v>3.54</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>5.05</v>
+        <v>5.65</v>
       </c>
       <c r="AA17">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC17">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AD17">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>1.75</v>
+      </c>
+      <c r="R18">
+        <v>2.5</v>
+      </c>
+      <c r="S18">
+        <v>1.22</v>
+      </c>
+      <c r="T18">
+        <v>3.6</v>
+      </c>
+      <c r="U18">
         <v>2.1</v>
       </c>
-      <c r="Q18">
-        <v>3.54</v>
-      </c>
-      <c r="R18">
-        <v>2.57</v>
-      </c>
-      <c r="S18">
-        <v>1.2</v>
-      </c>
-      <c r="T18">
-        <v>3.9</v>
-      </c>
-      <c r="U18">
-        <v>2.05</v>
-      </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.65</v>
+        <v>5.05</v>
       </c>
       <c r="AA18">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD18">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AG18">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,16 +3415,16 @@
         <v>3.3</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="U19">
         <v>2.32</v>
@@ -3572,10 +3572,10 @@
         <v>2.88</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
         <v>3.67</v>
@@ -3771,7 +3771,7 @@
         <v>4.8</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
         <v>2.38</v>
@@ -4064,7 +4064,7 @@
         <v>3.15</v>
       </c>
       <c r="P23">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="Q23">
         <v>3.34</v>
@@ -4097,7 +4097,7 @@
         <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
         <v>1.92</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="O25">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="P25">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
         <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W25">
         <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="AA25">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB25">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="AD25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,49 +4547,49 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="O26">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="P26">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="Q26">
-        <v>2.8</v>
+        <v>3.79</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U26">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z26">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC26">
         <v>2.69</v>
@@ -4598,13 +4598,13 @@
         <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O27">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="P27">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U27">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="P28">
-        <v>3.99</v>
+        <v>2.42</v>
       </c>
       <c r="Q28">
+        <v>3.1</v>
+      </c>
+      <c r="R28">
         <v>2.2</v>
       </c>
-      <c r="R28">
-        <v>2.3</v>
-      </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>4.45</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG28">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="O29">
-        <v>3.19</v>
+        <v>4.2</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>3.79</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="AA29">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB29">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AC29">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="O30">
-        <v>3.13</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
+        <v>4.45</v>
+      </c>
+      <c r="Q30">
+        <v>2.05</v>
+      </c>
+      <c r="R30">
+        <v>2.4</v>
+      </c>
+      <c r="S30">
+        <v>1.29</v>
+      </c>
+      <c r="T30">
         <v>3.4</v>
       </c>
-      <c r="Q30">
-        <v>2.63</v>
-      </c>
-      <c r="R30">
-        <v>2.2</v>
-      </c>
-      <c r="S30">
-        <v>1.35</v>
-      </c>
-      <c r="T30">
-        <v>2.7</v>
-      </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>3.03</v>
       </c>
       <c r="P31">
-        <v>4.45</v>
+        <v>2.82</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB31">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC31">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="AD31">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AG31">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>3.82</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5691,10 +5691,10 @@
         <v>1.85</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -5727,16 +5727,16 @@
         <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB33">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="AD33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
         <v>1.09</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="P34">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -5893,7 +5893,7 @@
         <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC34">
         <v>2.46</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="P35">
         <v>4.92</v>
@@ -6050,7 +6050,7 @@
         <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>5.51</v>
+        <v>5.49</v>
       </c>
       <c r="AA35">
         <v>1.47</v>
@@ -6509,7 +6509,7 @@
         <v>3.03</v>
       </c>
       <c r="P38">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q39">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="V39">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6702,28 +6702,28 @@
         <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB39">
         <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
         <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK39">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>3.78</v>
       </c>
       <c r="P40">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q40">
         <v>3.5</v>
@@ -6868,7 +6868,7 @@
         <v>4.34</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
         <v>2.23</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="O41">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="Q41">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="V41">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z41">
-        <v>3.04</v>
+        <v>4.34</v>
       </c>
       <c r="AA41">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AB41">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>3.34</v>
+        <v>2.72</v>
       </c>
       <c r="AD41">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AE41">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF41">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.14</v>
+        <v>3.46</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q42">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="U42">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>4.34</v>
+        <v>3.04</v>
       </c>
       <c r="AA42">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC42">
-        <v>2.72</v>
+        <v>3.34</v>
       </c>
       <c r="AD42">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,58 +7318,58 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q43">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="U43">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z43">
-        <v>3.3</v>
+        <v>4.06</v>
       </c>
       <c r="AA43">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB43">
         <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AD43">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
         <v>1.61</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
+        <v>1.25</v>
+      </c>
+      <c r="AK43">
         <v>1.33</v>
-      </c>
-      <c r="AK43">
-        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="O51">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
         <v>3.3</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
         <v>4.2</v>
@@ -2458,7 +2458,7 @@
         <v>1.14</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.17</v>
@@ -2470,7 +2470,7 @@
         <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC13">
         <v>2.46</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="O14">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="P14">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -2606,13 +2606,13 @@
         <v>2.75</v>
       </c>
       <c r="S14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V14">
         <v>1.73</v>
@@ -2627,16 +2627,16 @@
         <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="AA14">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="AC14">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AD14">
         <v>1.75</v>
@@ -2920,10 +2920,10 @@
         <v>1.75</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -2971,10 +2971,10 @@
         <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P23">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
         <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V23">
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.79</v>
+        <v>1.67</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>2.23</v>
+        <v>4.6</v>
       </c>
       <c r="Q24">
+        <v>2.2</v>
+      </c>
+      <c r="R24">
+        <v>2.3</v>
+      </c>
+      <c r="S24">
+        <v>1.29</v>
+      </c>
+      <c r="T24">
         <v>3.4</v>
       </c>
-      <c r="R24">
-        <v>2.11</v>
-      </c>
-      <c r="S24">
-        <v>1.33</v>
-      </c>
-      <c r="T24">
-        <v>2.96</v>
-      </c>
       <c r="U24">
-        <v>2.64</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.14</v>
+      </c>
+      <c r="Z24">
+        <v>4.45</v>
+      </c>
+      <c r="AA24">
+        <v>1.59</v>
+      </c>
+      <c r="AB24">
+        <v>2.16</v>
+      </c>
+      <c r="AC24">
+        <v>2.43</v>
+      </c>
+      <c r="AD24">
+        <v>1.44</v>
+      </c>
+      <c r="AE24">
+        <v>1.14</v>
+      </c>
+      <c r="AF24">
+        <v>1.61</v>
+      </c>
+      <c r="AG24">
+        <v>2.18</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.19</v>
       </c>
-      <c r="Z24">
-        <v>3.74</v>
-      </c>
-      <c r="AA24">
-        <v>1.8</v>
-      </c>
-      <c r="AB24">
-        <v>1.97</v>
-      </c>
-      <c r="AC24">
-        <v>2.83</v>
-      </c>
-      <c r="AD24">
-        <v>1.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.09</v>
-      </c>
-      <c r="AF24">
-        <v>1.6</v>
-      </c>
-      <c r="AG24">
-        <v>2.16</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.52</v>
-      </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,49 +4384,49 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="P25">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>3.79</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U25">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V25">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA25">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC25">
         <v>2.69</v>
@@ -4435,13 +4435,13 @@
         <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,49 +4547,49 @@
         </is>
       </c>
       <c r="N26">
+        <v>2.24</v>
+      </c>
+      <c r="O26">
+        <v>3.13</v>
+      </c>
+      <c r="P26">
+        <v>2.65</v>
+      </c>
+      <c r="Q26">
+        <v>2.8</v>
+      </c>
+      <c r="R26">
+        <v>2.25</v>
+      </c>
+      <c r="S26">
+        <v>1.3</v>
+      </c>
+      <c r="T26">
         <v>3.2</v>
       </c>
-      <c r="O26">
-        <v>3.19</v>
-      </c>
-      <c r="P26">
-        <v>2.04</v>
-      </c>
-      <c r="Q26">
-        <v>3.79</v>
-      </c>
-      <c r="R26">
-        <v>2.2</v>
-      </c>
-      <c r="S26">
-        <v>1.27</v>
-      </c>
-      <c r="T26">
-        <v>3.32</v>
-      </c>
       <c r="U26">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB26">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
         <v>2.69</v>
@@ -4598,13 +4598,13 @@
         <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="Q27">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC27">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="O28">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="AA28">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AC28">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AK28">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q29">
+        <v>3.1</v>
+      </c>
+      <c r="R29">
         <v>2.2</v>
       </c>
-      <c r="R29">
-        <v>2.3</v>
-      </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>4.45</v>
+        <v>3.98</v>
       </c>
       <c r="AA29">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AB29">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AC29">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD29">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG29">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,65 +5362,65 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.7</v>
+      </c>
+      <c r="O31">
+        <v>3.15</v>
+      </c>
+      <c r="P31">
+        <v>2.31</v>
+      </c>
+      <c r="Q31">
+        <v>3.34</v>
+      </c>
+      <c r="R31">
+        <v>2.1</v>
+      </c>
+      <c r="S31">
+        <v>1.35</v>
+      </c>
+      <c r="T31">
+        <v>2.77</v>
+      </c>
+      <c r="U31">
+        <v>2.82</v>
+      </c>
+      <c r="V31">
+        <v>1.4</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
+        <v>3.5</v>
+      </c>
+      <c r="AA31">
+        <v>1.81</v>
+      </c>
+      <c r="AB31">
+        <v>1.92</v>
+      </c>
+      <c r="AC31">
+        <v>3.26</v>
+      </c>
+      <c r="AD31">
+        <v>1.32</v>
+      </c>
+      <c r="AE31">
+        <v>1.09</v>
+      </c>
+      <c r="AF31">
+        <v>1.62</v>
+      </c>
+      <c r="AG31">
         <v>2.15</v>
       </c>
-      <c r="O31">
-        <v>3.03</v>
-      </c>
-      <c r="P31">
-        <v>2.82</v>
-      </c>
-      <c r="Q31">
-        <v>2.86</v>
-      </c>
-      <c r="R31">
-        <v>2.07</v>
-      </c>
-      <c r="S31">
-        <v>1.36</v>
-      </c>
-      <c r="T31">
-        <v>2.88</v>
-      </c>
-      <c r="U31">
-        <v>2.8</v>
-      </c>
-      <c r="V31">
-        <v>1.36</v>
-      </c>
-      <c r="W31">
-        <v>1.05</v>
-      </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
-      <c r="Y31">
-        <v>1.32</v>
-      </c>
-      <c r="Z31">
-        <v>3.24</v>
-      </c>
-      <c r="AA31">
-        <v>2</v>
-      </c>
-      <c r="AB31">
-        <v>1.76</v>
-      </c>
-      <c r="AC31">
-        <v>3.6</v>
-      </c>
-      <c r="AD31">
-        <v>1.24</v>
-      </c>
-      <c r="AE31">
-        <v>1.06</v>
-      </c>
-      <c r="AF31">
-        <v>1.76</v>
-      </c>
-      <c r="AG31">
-        <v>1.96</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.63</v>
+        <v>3.57</v>
       </c>
       <c r="O38">
-        <v>3.03</v>
+        <v>3.78</v>
       </c>
       <c r="P38">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U38">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
+        <v>1.21</v>
+      </c>
+      <c r="Z38">
+        <v>4.34</v>
+      </c>
+      <c r="AA38">
+        <v>1.66</v>
+      </c>
+      <c r="AB38">
+        <v>2.23</v>
+      </c>
+      <c r="AC38">
+        <v>2.66</v>
+      </c>
+      <c r="AD38">
+        <v>1.46</v>
+      </c>
+      <c r="AE38">
+        <v>1.18</v>
+      </c>
+      <c r="AF38">
+        <v>1.56</v>
+      </c>
+      <c r="AG38">
+        <v>2.28</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.24</v>
       </c>
-      <c r="Z38">
-        <v>3.34</v>
-      </c>
-      <c r="AA38">
-        <v>1.9</v>
-      </c>
-      <c r="AB38">
-        <v>1.9</v>
-      </c>
-      <c r="AC38">
-        <v>2.92</v>
-      </c>
-      <c r="AD38">
-        <v>1.31</v>
-      </c>
-      <c r="AE38">
-        <v>1.08</v>
-      </c>
-      <c r="AF38">
-        <v>1.67</v>
-      </c>
-      <c r="AG38">
-        <v>2.1</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.3</v>
-      </c>
       <c r="AK38">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="O39">
         <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
         <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="U39">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>3.3</v>
+        <v>4.34</v>
       </c>
       <c r="AA39">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AD39">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.57</v>
+        <v>2.8</v>
       </c>
       <c r="O40">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="Q40">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U40">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V40">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB40">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AK40">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.03</v>
       </c>
       <c r="P41">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>4.34</v>
+        <v>3.34</v>
       </c>
       <c r="AA41">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
+        <v>1.9</v>
+      </c>
+      <c r="AC41">
+        <v>2.92</v>
+      </c>
+      <c r="AD41">
+        <v>1.31</v>
+      </c>
+      <c r="AE41">
+        <v>1.08</v>
+      </c>
+      <c r="AF41">
+        <v>1.67</v>
+      </c>
+      <c r="AG41">
         <v>2.1</v>
       </c>
-      <c r="AC41">
-        <v>2.72</v>
-      </c>
-      <c r="AD41">
-        <v>1.45</v>
-      </c>
-      <c r="AE41">
-        <v>1.17</v>
-      </c>
-      <c r="AF41">
-        <v>1.53</v>
-      </c>
-      <c r="AG41">
-        <v>2.3</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7487,7 +7487,7 @@
         <v>4.5</v>
       </c>
       <c r="P44">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>2.05</v>
@@ -7502,7 +7502,7 @@
         <v>4</v>
       </c>
       <c r="U44">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="V44">
         <v>1.62</v>
@@ -7659,7 +7659,7 @@
         <v>2.62</v>
       </c>
       <c r="S45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T45">
         <v>5.75</v>
@@ -7668,7 +7668,7 @@
         <v>1.67</v>
       </c>
       <c r="V45">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="W45">
         <v>1.36</v>
@@ -7686,16 +7686,16 @@
         <v>1.2</v>
       </c>
       <c r="AB45">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC45">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AD45">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AE45">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF45">
         <v>1.18</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.65</v>
+        <v>1.06</v>
       </c>
       <c r="O46">
-        <v>4.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P46">
-        <v>4.54</v>
+        <v>27</v>
       </c>
       <c r="Q46">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>3.62</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T46">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="U46">
+        <v>1.85</v>
+      </c>
+      <c r="V46">
+        <v>1.9</v>
+      </c>
+      <c r="W46">
+        <v>1.29</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.05</v>
+      </c>
+      <c r="Z46">
+        <v>6.95</v>
+      </c>
+      <c r="AA46">
+        <v>1.28</v>
+      </c>
+      <c r="AB46">
+        <v>3.6</v>
+      </c>
+      <c r="AC46">
+        <v>1.72</v>
+      </c>
+      <c r="AD46">
+        <v>2.15</v>
+      </c>
+      <c r="AE46">
+        <v>1.44</v>
+      </c>
+      <c r="AF46">
         <v>2.25</v>
       </c>
-      <c r="V46">
-        <v>1.57</v>
-      </c>
-      <c r="W46">
-        <v>1.13</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.12</v>
-      </c>
-      <c r="Z46">
-        <v>4.65</v>
-      </c>
-      <c r="AA46">
-        <v>1.57</v>
-      </c>
-      <c r="AB46">
-        <v>2.33</v>
-      </c>
-      <c r="AC46">
-        <v>2.4</v>
-      </c>
-      <c r="AD46">
-        <v>1.56</v>
-      </c>
-      <c r="AE46">
-        <v>1.21</v>
-      </c>
-      <c r="AF46">
-        <v>1.56</v>
-      </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AK46">
-        <v>2.27</v>
+        <v>8</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.05</v>
+        <v>3.35</v>
       </c>
       <c r="O47">
-        <v>9.800000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="P47">
-        <v>29</v>
+        <v>2.1</v>
       </c>
       <c r="Q47">
+        <v>3.5</v>
+      </c>
+      <c r="R47">
+        <v>2.38</v>
+      </c>
+      <c r="S47">
         <v>1.25</v>
       </c>
-      <c r="R47">
-        <v>3.62</v>
-      </c>
-      <c r="S47">
-        <v>1.14</v>
-      </c>
       <c r="T47">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="U47">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="W47">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA47">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AB47">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC47">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="AD47">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AE47">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>9</v>
+        <v>1.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.1</v>
+        <v>1.17</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="P48">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="R48">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="S48">
+        <v>1.15</v>
+      </c>
+      <c r="T48">
+        <v>5.2</v>
+      </c>
+      <c r="U48">
+        <v>1.93</v>
+      </c>
+      <c r="V48">
+        <v>1.89</v>
+      </c>
+      <c r="W48">
         <v>1.25</v>
-      </c>
-      <c r="T48">
-        <v>3.84</v>
-      </c>
-      <c r="U48">
-        <v>2.2</v>
-      </c>
-      <c r="V48">
-        <v>1.64</v>
-      </c>
-      <c r="W48">
-        <v>1.17</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="AA48">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AB48">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC48">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD48">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG48">
-        <v>2.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AK48">
-        <v>1.36</v>
+        <v>5.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="O49">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="P49">
-        <v>14.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q49">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="R49">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="S49">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="V49">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="W49">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>7.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA49">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AB49">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC49">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AD49">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="AE49">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AF49">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>5.25</v>
+        <v>2.69</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="O50">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="P50">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="R50">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="U50">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA50">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AC50">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AE50">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>2.69</v>
+        <v>2.27</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3">
@@ -919,7 +919,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G4">
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AE5">
+        <v>1.26</v>
+      </c>
+      <c r="AF5">
+        <v>1.75</v>
+      </c>
+      <c r="AG5">
+        <v>1.85</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.14</v>
       </c>
-      <c r="AF5">
-        <v>1.62</v>
-      </c>
-      <c r="AG5">
-        <v>2.15</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.2</v>
-      </c>
       <c r="AK5">
-        <v>2.1</v>
+        <v>3.54</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>2.3</v>
       </c>
       <c r="AB7">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC7">
         <v>4.15</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
         <v>7.8</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
         <v>2.47</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V8">
         <v>1.35</v>
@@ -1643,10 +1643,10 @@
         <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
         <v>2.88</v>
@@ -1655,22 +1655,22 @@
         <v>2.2</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC8">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG8">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
         <v>1.08</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="O9">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P9">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
       </c>
       <c r="R9">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
         <v>2.21</v>
@@ -1809,16 +1809,16 @@
         <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z9">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AA9">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AB9">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC9">
         <v>4.95</v>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O10">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P10">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S10">
         <v>1.26</v>
@@ -1972,31 +1972,31 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>4.08</v>
+        <v>4.33</v>
       </c>
       <c r="AA10">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AD10">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.85</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>2.37</v>
+        <v>1.47</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="R11">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="T11">
-        <v>2.46</v>
+        <v>3.84</v>
       </c>
       <c r="U11">
-        <v>2.92</v>
+        <v>1.98</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
+        <v>1.08</v>
+      </c>
+      <c r="Z11">
+        <v>6.5</v>
+      </c>
+      <c r="AA11">
         <v>1.4</v>
       </c>
-      <c r="Z11">
-        <v>2.7</v>
-      </c>
-      <c r="AA11">
-        <v>2.18</v>
-      </c>
       <c r="AB11">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="AC11">
-        <v>3.98</v>
+        <v>1.98</v>
       </c>
       <c r="AD11">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="AE11">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG11">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK11">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-20 12:10:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.96</v>
+        <v>1.7</v>
       </c>
       <c r="O12">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="P12">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
+        <v>2.14</v>
+      </c>
+      <c r="R12">
+        <v>2.41</v>
+      </c>
+      <c r="S12">
+        <v>1.29</v>
+      </c>
+      <c r="T12">
+        <v>3.64</v>
+      </c>
+      <c r="U12">
+        <v>2.27</v>
+      </c>
+      <c r="V12">
+        <v>1.61</v>
+      </c>
+      <c r="W12">
+        <v>1.14</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.17</v>
+      </c>
+      <c r="Z12">
         <v>4.6</v>
       </c>
-      <c r="R12">
-        <v>2.6</v>
-      </c>
-      <c r="S12">
-        <v>1.18</v>
-      </c>
-      <c r="T12">
-        <v>3.84</v>
-      </c>
-      <c r="U12">
-        <v>2.04</v>
-      </c>
-      <c r="V12">
-        <v>1.67</v>
-      </c>
-      <c r="W12">
+      <c r="AA12">
+        <v>1.61</v>
+      </c>
+      <c r="AB12">
+        <v>2.35</v>
+      </c>
+      <c r="AC12">
+        <v>2.46</v>
+      </c>
+      <c r="AD12">
+        <v>1.47</v>
+      </c>
+      <c r="AE12">
         <v>1.15</v>
       </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.08</v>
-      </c>
-      <c r="Z12">
-        <v>6.04</v>
-      </c>
-      <c r="AA12">
-        <v>1.39</v>
-      </c>
-      <c r="AB12">
-        <v>2.66</v>
-      </c>
-      <c r="AC12">
-        <v>2.05</v>
-      </c>
-      <c r="AD12">
-        <v>1.72</v>
-      </c>
-      <c r="AE12">
-        <v>1.26</v>
-      </c>
       <c r="AF12">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-20 12:10:00</t>
+          <t>2026-10-20 13:45:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.7</v>
+        <v>8.75</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>6.25</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q13">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.64</v>
+        <v>4.75</v>
       </c>
       <c r="U13">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="V13">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>6.15</v>
       </c>
       <c r="AA13">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AB13">
-        <v>2.35</v>
+        <v>3.01</v>
       </c>
       <c r="AC13">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="AD13">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>8.75</v>
+        <v>5.4</v>
       </c>
       <c r="O14">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R14">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>4.75</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="V14">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
+        <v>1.36</v>
+      </c>
+      <c r="Z14">
+        <v>3.1</v>
+      </c>
+      <c r="AA14">
+        <v>2.15</v>
+      </c>
+      <c r="AB14">
+        <v>1.65</v>
+      </c>
+      <c r="AC14">
+        <v>4.2</v>
+      </c>
+      <c r="AD14">
+        <v>1.22</v>
+      </c>
+      <c r="AE14">
         <v>1.07</v>
       </c>
-      <c r="Z14">
-        <v>6.15</v>
-      </c>
-      <c r="AA14">
-        <v>1.36</v>
-      </c>
-      <c r="AB14">
-        <v>3.01</v>
-      </c>
-      <c r="AC14">
-        <v>2.03</v>
-      </c>
-      <c r="AD14">
-        <v>1.75</v>
-      </c>
-      <c r="AE14">
-        <v>1.33</v>
-      </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-20 13:45:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="P15">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AD15">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q17">
         <v>3.54</v>
@@ -3433,7 +3433,7 @@
         <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3445,10 +3445,10 @@
         <v>2.5</v>
       </c>
       <c r="AA19">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB19">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC19">
         <v>2.8</v>
@@ -3479,7 +3479,7 @@
         <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
         <v>3.67</v>
@@ -3587,13 +3587,13 @@
         <v>1.39</v>
       </c>
       <c r="T20">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="U20">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3738,7 +3738,7 @@
         <v>4.04</v>
       </c>
       <c r="P21">
-        <v>4.92</v>
+        <v>5.5</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
         <v>2.74</v>
@@ -3934,7 +3934,7 @@
         <v>2.93</v>
       </c>
       <c r="AA22">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
         <v>1.75</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>2.6</v>
+      </c>
+      <c r="O23">
+        <v>3.09</v>
+      </c>
+      <c r="P23">
+        <v>2.3</v>
+      </c>
+      <c r="Q23">
+        <v>3.34</v>
+      </c>
+      <c r="R23">
         <v>2.1</v>
-      </c>
-      <c r="O23">
-        <v>3.13</v>
-      </c>
-      <c r="P23">
-        <v>3.3</v>
-      </c>
-      <c r="Q23">
-        <v>2.63</v>
-      </c>
-      <c r="R23">
-        <v>2.2</v>
       </c>
       <c r="S23">
         <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U23">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="V23">
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC23">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="AD23">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q24">
+        <v>3.79</v>
+      </c>
+      <c r="R24">
         <v>2.2</v>
       </c>
-      <c r="R24">
-        <v>2.3</v>
-      </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>4.45</v>
+        <v>3.98</v>
       </c>
       <c r="AA24">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AB24">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AC24">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="O25">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>3.79</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S25">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="U25">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
+        <v>1.06</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>1.19</v>
+      </c>
+      <c r="Z25">
+        <v>3.74</v>
+      </c>
+      <c r="AA25">
+        <v>1.8</v>
+      </c>
+      <c r="AB25">
+        <v>1.97</v>
+      </c>
+      <c r="AC25">
+        <v>2.83</v>
+      </c>
+      <c r="AD25">
+        <v>1.33</v>
+      </c>
+      <c r="AE25">
         <v>1.09</v>
       </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>1.17</v>
-      </c>
-      <c r="Z25">
-        <v>3.98</v>
-      </c>
-      <c r="AA25">
-        <v>1.72</v>
-      </c>
-      <c r="AB25">
-        <v>2.06</v>
-      </c>
-      <c r="AC25">
-        <v>2.69</v>
-      </c>
-      <c r="AD25">
+      <c r="AF25">
+        <v>1.6</v>
+      </c>
+      <c r="AG25">
+        <v>2.16</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.52</v>
+      </c>
+      <c r="AK25">
         <v>1.36</v>
-      </c>
-      <c r="AE25">
-        <v>1.1</v>
-      </c>
-      <c r="AF25">
-        <v>1.58</v>
-      </c>
-      <c r="AG25">
-        <v>2.23</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.25</v>
-      </c>
-      <c r="AK25">
-        <v>1.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="O26">
-        <v>3.13</v>
+        <v>3.85</v>
       </c>
       <c r="P26">
-        <v>2.65</v>
+        <v>4.45</v>
       </c>
       <c r="Q26">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC26">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O27">
-        <v>3.03</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="Q27">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>3.24</v>
+        <v>4.45</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AB27">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="AC27">
-        <v>3.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AG27">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,37 +4873,37 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R28">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.19</v>
@@ -4912,25 +4912,25 @@
         <v>3.74</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB28">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
+        <v>1.27</v>
+      </c>
+      <c r="AK28">
         <v>1.52</v>
-      </c>
-      <c r="AK28">
-        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="O30">
-        <v>3.85</v>
+        <v>3.13</v>
       </c>
       <c r="P30">
-        <v>4.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q30">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD30">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="P31">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="Q31">
-        <v>3.34</v>
+        <v>2.86</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA31">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC31">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG31">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q33">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="R33">
+        <v>2.28</v>
+      </c>
+      <c r="S33">
+        <v>1.22</v>
+      </c>
+      <c r="T33">
+        <v>3.8</v>
+      </c>
+      <c r="U33">
         <v>2.25</v>
       </c>
-      <c r="S33">
-        <v>1.3</v>
-      </c>
-      <c r="T33">
-        <v>3.1</v>
-      </c>
-      <c r="U33">
-        <v>2.6</v>
-      </c>
       <c r="V33">
+        <v>1.57</v>
+      </c>
+      <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.17</v>
+      </c>
+      <c r="Z33">
+        <v>5</v>
+      </c>
+      <c r="AA33">
+        <v>1.53</v>
+      </c>
+      <c r="AB33">
+        <v>2.45</v>
+      </c>
+      <c r="AC33">
+        <v>2.45</v>
+      </c>
+      <c r="AD33">
+        <v>1.53</v>
+      </c>
+      <c r="AE33">
+        <v>1.2</v>
+      </c>
+      <c r="AF33">
+        <v>1.47</v>
+      </c>
+      <c r="AG33">
+        <v>2.63</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.21</v>
+      </c>
+      <c r="AK33">
         <v>1.45</v>
-      </c>
-      <c r="W33">
-        <v>1.07</v>
-      </c>
-      <c r="X33">
-        <v>1</v>
-      </c>
-      <c r="Y33">
-        <v>1.21</v>
-      </c>
-      <c r="Z33">
-        <v>3.58</v>
-      </c>
-      <c r="AA33">
-        <v>1.77</v>
-      </c>
-      <c r="AB33">
-        <v>1.91</v>
-      </c>
-      <c r="AC33">
-        <v>3.07</v>
-      </c>
-      <c r="AD33">
-        <v>1.36</v>
-      </c>
-      <c r="AE33">
-        <v>1.09</v>
-      </c>
-      <c r="AF33">
-        <v>1.67</v>
-      </c>
-      <c r="AG33">
-        <v>2.1</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.25</v>
-      </c>
-      <c r="AK33">
-        <v>1.83</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="O34">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="P34">
-        <v>2.49</v>
+        <v>4.92</v>
       </c>
       <c r="Q34">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="R34">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>5.09</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC34">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AD34">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AE34">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="O35">
-        <v>3.89</v>
+        <v>4.25</v>
       </c>
       <c r="P35">
-        <v>4.92</v>
+        <v>4.9</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U35">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="V35">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W35">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z35">
-        <v>5.49</v>
+        <v>6.5</v>
       </c>
       <c r="AA35">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC35">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AD35">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AE35">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF35">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK35">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.42</v>
+        <v>4</v>
       </c>
       <c r="O36">
-        <v>4.65</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q36">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="R36">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="S36">
         <v>1.2</v>
@@ -6198,43 +6198,43 @@
         <v>4</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>6.08</v>
+        <v>4.9</v>
       </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AB36">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AD36">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AE36">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>2.38</v>
+        <v>1.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.58</v>
+        <v>2.13</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="Q37">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>4.33</v>
+      </c>
+      <c r="AA37">
+        <v>1.67</v>
+      </c>
+      <c r="AB37">
+        <v>2.1</v>
+      </c>
+      <c r="AC37">
+        <v>2.88</v>
+      </c>
+      <c r="AD37">
+        <v>1.4</v>
+      </c>
+      <c r="AE37">
         <v>1.14</v>
       </c>
-      <c r="Z37">
-        <v>4.9</v>
-      </c>
-      <c r="AA37">
-        <v>1.5</v>
-      </c>
-      <c r="AB37">
-        <v>2.38</v>
-      </c>
-      <c r="AC37">
-        <v>2.2</v>
-      </c>
-      <c r="AD37">
-        <v>1.61</v>
-      </c>
-      <c r="AE37">
-        <v>1.2</v>
-      </c>
       <c r="AF37">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.57</v>
+        <v>2.83</v>
       </c>
       <c r="O38">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="P38">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="Q38">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S38">
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="U38">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD38">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.43</v>
       </c>
       <c r="P39">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q39">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="S39">
         <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AC39">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="O40">
         <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S40">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC40">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD40">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
         <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,61 +7158,61 @@
         <v>3.46</v>
       </c>
       <c r="O42">
+        <v>3.31</v>
+      </c>
+      <c r="P42">
+        <v>2.02</v>
+      </c>
+      <c r="Q42">
+        <v>3.8</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="S42">
+        <v>1.36</v>
+      </c>
+      <c r="T42">
+        <v>2.88</v>
+      </c>
+      <c r="U42">
+        <v>2.88</v>
+      </c>
+      <c r="V42">
+        <v>1.36</v>
+      </c>
+      <c r="W42">
+        <v>1.05</v>
+      </c>
+      <c r="X42">
+        <v>1.05</v>
+      </c>
+      <c r="Y42">
+        <v>1.3</v>
+      </c>
+      <c r="Z42">
+        <v>3.4</v>
+      </c>
+      <c r="AA42">
+        <v>2</v>
+      </c>
+      <c r="AB42">
+        <v>1.8</v>
+      </c>
+      <c r="AC42">
         <v>3.5</v>
       </c>
-      <c r="P42">
-        <v>2.05</v>
-      </c>
-      <c r="Q42">
-        <v>3.9</v>
-      </c>
-      <c r="R42">
-        <v>2.1</v>
-      </c>
-      <c r="S42">
-        <v>1.38</v>
-      </c>
-      <c r="T42">
-        <v>2.75</v>
-      </c>
-      <c r="U42">
-        <v>2.75</v>
-      </c>
-      <c r="V42">
-        <v>1.38</v>
-      </c>
-      <c r="W42">
-        <v>1.06</v>
-      </c>
-      <c r="X42">
-        <v>1.02</v>
-      </c>
-      <c r="Y42">
+      <c r="AD42">
         <v>1.29</v>
       </c>
-      <c r="Z42">
-        <v>3.04</v>
-      </c>
-      <c r="AA42">
-        <v>2.01</v>
-      </c>
-      <c r="AB42">
-        <v>1.75</v>
-      </c>
-      <c r="AC42">
-        <v>3.34</v>
-      </c>
-      <c r="AD42">
-        <v>1.24</v>
-      </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
         <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.91</v>
+        <v>1.88</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.17</v>
+        <v>3.81</v>
       </c>
       <c r="Q43">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
         <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AD43">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="O51">
         <v>3.3</v>
@@ -8655,13 +8655,13 @@
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AA51">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
         <v>1.8</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
+        <v>2.38</v>
+      </c>
+      <c r="S4">
+        <v>1.3</v>
+      </c>
+      <c r="T4">
+        <v>3.3</v>
+      </c>
+      <c r="U4">
+        <v>2.34</v>
+      </c>
+      <c r="V4">
+        <v>1.51</v>
+      </c>
+      <c r="W4">
+        <v>1.11</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.18</v>
+      </c>
+      <c r="Z4">
+        <v>4.4</v>
+      </c>
+      <c r="AA4">
+        <v>1.62</v>
+      </c>
+      <c r="AB4">
         <v>2.12</v>
       </c>
-      <c r="S4">
-        <v>1.25</v>
-      </c>
-      <c r="T4">
-        <v>2.94</v>
-      </c>
-      <c r="U4">
-        <v>2.38</v>
-      </c>
-      <c r="V4">
+      <c r="AC4">
+        <v>2.63</v>
+      </c>
+      <c r="AD4">
         <v>1.47</v>
       </c>
-      <c r="W4">
-        <v>1.12</v>
-      </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
+      <c r="AE4">
         <v>1.15</v>
       </c>
-      <c r="Z4">
-        <v>4.3</v>
-      </c>
-      <c r="AA4">
+      <c r="AF4">
         <v>1.6</v>
       </c>
-      <c r="AB4">
-        <v>2.15</v>
-      </c>
-      <c r="AC4">
-        <v>2.43</v>
-      </c>
-      <c r="AD4">
-        <v>1.44</v>
-      </c>
-      <c r="AE4">
-        <v>1.14</v>
-      </c>
-      <c r="AF4">
-        <v>1.62</v>
-      </c>
       <c r="AG4">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK4">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="P5">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="S5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="V5">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA5">
         <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AC5">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD5">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
         <v>4.33</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q10">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S10">
         <v>1.26</v>
@@ -1984,7 +1984,7 @@
         <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD10">
         <v>1.4</v>
@@ -1993,10 +1993,10 @@
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,28 +2105,28 @@
         <v>5.3</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P11">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q11">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R11">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S11">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T11">
         <v>3.84</v>
       </c>
       <c r="U11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V11">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W11">
         <v>1.15</v>
@@ -2150,7 +2150,7 @@
         <v>1.98</v>
       </c>
       <c r="AD11">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AE11">
         <v>1.29</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>4.03</v>
       </c>
       <c r="Q16">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S16">
         <v>1.29</v>
@@ -2938,7 +2938,7 @@
         <v>3.4</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
         <v>1.55</v>
@@ -2953,28 +2953,28 @@
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AC16">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AD16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q17">
-        <v>3.54</v>
+        <v>3.01</v>
       </c>
       <c r="R17">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="S17">
         <v>1.2</v>
@@ -3101,40 +3101,40 @@
         <v>3.9</v>
       </c>
       <c r="U17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V17">
         <v>1.67</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>5.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AC17">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG17">
         <v>2.7</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,16 +3252,16 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U18">
         <v>2.1</v>
@@ -3273,31 +3273,31 @@
         <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>5.05</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
         <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
         <v>2.1</v>
@@ -3316,7 +3316,7 @@
         <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>2.56</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
         <v>2.32</v>
@@ -3433,10 +3433,10 @@
         <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.25</v>
@@ -3451,10 +3451,10 @@
         <v>1.58</v>
       </c>
       <c r="AC19">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="O20">
         <v>3.2</v>
@@ -3578,13 +3578,13 @@
         <v>2.37</v>
       </c>
       <c r="Q20">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="R20">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T20">
         <v>2.58</v>
@@ -3596,37 +3596,37 @@
         <v>1.37</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD20">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF20">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="O21">
-        <v>4.04</v>
+        <v>4.4</v>
       </c>
       <c r="P21">
         <v>5.5</v>
       </c>
       <c r="Q21">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U21">
         <v>2.09</v>
       </c>
       <c r="V21">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AC21">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD21">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF21">
         <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="AA22">
         <v>2.05</v>
@@ -3940,7 +3940,7 @@
         <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
         <v>1.25</v>
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O23">
-        <v>3.09</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
+        <v>1.45</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.2</v>
+      </c>
+      <c r="Z23">
+        <v>4.33</v>
+      </c>
+      <c r="AA23">
+        <v>1.72</v>
+      </c>
+      <c r="AB23">
+        <v>2.05</v>
+      </c>
+      <c r="AC23">
+        <v>2.88</v>
+      </c>
+      <c r="AD23">
         <v>1.4</v>
       </c>
-      <c r="W23">
-        <v>1.07</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
+      <c r="AE23">
+        <v>1.14</v>
+      </c>
+      <c r="AF23">
+        <v>1.65</v>
+      </c>
+      <c r="AG23">
+        <v>2.2</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.22</v>
       </c>
-      <c r="Z23">
-        <v>3.5</v>
-      </c>
-      <c r="AA23">
-        <v>1.85</v>
-      </c>
-      <c r="AB23">
-        <v>1.92</v>
-      </c>
-      <c r="AC23">
-        <v>3.26</v>
-      </c>
-      <c r="AD23">
-        <v>1.32</v>
-      </c>
-      <c r="AE23">
-        <v>1.09</v>
-      </c>
-      <c r="AF23">
-        <v>1.62</v>
-      </c>
-      <c r="AG23">
-        <v>2.15</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.29</v>
-      </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.79</v>
+        <v>2.83</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="V24">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AA24">
         <v>1.72</v>
       </c>
       <c r="AB24">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC24">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.79</v>
+        <v>2.32</v>
       </c>
       <c r="O25">
+        <v>3.35</v>
+      </c>
+      <c r="P25">
+        <v>2.7</v>
+      </c>
+      <c r="Q25">
+        <v>2.71</v>
+      </c>
+      <c r="R25">
+        <v>2.2</v>
+      </c>
+      <c r="S25">
+        <v>1.29</v>
+      </c>
+      <c r="T25">
         <v>3.3</v>
       </c>
-      <c r="P25">
-        <v>2.18</v>
-      </c>
-      <c r="Q25">
-        <v>3.4</v>
-      </c>
-      <c r="R25">
-        <v>2.11</v>
-      </c>
-      <c r="S25">
-        <v>1.33</v>
-      </c>
-      <c r="T25">
-        <v>2.96</v>
-      </c>
       <c r="U25">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC25">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="O26">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q26">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S26">
+        <v>1.36</v>
+      </c>
+      <c r="T26">
+        <v>2.88</v>
+      </c>
+      <c r="U26">
+        <v>2.88</v>
+      </c>
+      <c r="V26">
+        <v>1.36</v>
+      </c>
+      <c r="W26">
+        <v>1.06</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
         <v>1.29</v>
       </c>
-      <c r="T26">
+      <c r="Z26">
+        <v>3.5</v>
+      </c>
+      <c r="AA26">
+        <v>1.92</v>
+      </c>
+      <c r="AB26">
+        <v>1.85</v>
+      </c>
+      <c r="AC26">
         <v>3.4</v>
       </c>
-      <c r="U26">
-        <v>2.3</v>
-      </c>
-      <c r="V26">
-        <v>1.55</v>
-      </c>
-      <c r="W26">
-        <v>1.12</v>
-      </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>1.15</v>
-      </c>
-      <c r="Z26">
-        <v>4.25</v>
-      </c>
-      <c r="AA26">
+      <c r="AD26">
+        <v>1.3</v>
+      </c>
+      <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
+        <v>1.73</v>
+      </c>
+      <c r="AG26">
+        <v>2.1</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.23</v>
+      </c>
+      <c r="AK26">
         <v>1.6</v>
-      </c>
-      <c r="AB26">
-        <v>2.3</v>
-      </c>
-      <c r="AC26">
-        <v>2.38</v>
-      </c>
-      <c r="AD26">
-        <v>1.46</v>
-      </c>
-      <c r="AE26">
-        <v>1.16</v>
-      </c>
-      <c r="AF26">
-        <v>1.64</v>
-      </c>
-      <c r="AG26">
-        <v>2.13</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.17</v>
-      </c>
-      <c r="AK26">
-        <v>2.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4728,10 +4728,10 @@
         <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U27">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V27">
         <v>1.55</v>
@@ -4743,31 +4743,31 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA27">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD27">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.24</v>
+        <v>2.83</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC28">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="P29">
-        <v>2.42</v>
+        <v>4.45</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AC29">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AD29">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF29">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O30">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
         <v>3.1</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC30">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
         <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
         <v>2</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="O31">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="Q31">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="R31">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.04</v>
       </c>
       <c r="Y31">
+        <v>1.27</v>
+      </c>
+      <c r="Z31">
+        <v>3.63</v>
+      </c>
+      <c r="AA31">
+        <v>1.83</v>
+      </c>
+      <c r="AB31">
+        <v>1.93</v>
+      </c>
+      <c r="AC31">
+        <v>3.28</v>
+      </c>
+      <c r="AD31">
         <v>1.32</v>
       </c>
-      <c r="Z31">
-        <v>3.24</v>
-      </c>
-      <c r="AA31">
-        <v>2</v>
-      </c>
-      <c r="AB31">
-        <v>1.76</v>
-      </c>
-      <c r="AC31">
-        <v>3.6</v>
-      </c>
-      <c r="AD31">
+      <c r="AE31">
+        <v>1.13</v>
+      </c>
+      <c r="AF31">
+        <v>1.65</v>
+      </c>
+      <c r="AG31">
+        <v>2.2</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.24</v>
       </c>
-      <c r="AE31">
-        <v>1.06</v>
-      </c>
-      <c r="AF31">
-        <v>1.76</v>
-      </c>
-      <c r="AG31">
-        <v>1.96</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.28</v>
-      </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O32">
         <v>4.1</v>
@@ -5534,40 +5534,40 @@
         <v>5.25</v>
       </c>
       <c r="Q32">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R32">
         <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5576,13 +5576,13 @@
         <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
         <v>2.3</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,49 +6340,49 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.13</v>
+        <v>2.83</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="P37">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="Q37">
-        <v>2.54</v>
+        <v>3.21</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="U37">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC37">
         <v>2.88</v>
@@ -6391,13 +6391,13 @@
         <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,37 +6503,37 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="O38">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>2.12</v>
+        <v>3.81</v>
       </c>
       <c r="Q38">
-        <v>3.21</v>
+        <v>2.35</v>
       </c>
       <c r="R38">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
@@ -6542,25 +6542,25 @@
         <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC38">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE38">
         <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="O39">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="Q39">
-        <v>2.94</v>
+        <v>3.47</v>
       </c>
       <c r="R39">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB39">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="P40">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q40">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="R40">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AB40">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="P41">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q41">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="R41">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7025,16 +7025,16 @@
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC41">
         <v>3.1</v>
@@ -7043,7 +7043,7 @@
         <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
         <v>1.67</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.46</v>
+        <v>2.13</v>
       </c>
       <c r="O42">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="Q42">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
+        <v>3.3</v>
+      </c>
+      <c r="U42">
+        <v>2.35</v>
+      </c>
+      <c r="V42">
+        <v>1.5</v>
+      </c>
+      <c r="W42">
+        <v>1.08</v>
+      </c>
+      <c r="X42">
+        <v>1.02</v>
+      </c>
+      <c r="Y42">
+        <v>1.2</v>
+      </c>
+      <c r="Z42">
+        <v>4.33</v>
+      </c>
+      <c r="AA42">
+        <v>1.67</v>
+      </c>
+      <c r="AB42">
+        <v>2.1</v>
+      </c>
+      <c r="AC42">
         <v>2.88</v>
       </c>
-      <c r="U42">
-        <v>2.88</v>
-      </c>
-      <c r="V42">
-        <v>1.36</v>
-      </c>
-      <c r="W42">
-        <v>1.05</v>
-      </c>
-      <c r="X42">
-        <v>1.05</v>
-      </c>
-      <c r="Y42">
-        <v>1.3</v>
-      </c>
-      <c r="Z42">
-        <v>3.4</v>
-      </c>
-      <c r="AA42">
-        <v>2</v>
-      </c>
-      <c r="AB42">
-        <v>1.8</v>
-      </c>
-      <c r="AC42">
-        <v>3.5</v>
-      </c>
       <c r="AD42">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="O43">
         <v>3.3</v>
       </c>
       <c r="P43">
-        <v>3.81</v>
+        <v>2.25</v>
       </c>
       <c r="Q43">
-        <v>2.35</v>
+        <v>3.11</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T43">
         <v>3.2</v>
@@ -7345,7 +7345,7 @@
         <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.04</v>
@@ -7354,28 +7354,28 @@
         <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
         <v>3.3</v>
@@ -8631,52 +8631,52 @@
         <v>2.4</v>
       </c>
       <c r="Q51">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S51">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA51">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC51">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD51">
         <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
         <v>2</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8815,34 +8815,34 @@
         <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB52">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC52">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD52">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
         <v>1.87</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1613,58 +1613,58 @@
         </is>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>7.39</v>
       </c>
       <c r="O8">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q8">
         <v>7.8</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U8">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
         <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z8">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA8">
         <v>2.2</v>
       </c>
       <c r="AB8">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC8">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="AD8">
         <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
         <v>2.45</v>
@@ -1779,16 +1779,16 @@
         <v>2.31</v>
       </c>
       <c r="O9">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
       </c>
       <c r="R9">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S9">
         <v>1.5</v>
@@ -1809,22 +1809,22 @@
         <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z9">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AA9">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AB9">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AC9">
         <v>4.95</v>
       </c>
       <c r="AD9">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
@@ -1833,7 +1833,7 @@
         <v>2.11</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="O10">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="P10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q10">
         <v>1.93</v>
       </c>
       <c r="R10">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="S10">
         <v>1.26</v>
@@ -2012,7 +2012,7 @@
         <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P11">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q11">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="R11">
         <v>2.46</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O12">
+        <v>4.3</v>
+      </c>
+      <c r="P12">
         <v>4.05</v>
       </c>
-      <c r="P12">
-        <v>4.2</v>
-      </c>
       <c r="Q12">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R12">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
         <v>3.64</v>
@@ -2292,37 +2292,37 @@
         <v>1.61</v>
       </c>
       <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
         <v>1.14</v>
       </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.17</v>
-      </c>
       <c r="Z12">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB12">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC12">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,55 +2428,55 @@
         </is>
       </c>
       <c r="N13">
-        <v>8.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O13">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="P13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>5.61</v>
       </c>
       <c r="R13">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T13">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="U13">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V13">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z13">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB13">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="AC13">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE13">
         <v>1.33</v>
@@ -2485,7 +2485,7 @@
         <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK13">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD14">
         <v>1.22</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O15">
         <v>3.05</v>
       </c>
       <c r="P15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
         <v>3.5</v>
@@ -2784,28 +2784,28 @@
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB15">
         <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
         <v>1.9</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.47</v>
       </c>
       <c r="P16">
         <v>4.03</v>
       </c>
       <c r="Q16">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R16">
         <v>2.32</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
         <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P17">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q17">
         <v>3.01</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="Q18">
         <v>1.88</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O19">
         <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
         <v>2.56</v>
@@ -3575,58 +3575,58 @@
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S20">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T20">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="U20">
         <v>2.76</v>
       </c>
       <c r="V20">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
+        <v>1.04</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.3</v>
+      </c>
+      <c r="AA20">
+        <v>1.96</v>
+      </c>
+      <c r="AB20">
+        <v>1.85</v>
+      </c>
+      <c r="AC20">
+        <v>3.2</v>
+      </c>
+      <c r="AD20">
+        <v>1.3</v>
+      </c>
+      <c r="AE20">
         <v>1.06</v>
       </c>
-      <c r="X20">
-        <v>1.05</v>
-      </c>
-      <c r="Y20">
-        <v>1.3</v>
-      </c>
-      <c r="Z20">
-        <v>3.4</v>
-      </c>
-      <c r="AA20">
-        <v>2</v>
-      </c>
-      <c r="AB20">
-        <v>1.8</v>
-      </c>
-      <c r="AC20">
-        <v>3.5</v>
-      </c>
-      <c r="AD20">
-        <v>1.29</v>
-      </c>
-      <c r="AE20">
-        <v>1.08</v>
-      </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         <v>4.4</v>
       </c>
       <c r="P21">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="Q21">
         <v>1.93</v>
       </c>
       <c r="R21">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
         <v>1.2</v>
@@ -3780,16 +3780,16 @@
         <v>2.25</v>
       </c>
       <c r="AD21">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE21">
         <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG21">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3934,10 +3934,10 @@
         <v>3.25</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC22">
         <v>3.8</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,58 +4058,58 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q23">
-        <v>3.18</v>
+        <v>2.08</v>
       </c>
       <c r="R23">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S23">
         <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
         <v>1.65</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="Q24">
-        <v>2.83</v>
+        <v>3.35</v>
       </c>
       <c r="R24">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>4.1</v>
+        <v>3.63</v>
       </c>
       <c r="AA24">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB24">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD24">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S25">
+        <v>1.36</v>
+      </c>
+      <c r="T25">
+        <v>2.84</v>
+      </c>
+      <c r="U25">
+        <v>2.88</v>
+      </c>
+      <c r="V25">
+        <v>1.36</v>
+      </c>
+      <c r="W25">
+        <v>1.05</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>1.33</v>
+      </c>
+      <c r="Z25">
+        <v>3.25</v>
+      </c>
+      <c r="AA25">
+        <v>2.02</v>
+      </c>
+      <c r="AB25">
+        <v>1.74</v>
+      </c>
+      <c r="AC25">
+        <v>3.6</v>
+      </c>
+      <c r="AD25">
         <v>1.29</v>
       </c>
-      <c r="T25">
-        <v>3.3</v>
-      </c>
-      <c r="U25">
-        <v>2.6</v>
-      </c>
-      <c r="V25">
-        <v>1.44</v>
-      </c>
-      <c r="W25">
-        <v>1.07</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.22</v>
-      </c>
-      <c r="Z25">
-        <v>4.1</v>
-      </c>
-      <c r="AA25">
-        <v>1.75</v>
-      </c>
-      <c r="AB25">
-        <v>2.01</v>
-      </c>
-      <c r="AC25">
-        <v>2.88</v>
-      </c>
-      <c r="AD25">
-        <v>1.4</v>
-      </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O26">
+        <v>3.3</v>
+      </c>
+      <c r="P26">
+        <v>2.15</v>
+      </c>
+      <c r="Q26">
         <v>3.25</v>
       </c>
-      <c r="P26">
-        <v>3.3</v>
-      </c>
-      <c r="Q26">
-        <v>2.51</v>
-      </c>
       <c r="R26">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
         <v>1.36</v>
       </c>
       <c r="T26">
+        <v>3.3</v>
+      </c>
+      <c r="U26">
+        <v>2.55</v>
+      </c>
+      <c r="V26">
+        <v>1.46</v>
+      </c>
+      <c r="W26">
+        <v>1.08</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.22</v>
+      </c>
+      <c r="Z26">
+        <v>4.2</v>
+      </c>
+      <c r="AA26">
+        <v>1.8</v>
+      </c>
+      <c r="AB26">
+        <v>1.96</v>
+      </c>
+      <c r="AC26">
         <v>2.88</v>
       </c>
-      <c r="U26">
-        <v>2.88</v>
-      </c>
-      <c r="V26">
-        <v>1.36</v>
-      </c>
-      <c r="W26">
-        <v>1.06</v>
-      </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
-      <c r="Y26">
-        <v>1.29</v>
-      </c>
-      <c r="Z26">
-        <v>3.5</v>
-      </c>
-      <c r="AA26">
-        <v>1.92</v>
-      </c>
-      <c r="AB26">
-        <v>1.85</v>
-      </c>
-      <c r="AC26">
-        <v>3.4</v>
-      </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AK26">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,58 +4710,58 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.67</v>
+        <v>3.14</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
         <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA27">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AB27">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
         <v>1.65</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.83</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
         <v>1.29</v>
@@ -4894,13 +4894,13 @@
         <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.03</v>
@@ -4909,13 +4909,13 @@
         <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC28">
         <v>2.88</v>
@@ -4924,13 +4924,13 @@
         <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="R29">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
+        <v>1.71</v>
+      </c>
+      <c r="AB29">
+        <v>2.15</v>
+      </c>
+      <c r="AC29">
+        <v>2.7</v>
+      </c>
+      <c r="AD29">
+        <v>1.42</v>
+      </c>
+      <c r="AE29">
+        <v>1.14</v>
+      </c>
+      <c r="AF29">
         <v>1.57</v>
       </c>
-      <c r="AB29">
+      <c r="AG29">
         <v>2.38</v>
       </c>
-      <c r="AC29">
-        <v>2.55</v>
-      </c>
-      <c r="AD29">
-        <v>1.5</v>
-      </c>
-      <c r="AE29">
-        <v>1.2</v>
-      </c>
-      <c r="AF29">
-        <v>1.65</v>
-      </c>
-      <c r="AG29">
-        <v>2.2</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK29">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="Q30">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R30">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
         <v>2.88</v>
@@ -5226,37 +5226,37 @@
         <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB30">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AC30">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,58 +5362,58 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="P31">
+        <v>4.65</v>
+      </c>
+      <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
         <v>2.4</v>
       </c>
-      <c r="Q31">
-        <v>3.35</v>
-      </c>
-      <c r="R31">
-        <v>2.09</v>
-      </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U31">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>3.63</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AC31">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
         <v>1.65</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="O32">
         <v>4.1</v>
@@ -5537,7 +5537,7 @@
         <v>2</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5555,7 +5555,7 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
@@ -5564,10 +5564,10 @@
         <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5579,10 +5579,10 @@
         <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
         <v>2.4</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
         <v>4.4</v>
       </c>
       <c r="P34">
-        <v>4.92</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
         <v>1.97</v>
@@ -5872,7 +5872,7 @@
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V34">
         <v>1.65</v>
@@ -5896,7 +5896,7 @@
         <v>2.7</v>
       </c>
       <c r="AC34">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AD34">
         <v>1.67</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK34">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="O35">
         <v>4.25</v>
@@ -6023,10 +6023,10 @@
         <v>4.9</v>
       </c>
       <c r="Q35">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="R35">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S35">
         <v>1.17</v>
@@ -6053,7 +6053,7 @@
         <v>6.5</v>
       </c>
       <c r="AA35">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
         <v>2.87</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK35">
         <v>2.33</v>
@@ -6180,10 +6180,10 @@
         <v>4</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,77 +6340,77 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="O37">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="P37">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q37">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="R37">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S37">
+        <v>1.36</v>
+      </c>
+      <c r="T37">
+        <v>2.88</v>
+      </c>
+      <c r="U37">
+        <v>2.88</v>
+      </c>
+      <c r="V37">
+        <v>1.36</v>
+      </c>
+      <c r="W37">
+        <v>1.05</v>
+      </c>
+      <c r="X37">
+        <v>1.05</v>
+      </c>
+      <c r="Y37">
+        <v>1.3</v>
+      </c>
+      <c r="Z37">
+        <v>3.4</v>
+      </c>
+      <c r="AA37">
+        <v>2</v>
+      </c>
+      <c r="AB37">
+        <v>1.8</v>
+      </c>
+      <c r="AC37">
+        <v>3.5</v>
+      </c>
+      <c r="AD37">
         <v>1.29</v>
       </c>
-      <c r="T37">
-        <v>2.83</v>
-      </c>
-      <c r="U37">
-        <v>2.55</v>
-      </c>
-      <c r="V37">
-        <v>1.45</v>
-      </c>
-      <c r="W37">
-        <v>1.07</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.22</v>
-      </c>
-      <c r="Z37">
-        <v>4.1</v>
-      </c>
-      <c r="AA37">
-        <v>1.78</v>
-      </c>
-      <c r="AB37">
-        <v>1.98</v>
-      </c>
-      <c r="AC37">
-        <v>2.88</v>
-      </c>
-      <c r="AD37">
-        <v>1.4</v>
-      </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
+        <v>1.8</v>
+      </c>
+      <c r="AG37">
+        <v>2</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.65</v>
-      </c>
-      <c r="AG37">
-        <v>2.2</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.25</v>
       </c>
       <c r="AK37">
         <v>1.25</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,22 +6503,22 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="P38">
-        <v>3.81</v>
+        <v>2.3</v>
       </c>
       <c r="Q38">
-        <v>2.35</v>
+        <v>3.11</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T38">
         <v>3.2</v>
@@ -6530,7 +6530,7 @@
         <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.04</v>
@@ -6539,28 +6539,28 @@
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA38">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC38">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
         <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,65 +6666,65 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="P39">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="Q39">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="R39">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>4.5</v>
+        <v>4.09</v>
       </c>
       <c r="AA39">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AB39">
+        <v>1.98</v>
+      </c>
+      <c r="AC39">
+        <v>2.88</v>
+      </c>
+      <c r="AD39">
+        <v>1.4</v>
+      </c>
+      <c r="AE39">
+        <v>1.13</v>
+      </c>
+      <c r="AF39">
+        <v>1.65</v>
+      </c>
+      <c r="AG39">
         <v>2.2</v>
       </c>
-      <c r="AC39">
-        <v>2.63</v>
-      </c>
-      <c r="AD39">
-        <v>1.47</v>
-      </c>
-      <c r="AE39">
-        <v>1.2</v>
-      </c>
-      <c r="AF39">
-        <v>1.6</v>
-      </c>
-      <c r="AG39">
-        <v>2.3</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="O40">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q40">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB40">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD40">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         <v>3.75</v>
       </c>
       <c r="P42">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="Q42">
         <v>2.54</v>
@@ -7194,13 +7194,13 @@
         <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
         <v>1.4</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="O43">
         <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.25</v>
+        <v>3.81</v>
       </c>
       <c r="Q43">
-        <v>3.11</v>
+        <v>2.35</v>
       </c>
       <c r="R43">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
         <v>3.2</v>
@@ -7345,7 +7345,7 @@
         <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.04</v>
@@ -7354,28 +7354,28 @@
         <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD43">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O44">
         <v>4.5</v>
       </c>
       <c r="P44">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q44">
         <v>2.05</v>
       </c>
       <c r="R44">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T44">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U44">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="V44">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W44">
         <v>1.19</v>
@@ -7517,28 +7517,28 @@
         <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA44">
         <v>1.46</v>
       </c>
       <c r="AB44">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AC44">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD44">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE44">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
         <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,28 +7647,28 @@
         <v>2.4</v>
       </c>
       <c r="O45">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P45">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q45">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="S45">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T45">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="U45">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V45">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="W45">
         <v>1.36</v>
@@ -7677,31 +7677,31 @@
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z45">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA45">
         <v>1.2</v>
       </c>
       <c r="AB45">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AC45">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AD45">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AE45">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF45">
         <v>1.18</v>
       </c>
       <c r="AG45">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="O46">
-        <v>9.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="P46">
-        <v>27</v>
+        <v>22.61</v>
       </c>
       <c r="Q46">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="R46">
-        <v>3.62</v>
+        <v>3.49</v>
       </c>
       <c r="S46">
         <v>1.14</v>
       </c>
       <c r="T46">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="U46">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V46">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="W46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z46">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="AA46">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB46">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AC46">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AD46">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AE46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF46">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AG46">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AK46">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,43 +7970,43 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="O47">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="P47">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q47">
         <v>3.5</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="S47">
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V47">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA47">
         <v>1.49</v>
@@ -8015,10 +8015,10 @@
         <v>2.4</v>
       </c>
       <c r="AC47">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AD47">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE47">
         <v>1.22</v>
@@ -8027,7 +8027,7 @@
         <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O48">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="P48">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Q48">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R48">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="S48">
         <v>1.15</v>
       </c>
       <c r="T48">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="U48">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V48">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="W48">
         <v>1.25</v>
@@ -8166,10 +8166,10 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z48">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA48">
         <v>1.3</v>
@@ -8178,19 +8178,19 @@
         <v>3.5</v>
       </c>
       <c r="AC48">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD48">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE48">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF48">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.03</v>
       </c>
       <c r="AK48">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,28 +8299,28 @@
         <v>1.5</v>
       </c>
       <c r="O49">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="P49">
-        <v>6.25</v>
+        <v>5.96</v>
       </c>
       <c r="Q49">
         <v>1.96</v>
       </c>
       <c r="R49">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="S49">
         <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="U49">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V49">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W49">
         <v>1.14</v>
@@ -8329,31 +8329,31 @@
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA49">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB49">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC49">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD49">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AE49">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK49">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O50">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T50">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V50">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>4.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
+        <v>1.5</v>
+      </c>
+      <c r="AB50">
+        <v>2.66</v>
+      </c>
+      <c r="AC50">
+        <v>2.3</v>
+      </c>
+      <c r="AD50">
         <v>1.57</v>
       </c>
-      <c r="AB50">
-        <v>2.33</v>
-      </c>
-      <c r="AC50">
-        <v>2.4</v>
-      </c>
-      <c r="AD50">
-        <v>1.56</v>
-      </c>
       <c r="AE50">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF50">
         <v>1.56</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8625,10 +8625,10 @@
         <v>2.9</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q51">
         <v>3.13</v>
@@ -8640,7 +8640,7 @@
         <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U51">
         <v>2.88</v>
@@ -8791,7 +8791,7 @@
         <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -8821,13 +8821,13 @@
         <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="AA52">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AB52">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC52">
         <v>4.2</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="O2">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O4">
         <v>3.5</v>
@@ -1006,7 +1006,7 @@
         <v>2.12</v>
       </c>
       <c r="AC4">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD4">
         <v>1.47</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK4">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="O5">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="P5">
-        <v>9.199999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q5">
         <v>1.5</v>
       </c>
       <c r="R5">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="S5">
         <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U5">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AC5">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AD5">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>2.3</v>
       </c>
       <c r="AB7">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC7">
         <v>4.15</v>
@@ -1625,13 +1625,13 @@
         <v>7.8</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
         <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="U8">
         <v>3.35</v>
@@ -1643,7 +1643,7 @@
         <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
         <v>1.44</v>
@@ -1652,22 +1652,22 @@
         <v>2.75</v>
       </c>
       <c r="AA8">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC8">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="AD8">
         <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AG8">
         <v>1.53</v>
@@ -1686,7 +1686,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
         <v>2.87</v>
@@ -1785,13 +1785,13 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T9">
         <v>2.21</v>
@@ -1803,19 +1803,19 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z9">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AA9">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AB9">
         <v>1.45</v>
@@ -1824,16 +1824,16 @@
         <v>4.95</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,13 +1945,13 @@
         <v>4.25</v>
       </c>
       <c r="P10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>1.93</v>
       </c>
       <c r="R10">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="S10">
         <v>1.26</v>
@@ -1972,19 +1972,19 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA10">
         <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD10">
         <v>1.4</v>
@@ -1993,10 +1993,10 @@
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O11">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="P11">
         <v>1.5</v>
       </c>
       <c r="Q11">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="R11">
         <v>2.46</v>
@@ -2123,7 +2123,7 @@
         <v>3.84</v>
       </c>
       <c r="U11">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
         <v>1.67</v>
@@ -2144,16 +2144,16 @@
         <v>1.4</v>
       </c>
       <c r="AB11">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AC11">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AD11">
         <v>1.76</v>
       </c>
       <c r="AE11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF11">
         <v>1.5</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
         <v>1.08</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P14">
         <v>1.5</v>
@@ -2609,13 +2609,13 @@
         <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
         <v>1.03</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="O16">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="P16">
         <v>4.03</v>
@@ -2971,7 +2971,7 @@
         <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
         <v>2.3</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.75</v>
+        <v>1.37</v>
       </c>
       <c r="O17">
-        <v>3.85</v>
+        <v>5.19</v>
       </c>
       <c r="P17">
-        <v>1.99</v>
+        <v>6.72</v>
       </c>
       <c r="Q17">
-        <v>3.01</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S17">
         <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
+        <v>1.13</v>
+      </c>
+      <c r="Z17">
+        <v>5.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.47</v>
+      </c>
+      <c r="AB17">
+        <v>2.5</v>
+      </c>
+      <c r="AC17">
+        <v>2.14</v>
+      </c>
+      <c r="AD17">
+        <v>1.6</v>
+      </c>
+      <c r="AE17">
+        <v>1.22</v>
+      </c>
+      <c r="AF17">
+        <v>1.65</v>
+      </c>
+      <c r="AG17">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.1</v>
       </c>
-      <c r="Z17">
-        <v>6.5</v>
-      </c>
-      <c r="AA17">
-        <v>1.4</v>
-      </c>
-      <c r="AB17">
-        <v>2.88</v>
-      </c>
-      <c r="AC17">
-        <v>2.1</v>
-      </c>
-      <c r="AD17">
-        <v>1.73</v>
-      </c>
-      <c r="AE17">
-        <v>1.3</v>
-      </c>
-      <c r="AF17">
-        <v>1.4</v>
-      </c>
-      <c r="AG17">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.18</v>
-      </c>
       <c r="AK17">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.37</v>
+        <v>2.73</v>
       </c>
       <c r="O18">
-        <v>5.19</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>6.72</v>
+        <v>2.05</v>
       </c>
       <c r="Q18">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="S18">
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC18">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE18">
         <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>2.58</v>
+        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O19">
         <v>3.3</v>
@@ -3421,10 +3421,10 @@
         <v>2.17</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
         <v>2.32</v>
@@ -3735,16 +3735,16 @@
         <v>1.53</v>
       </c>
       <c r="O21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P21">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="Q21">
         <v>1.93</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="S21">
         <v>1.2</v>
@@ -3777,7 +3777,7 @@
         <v>2.63</v>
       </c>
       <c r="AC21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
         <v>1.61</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
-        <v>2.08</v>
+        <v>2.51</v>
       </c>
       <c r="R23">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z23">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
+        <v>1.92</v>
+      </c>
+      <c r="AB23">
+        <v>1.84</v>
+      </c>
+      <c r="AC23">
+        <v>3.4</v>
+      </c>
+      <c r="AD23">
+        <v>1.3</v>
+      </c>
+      <c r="AE23">
+        <v>1.1</v>
+      </c>
+      <c r="AF23">
+        <v>1.73</v>
+      </c>
+      <c r="AG23">
+        <v>2.1</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.23</v>
+      </c>
+      <c r="AK23">
         <v>1.6</v>
-      </c>
-      <c r="AB23">
-        <v>2.3</v>
-      </c>
-      <c r="AC23">
-        <v>2.63</v>
-      </c>
-      <c r="AD23">
-        <v>1.47</v>
-      </c>
-      <c r="AE23">
-        <v>1.2</v>
-      </c>
-      <c r="AF23">
-        <v>1.65</v>
-      </c>
-      <c r="AG23">
-        <v>2.2</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.17</v>
-      </c>
-      <c r="AK23">
-        <v>1.97</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="R24">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.11</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.2</v>
+      </c>
+      <c r="Z24">
+        <v>4.1</v>
+      </c>
+      <c r="AA24">
+        <v>1.71</v>
+      </c>
+      <c r="AB24">
+        <v>2.15</v>
+      </c>
+      <c r="AC24">
+        <v>2.7</v>
+      </c>
+      <c r="AD24">
+        <v>1.42</v>
+      </c>
+      <c r="AE24">
+        <v>1.14</v>
+      </c>
+      <c r="AF24">
+        <v>1.57</v>
+      </c>
+      <c r="AG24">
+        <v>2.38</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.4</v>
       </c>
-      <c r="W24">
-        <v>1.07</v>
-      </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>1.27</v>
-      </c>
-      <c r="Z24">
-        <v>3.63</v>
-      </c>
-      <c r="AA24">
-        <v>1.83</v>
-      </c>
-      <c r="AB24">
-        <v>1.93</v>
-      </c>
-      <c r="AC24">
-        <v>3.28</v>
-      </c>
-      <c r="AD24">
-        <v>1.32</v>
-      </c>
-      <c r="AE24">
-        <v>1.13</v>
-      </c>
-      <c r="AF24">
-        <v>1.65</v>
-      </c>
-      <c r="AG24">
-        <v>2.2</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.24</v>
-      </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
+        <v>2.15</v>
+      </c>
+      <c r="Q25">
+        <v>3.3</v>
+      </c>
+      <c r="R25">
+        <v>2.2</v>
+      </c>
+      <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>3.2</v>
+      </c>
+      <c r="U25">
+        <v>2.6</v>
+      </c>
+      <c r="V25">
+        <v>1.45</v>
+      </c>
+      <c r="W25">
+        <v>1.07</v>
+      </c>
+      <c r="X25">
+        <v>1.03</v>
+      </c>
+      <c r="Y25">
+        <v>1.22</v>
+      </c>
+      <c r="Z25">
+        <v>4.1</v>
+      </c>
+      <c r="AA25">
+        <v>1.8</v>
+      </c>
+      <c r="AB25">
+        <v>1.9</v>
+      </c>
+      <c r="AC25">
         <v>3.1</v>
       </c>
-      <c r="Q25">
-        <v>2.65</v>
-      </c>
-      <c r="R25">
-        <v>2.01</v>
-      </c>
-      <c r="S25">
+      <c r="AD25">
         <v>1.36</v>
       </c>
-      <c r="T25">
-        <v>2.84</v>
-      </c>
-      <c r="U25">
-        <v>2.88</v>
-      </c>
-      <c r="V25">
-        <v>1.36</v>
-      </c>
-      <c r="W25">
-        <v>1.05</v>
-      </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>1.33</v>
-      </c>
-      <c r="Z25">
-        <v>3.25</v>
-      </c>
-      <c r="AA25">
-        <v>2.02</v>
-      </c>
-      <c r="AB25">
-        <v>1.74</v>
-      </c>
-      <c r="AC25">
-        <v>3.6</v>
-      </c>
-      <c r="AD25">
-        <v>1.29</v>
-      </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q26">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
         <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.14</v>
+        <v>1.73</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q27">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z27">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA27">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.32</v>
+        <v>3.14</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S28">
         <v>1.29</v>
@@ -4894,28 +4894,28 @@
         <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
         <v>2.88</v>
@@ -4924,7 +4924,7 @@
         <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
         <v>1.65</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q29">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="R29">
         <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA29">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB29">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC29">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG29">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK29">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="R30">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA30">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="AC30">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>2.19</v>
       </c>
       <c r="O31">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q31">
+        <v>2.65</v>
+      </c>
+      <c r="R31">
+        <v>2.01</v>
+      </c>
+      <c r="S31">
+        <v>1.36</v>
+      </c>
+      <c r="T31">
+        <v>2.8</v>
+      </c>
+      <c r="U31">
+        <v>2.88</v>
+      </c>
+      <c r="V31">
+        <v>1.38</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
+        <v>3.25</v>
+      </c>
+      <c r="AA31">
+        <v>1.97</v>
+      </c>
+      <c r="AB31">
+        <v>1.74</v>
+      </c>
+      <c r="AC31">
+        <v>3.6</v>
+      </c>
+      <c r="AD31">
+        <v>1.26</v>
+      </c>
+      <c r="AE31">
+        <v>1.06</v>
+      </c>
+      <c r="AF31">
+        <v>1.8</v>
+      </c>
+      <c r="AG31">
         <v>2</v>
       </c>
-      <c r="R31">
-        <v>2.4</v>
-      </c>
-      <c r="S31">
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.25</v>
       </c>
-      <c r="T31">
-        <v>3.6</v>
-      </c>
-      <c r="U31">
-        <v>2.25</v>
-      </c>
-      <c r="V31">
-        <v>1.55</v>
-      </c>
-      <c r="W31">
-        <v>1.11</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.17</v>
-      </c>
-      <c r="Z31">
-        <v>5</v>
-      </c>
-      <c r="AA31">
-        <v>1.57</v>
-      </c>
-      <c r="AB31">
-        <v>2.38</v>
-      </c>
-      <c r="AC31">
-        <v>2.55</v>
-      </c>
-      <c r="AD31">
+      <c r="AK31">
         <v>1.5</v>
-      </c>
-      <c r="AE31">
-        <v>1.2</v>
-      </c>
-      <c r="AF31">
-        <v>1.65</v>
-      </c>
-      <c r="AG31">
-        <v>2.2</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.17</v>
-      </c>
-      <c r="AK31">
-        <v>2.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>5.25</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5552,16 +5552,16 @@
         <v>1.45</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA32">
         <v>1.74</v>
@@ -5576,13 +5576,13 @@
         <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="P33">
         <v>2.4</v>
@@ -5703,10 +5703,10 @@
         <v>2.28</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
         <v>2.25</v>
@@ -5727,25 +5727,25 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AD33">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF33">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>1.6</v>
       </c>
       <c r="O34">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P34">
         <v>4.6</v>
@@ -5872,7 +5872,7 @@
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V34">
         <v>1.65</v>
@@ -5890,13 +5890,13 @@
         <v>6.5</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB34">
         <v>2.7</v>
       </c>
       <c r="AC34">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD34">
         <v>1.67</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
         <v>4.9</v>
@@ -6053,10 +6053,10 @@
         <v>6.5</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC35">
         <v>2</v>
@@ -6207,34 +6207,34 @@
         <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA36">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC36">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD36">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2.02</v>
+        <v>3.68</v>
       </c>
       <c r="Q37">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.28</v>
+      </c>
+      <c r="Z37">
+        <v>3.42</v>
+      </c>
+      <c r="AA37">
+        <v>1.8</v>
+      </c>
+      <c r="AB37">
+        <v>1.9</v>
+      </c>
+      <c r="AC37">
+        <v>2.97</v>
+      </c>
+      <c r="AD37">
         <v>1.3</v>
-      </c>
-      <c r="Z37">
-        <v>3.4</v>
-      </c>
-      <c r="AA37">
-        <v>2</v>
-      </c>
-      <c r="AB37">
-        <v>1.8</v>
-      </c>
-      <c r="AC37">
-        <v>3.5</v>
-      </c>
-      <c r="AD37">
-        <v>1.29</v>
       </c>
       <c r="AE37">
         <v>1.08</v>
       </c>
       <c r="AF37">
+        <v>1.7</v>
+      </c>
+      <c r="AG37">
+        <v>2.04</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.27</v>
+      </c>
+      <c r="AK37">
         <v>1.8</v>
-      </c>
-      <c r="AG37">
-        <v>2</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.65</v>
-      </c>
-      <c r="AK37">
-        <v>1.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="O38">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="Q38">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="R38">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S38">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
         <v>1.07</v>
@@ -6536,16 +6536,16 @@
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB38">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC38">
         <v>3.1</v>
@@ -6554,7 +6554,7 @@
         <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.67</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.73</v>
+        <v>2.26</v>
       </c>
       <c r="O39">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q39">
-        <v>3.41</v>
+        <v>2.54</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="V39">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>4.09</v>
+        <v>3.6</v>
       </c>
       <c r="AA39">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB39">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC39">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AD39">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,65 +6829,65 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P40">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="Q40">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="R40">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA40">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AB40">
+        <v>1.98</v>
+      </c>
+      <c r="AC40">
+        <v>2.77</v>
+      </c>
+      <c r="AD40">
+        <v>1.36</v>
+      </c>
+      <c r="AE40">
+        <v>1.1</v>
+      </c>
+      <c r="AF40">
+        <v>1.65</v>
+      </c>
+      <c r="AG40">
         <v>2.2</v>
       </c>
-      <c r="AC40">
-        <v>2.63</v>
-      </c>
-      <c r="AD40">
-        <v>1.47</v>
-      </c>
-      <c r="AE40">
-        <v>1.2</v>
-      </c>
-      <c r="AF40">
-        <v>1.6</v>
-      </c>
-      <c r="AG40">
-        <v>2.3</v>
-      </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>3.7</v>
+      </c>
+      <c r="O41">
+        <v>3.7</v>
+      </c>
+      <c r="P41">
+        <v>1.82</v>
+      </c>
+      <c r="Q41">
+        <v>3.75</v>
+      </c>
+      <c r="R41">
+        <v>2.3</v>
+      </c>
+      <c r="S41">
+        <v>1.29</v>
+      </c>
+      <c r="T41">
+        <v>3.18</v>
+      </c>
+      <c r="U41">
         <v>2.42</v>
       </c>
-      <c r="O41">
-        <v>3.43</v>
-      </c>
-      <c r="P41">
-        <v>2.38</v>
-      </c>
-      <c r="Q41">
-        <v>2.94</v>
-      </c>
-      <c r="R41">
-        <v>2.04</v>
-      </c>
-      <c r="S41">
-        <v>1.33</v>
-      </c>
-      <c r="T41">
-        <v>3</v>
-      </c>
-      <c r="U41">
-        <v>2.75</v>
-      </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AB41">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AC41">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P42">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q42">
-        <v>2.54</v>
+        <v>3.11</v>
       </c>
       <c r="R42">
+        <v>2.06</v>
+      </c>
+      <c r="S42">
+        <v>1.37</v>
+      </c>
+      <c r="T42">
+        <v>3.2</v>
+      </c>
+      <c r="U42">
+        <v>2.6</v>
+      </c>
+      <c r="V42">
+        <v>1.44</v>
+      </c>
+      <c r="W42">
+        <v>1.07</v>
+      </c>
+      <c r="X42">
+        <v>1.03</v>
+      </c>
+      <c r="Y42">
+        <v>1.22</v>
+      </c>
+      <c r="Z42">
+        <v>3.3</v>
+      </c>
+      <c r="AA42">
+        <v>1.83</v>
+      </c>
+      <c r="AB42">
+        <v>1.93</v>
+      </c>
+      <c r="AC42">
+        <v>3.1</v>
+      </c>
+      <c r="AD42">
+        <v>1.36</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
+        <v>1.65</v>
+      </c>
+      <c r="AG42">
         <v>2.2</v>
       </c>
-      <c r="S42">
-        <v>1.29</v>
-      </c>
-      <c r="T42">
-        <v>3.3</v>
-      </c>
-      <c r="U42">
-        <v>2.35</v>
-      </c>
-      <c r="V42">
-        <v>1.5</v>
-      </c>
-      <c r="W42">
-        <v>1.08</v>
-      </c>
-      <c r="X42">
-        <v>1.02</v>
-      </c>
-      <c r="Y42">
-        <v>1.2</v>
-      </c>
-      <c r="Z42">
-        <v>4.33</v>
-      </c>
-      <c r="AA42">
-        <v>1.65</v>
-      </c>
-      <c r="AB42">
-        <v>2.06</v>
-      </c>
-      <c r="AC42">
-        <v>2.55</v>
-      </c>
-      <c r="AD42">
-        <v>1.4</v>
-      </c>
-      <c r="AE42">
-        <v>1.14</v>
-      </c>
-      <c r="AF42">
-        <v>1.6</v>
-      </c>
-      <c r="AG42">
-        <v>2.3</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.87</v>
+        <v>3.46</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="P43">
-        <v>3.81</v>
+        <v>2.02</v>
       </c>
       <c r="Q43">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S43">
+        <v>1.36</v>
+      </c>
+      <c r="T43">
+        <v>2.88</v>
+      </c>
+      <c r="U43">
+        <v>2.88</v>
+      </c>
+      <c r="V43">
+        <v>1.36</v>
+      </c>
+      <c r="W43">
+        <v>1.05</v>
+      </c>
+      <c r="X43">
+        <v>1.05</v>
+      </c>
+      <c r="Y43">
         <v>1.3</v>
       </c>
-      <c r="T43">
-        <v>3.2</v>
-      </c>
-      <c r="U43">
-        <v>2.6</v>
-      </c>
-      <c r="V43">
-        <v>1.44</v>
-      </c>
-      <c r="W43">
+      <c r="Z43">
+        <v>3.4</v>
+      </c>
+      <c r="AA43">
+        <v>2</v>
+      </c>
+      <c r="AB43">
+        <v>1.8</v>
+      </c>
+      <c r="AC43">
+        <v>3.5</v>
+      </c>
+      <c r="AD43">
+        <v>1.29</v>
+      </c>
+      <c r="AE43">
         <v>1.08</v>
       </c>
-      <c r="X43">
-        <v>1.04</v>
-      </c>
-      <c r="Y43">
-        <v>1.22</v>
-      </c>
-      <c r="Z43">
-        <v>4.1</v>
-      </c>
-      <c r="AA43">
+      <c r="AF43">
         <v>1.8</v>
       </c>
-      <c r="AB43">
-        <v>1.96</v>
-      </c>
-      <c r="AC43">
-        <v>3.04</v>
-      </c>
-      <c r="AD43">
-        <v>1.38</v>
-      </c>
-      <c r="AE43">
-        <v>1.13</v>
-      </c>
-      <c r="AF43">
-        <v>1.73</v>
-      </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK43">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="O51">
         <v>3.25</v>
@@ -8640,46 +8640,46 @@
         <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC51">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q3">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="R3">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
         <v>1.69</v>
@@ -828,34 +828,34 @@
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y3">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Z3">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AA3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB3">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC3">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE3">
         <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AG3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="O10">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q10">
         <v>1.93</v>
       </c>
       <c r="R10">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="S10">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
         <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1978,19 +1978,19 @@
         <v>4.2</v>
       </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.6</v>
+        <v>5.42</v>
       </c>
       <c r="O11">
         <v>4.3</v>
       </c>
       <c r="P11">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S11">
         <v>1.17</v>
       </c>
       <c r="T11">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="U11">
         <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2141,7 +2141,7 @@
         <v>6.5</v>
       </c>
       <c r="AA11">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB11">
         <v>2.89</v>
@@ -2156,10 +2156,10 @@
         <v>1.3</v>
       </c>
       <c r="AF11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG11">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2917,28 +2917,28 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O16">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S16">
         <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V16">
         <v>1.56</v>
@@ -2953,19 +2953,19 @@
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB16">
+        <v>2.35</v>
+      </c>
+      <c r="AC16">
         <v>2.38</v>
       </c>
-      <c r="AC16">
-        <v>2.55</v>
-      </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE16">
         <v>1.2</v>
@@ -2974,7 +2974,7 @@
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.37</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
-        <v>5.19</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>6.72</v>
+        <v>2.05</v>
       </c>
       <c r="Q17">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="R17">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S17">
         <v>1.2</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U17">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AC17">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AD17">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE17">
+        <v>1.28</v>
+      </c>
+      <c r="AF17">
+        <v>1.36</v>
+      </c>
+      <c r="AG17">
+        <v>2.8</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.22</v>
       </c>
-      <c r="AF17">
-        <v>1.65</v>
-      </c>
-      <c r="AG17">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.1</v>
-      </c>
       <c r="AK17">
-        <v>2.58</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,65 +3243,65 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.73</v>
+        <v>1.4</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P18">
-        <v>2.05</v>
+        <v>6.72</v>
       </c>
       <c r="Q18">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="R18">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB18">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AC18">
+        <v>2.14</v>
+      </c>
+      <c r="AD18">
+        <v>1.61</v>
+      </c>
+      <c r="AE18">
+        <v>1.22</v>
+      </c>
+      <c r="AF18">
+        <v>1.65</v>
+      </c>
+      <c r="AG18">
         <v>2.1</v>
       </c>
-      <c r="AD18">
-        <v>1.73</v>
-      </c>
-      <c r="AE18">
-        <v>1.25</v>
-      </c>
-      <c r="AF18">
-        <v>1.36</v>
-      </c>
-      <c r="AG18">
-        <v>2.8</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>2.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="O20">
         <v>3.2</v>
@@ -3584,22 +3584,22 @@
         <v>1.99</v>
       </c>
       <c r="S20">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
         <v>2.76</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.29</v>
@@ -3608,7 +3608,7 @@
         <v>3.3</v>
       </c>
       <c r="AA20">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
         <v>1.85</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q23">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="R23">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="U23">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AC23">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="R24">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S24">
+        <v>1.36</v>
+      </c>
+      <c r="T24">
+        <v>2.88</v>
+      </c>
+      <c r="U24">
+        <v>2.88</v>
+      </c>
+      <c r="V24">
+        <v>1.36</v>
+      </c>
+      <c r="W24">
+        <v>1.06</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
         <v>1.29</v>
       </c>
-      <c r="T24">
-        <v>3.3</v>
-      </c>
-      <c r="U24">
-        <v>2.67</v>
-      </c>
-      <c r="V24">
-        <v>1.44</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
       <c r="Z24">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AB24">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AC24">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD24">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="Q26">
-        <v>3.35</v>
+        <v>2.65</v>
       </c>
       <c r="R26">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA26">
+        <v>1.97</v>
+      </c>
+      <c r="AB26">
+        <v>1.74</v>
+      </c>
+      <c r="AC26">
+        <v>3.6</v>
+      </c>
+      <c r="AD26">
+        <v>1.26</v>
+      </c>
+      <c r="AE26">
+        <v>1.06</v>
+      </c>
+      <c r="AF26">
         <v>1.8</v>
       </c>
-      <c r="AB26">
-        <v>1.9</v>
-      </c>
-      <c r="AC26">
-        <v>3.1</v>
-      </c>
-      <c r="AD26">
-        <v>1.36</v>
-      </c>
-      <c r="AE26">
-        <v>1.13</v>
-      </c>
-      <c r="AF26">
-        <v>1.62</v>
-      </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.73</v>
+        <v>3.14</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA27">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.14</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
-        <v>3.18</v>
+        <v>2.71</v>
       </c>
       <c r="R28">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AK28">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="R29">
         <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB29">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC29">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="Q31">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="R31">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA31">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB31">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD31">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R37">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U37">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AC37">
-        <v>2.97</v>
+        <v>2.57</v>
       </c>
       <c r="AD37">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG37">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,65 +6503,65 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>2.54</v>
+        <v>3.68</v>
       </c>
       <c r="Q38">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
+        <v>2.12</v>
+      </c>
+      <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.1</v>
+      </c>
+      <c r="U38">
+        <v>2.56</v>
+      </c>
+      <c r="V38">
+        <v>1.43</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.28</v>
+      </c>
+      <c r="Z38">
+        <v>3.42</v>
+      </c>
+      <c r="AA38">
+        <v>1.8</v>
+      </c>
+      <c r="AB38">
+        <v>1.9</v>
+      </c>
+      <c r="AC38">
+        <v>2.97</v>
+      </c>
+      <c r="AD38">
+        <v>1.3</v>
+      </c>
+      <c r="AE38">
+        <v>1.08</v>
+      </c>
+      <c r="AF38">
+        <v>1.7</v>
+      </c>
+      <c r="AG38">
         <v>2.04</v>
       </c>
-      <c r="S38">
-        <v>1.33</v>
-      </c>
-      <c r="T38">
-        <v>3</v>
-      </c>
-      <c r="U38">
-        <v>2.75</v>
-      </c>
-      <c r="V38">
-        <v>1.4</v>
-      </c>
-      <c r="W38">
-        <v>1.07</v>
-      </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.25</v>
-      </c>
-      <c r="Z38">
-        <v>3.8</v>
-      </c>
-      <c r="AA38">
-        <v>1.9</v>
-      </c>
-      <c r="AB38">
-        <v>1.86</v>
-      </c>
-      <c r="AC38">
-        <v>3.1</v>
-      </c>
-      <c r="AD38">
-        <v>1.36</v>
-      </c>
-      <c r="AE38">
-        <v>1.1</v>
-      </c>
-      <c r="AF38">
-        <v>1.67</v>
-      </c>
-      <c r="AG38">
-        <v>2.15</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="O39">
         <v>3.7</v>
       </c>
       <c r="P39">
-        <v>2.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q39">
-        <v>2.54</v>
+        <v>3.75</v>
       </c>
       <c r="R39">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U39">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6699,31 +6699,31 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA39">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB39">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AC39">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE39">
         <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="O41">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>1.82</v>
+        <v>2.54</v>
       </c>
       <c r="Q41">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AC41">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
+        <v>1.36</v>
+      </c>
+      <c r="AE41">
+        <v>1.1</v>
+      </c>
+      <c r="AF41">
+        <v>1.67</v>
+      </c>
+      <c r="AG41">
+        <v>2.15</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.39</v>
       </c>
-      <c r="AE41">
-        <v>1.12</v>
-      </c>
-      <c r="AF41">
-        <v>1.57</v>
-      </c>
-      <c r="AG41">
-        <v>2.19</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.25</v>
-      </c>
       <c r="AK41">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8791,10 +8791,10 @@
         <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="Q52">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="R52">
         <v>2</v>
@@ -8815,25 +8815,25 @@
         <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z52">
         <v>2.93</v>
       </c>
       <c r="AA52">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AB52">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC52">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD52">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE52">
         <v>1.06</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="P3">
         <v>2.45</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="O14">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="P14">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S14">
         <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
       <c r="U14">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
         <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB14">
         <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="AD14">
         <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG14">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK14">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
         <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="U15">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
         <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
         <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AG15">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O19">
         <v>3.3</v>
@@ -3415,16 +3415,16 @@
         <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R19">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
         <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U19">
         <v>2.32</v>
@@ -3433,7 +3433,7 @@
         <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3442,19 +3442,19 @@
         <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA19">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="AB19">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3463,7 +3463,7 @@
         <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O21">
         <v>4.3</v>
@@ -3747,22 +3747,22 @@
         <v>2.37</v>
       </c>
       <c r="S21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
         <v>2.09</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.14</v>
@@ -3771,13 +3771,13 @@
         <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC21">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AD21">
         <v>1.61</v>
@@ -3786,7 +3786,7 @@
         <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3901,7 +3901,7 @@
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3910,16 +3910,16 @@
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -3928,31 +3928,31 @@
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC22">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>4</v>
       </c>
       <c r="P23">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="Q23">
         <v>2.2</v>
@@ -4082,7 +4082,7 @@
         <v>2.31</v>
       </c>
       <c r="V23">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W23">
         <v>1.1</v>
@@ -4097,10 +4097,10 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
         <v>2.59</v>
@@ -4233,19 +4233,19 @@
         <v>2.51</v>
       </c>
       <c r="R24">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U24">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4269,16 +4269,16 @@
         <v>3.4</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA25">
+        <v>1.98</v>
+      </c>
+      <c r="AB25">
+        <v>1.71</v>
+      </c>
+      <c r="AC25">
+        <v>3.7</v>
+      </c>
+      <c r="AD25">
+        <v>1.27</v>
+      </c>
+      <c r="AE25">
+        <v>1.05</v>
+      </c>
+      <c r="AF25">
         <v>1.8</v>
       </c>
-      <c r="AB25">
-        <v>1.9</v>
-      </c>
-      <c r="AC25">
-        <v>3.1</v>
-      </c>
-      <c r="AD25">
-        <v>1.36</v>
-      </c>
-      <c r="AE25">
-        <v>1.13</v>
-      </c>
-      <c r="AF25">
-        <v>1.65</v>
-      </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="R26">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.25</v>
+        <v>4.22</v>
       </c>
       <c r="AA26">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AD26">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q27">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="R27">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="V27">
         <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC27">
         <v>2.88</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
         <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK27">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="Q28">
         <v>2.71</v>
@@ -4912,13 +4912,13 @@
         <v>3.8</v>
       </c>
       <c r="AA28">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC28">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="AD28">
         <v>1.33</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q29">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U29">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA29">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AC29">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
         <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O30">
         <v>3.8</v>
@@ -5214,10 +5214,10 @@
         <v>2.26</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
         <v>2.25</v>
@@ -5232,25 +5232,25 @@
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="AA30">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB30">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AC30">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AD30">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
         <v>1.65</v>
@@ -5368,25 +5368,25 @@
         <v>3.15</v>
       </c>
       <c r="P31">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R31">
         <v>2.09</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
         <v>1.07</v>
@@ -5395,31 +5395,31 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC31">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="AD31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5543,13 +5543,13 @@
         <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U32">
         <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
         <v>1.07</v>
@@ -5567,7 +5567,7 @@
         <v>1.74</v>
       </c>
       <c r="AB32">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5582,7 +5582,7 @@
         <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5694,10 +5694,10 @@
         <v>3.66</v>
       </c>
       <c r="P33">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q33">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
         <v>2.28</v>
@@ -5727,10 +5727,10 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC33">
         <v>2.34</v>
@@ -5739,7 +5739,7 @@
         <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
         <v>1.5</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O34">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P34">
-        <v>4.6</v>
+        <v>4.92</v>
       </c>
       <c r="Q34">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="S34">
         <v>1.2</v>
@@ -5872,13 +5872,13 @@
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
         <v>1.65</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5896,7 +5896,7 @@
         <v>2.7</v>
       </c>
       <c r="AC34">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD34">
         <v>1.67</v>
@@ -5908,7 +5908,7 @@
         <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,16 +6017,16 @@
         <v>1.53</v>
       </c>
       <c r="O35">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P35">
-        <v>4.9</v>
+        <v>5.47</v>
       </c>
       <c r="Q35">
         <v>1.96</v>
       </c>
       <c r="R35">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="S35">
         <v>1.17</v>
@@ -6035,10 +6035,10 @@
         <v>4.5</v>
       </c>
       <c r="U35">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="V35">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W35">
         <v>1.2</v>
@@ -6047,7 +6047,7 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z35">
         <v>6.5</v>
@@ -6056,7 +6056,7 @@
         <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC35">
         <v>2</v>
@@ -6071,7 +6071,7 @@
         <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6183,19 +6183,19 @@
         <v>4</v>
       </c>
       <c r="P36">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q36">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R36">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U36">
         <v>2.2</v>
@@ -6204,7 +6204,7 @@
         <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6213,22 +6213,22 @@
         <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB36">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC36">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF36">
         <v>1.5</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.26</v>
+        <v>3.48</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2.85</v>
+        <v>2.02</v>
       </c>
       <c r="Q37">
-        <v>2.54</v>
+        <v>3.8</v>
       </c>
       <c r="R37">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AB37">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AC37">
-        <v>2.57</v>
+        <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AG37">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AK37">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
+        <v>3.19</v>
+      </c>
+      <c r="O38">
+        <v>3.5</v>
+      </c>
+      <c r="P38">
+        <v>2.12</v>
+      </c>
+      <c r="Q38">
+        <v>3.84</v>
+      </c>
+      <c r="R38">
+        <v>2.11</v>
+      </c>
+      <c r="S38">
+        <v>1.32</v>
+      </c>
+      <c r="T38">
+        <v>3.02</v>
+      </c>
+      <c r="U38">
+        <v>2.48</v>
+      </c>
+      <c r="V38">
+        <v>1.46</v>
+      </c>
+      <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="Y38">
+        <v>1.25</v>
+      </c>
+      <c r="Z38">
+        <v>3.8</v>
+      </c>
+      <c r="AA38">
+        <v>1.78</v>
+      </c>
+      <c r="AB38">
         <v>1.93</v>
       </c>
-      <c r="O38">
-        <v>3.25</v>
-      </c>
-      <c r="P38">
-        <v>3.68</v>
-      </c>
-      <c r="Q38">
-        <v>2.5</v>
-      </c>
-      <c r="R38">
-        <v>2.12</v>
-      </c>
-      <c r="S38">
-        <v>1.3</v>
-      </c>
-      <c r="T38">
-        <v>3.1</v>
-      </c>
-      <c r="U38">
-        <v>2.56</v>
-      </c>
-      <c r="V38">
-        <v>1.43</v>
-      </c>
-      <c r="W38">
-        <v>1.08</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.28</v>
-      </c>
-      <c r="Z38">
-        <v>3.42</v>
-      </c>
-      <c r="AA38">
-        <v>1.8</v>
-      </c>
-      <c r="AB38">
-        <v>1.9</v>
-      </c>
       <c r="AC38">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="O39">
         <v>3.7</v>
       </c>
       <c r="P39">
-        <v>1.82</v>
+        <v>2.93</v>
       </c>
       <c r="Q39">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U39">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W39">
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA39">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB39">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE39">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG39">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,52 +6829,52 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="O40">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="Q40">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="R40">
         <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AB40">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AD40">
         <v>1.36</v>
@@ -6883,10 +6883,10 @@
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AK40">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
+        <v>3.7</v>
+      </c>
+      <c r="O41">
+        <v>3.8</v>
+      </c>
+      <c r="P41">
+        <v>1.82</v>
+      </c>
+      <c r="Q41">
+        <v>3.75</v>
+      </c>
+      <c r="R41">
+        <v>2.39</v>
+      </c>
+      <c r="S41">
+        <v>1.29</v>
+      </c>
+      <c r="T41">
+        <v>3.18</v>
+      </c>
+      <c r="U41">
         <v>2.42</v>
       </c>
-      <c r="O41">
-        <v>3.3</v>
-      </c>
-      <c r="P41">
-        <v>2.54</v>
-      </c>
-      <c r="Q41">
-        <v>3.2</v>
-      </c>
-      <c r="R41">
-        <v>2.04</v>
-      </c>
-      <c r="S41">
-        <v>1.33</v>
-      </c>
-      <c r="T41">
-        <v>3</v>
-      </c>
-      <c r="U41">
-        <v>2.75</v>
-      </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
+        <v>1.2</v>
+      </c>
+      <c r="Z41">
+        <v>3.9</v>
+      </c>
+      <c r="AA41">
+        <v>1.68</v>
+      </c>
+      <c r="AB41">
+        <v>2.11</v>
+      </c>
+      <c r="AC41">
+        <v>2.59</v>
+      </c>
+      <c r="AD41">
+        <v>1.42</v>
+      </c>
+      <c r="AE41">
+        <v>1.12</v>
+      </c>
+      <c r="AF41">
+        <v>1.6</v>
+      </c>
+      <c r="AG41">
+        <v>2.16</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.22</v>
+      </c>
+      <c r="AK41">
         <v>1.25</v>
-      </c>
-      <c r="Z41">
-        <v>3.8</v>
-      </c>
-      <c r="AA41">
-        <v>1.9</v>
-      </c>
-      <c r="AB41">
-        <v>1.86</v>
-      </c>
-      <c r="AC41">
-        <v>3.1</v>
-      </c>
-      <c r="AD41">
-        <v>1.36</v>
-      </c>
-      <c r="AE41">
-        <v>1.1</v>
-      </c>
-      <c r="AF41">
-        <v>1.67</v>
-      </c>
-      <c r="AG41">
-        <v>2.15</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.39</v>
-      </c>
-      <c r="AK41">
-        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="O42">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="P42">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q42">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="R42">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U42">
         <v>2.6</v>
@@ -7182,31 +7182,31 @@
         <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB42">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD42">
         <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
         <v>1.65</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.46</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.02</v>
+        <v>3.7</v>
       </c>
       <c r="Q43">
+        <v>2.55</v>
+      </c>
+      <c r="R43">
+        <v>2.12</v>
+      </c>
+      <c r="S43">
+        <v>1.33</v>
+      </c>
+      <c r="T43">
+        <v>3.1</v>
+      </c>
+      <c r="U43">
+        <v>2.57</v>
+      </c>
+      <c r="V43">
+        <v>1.43</v>
+      </c>
+      <c r="W43">
+        <v>1.08</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
+        <v>1.25</v>
+      </c>
+      <c r="Z43">
         <v>3.8</v>
       </c>
-      <c r="R43">
-        <v>2</v>
-      </c>
-      <c r="S43">
+      <c r="AA43">
+        <v>1.87</v>
+      </c>
+      <c r="AB43">
+        <v>1.9</v>
+      </c>
+      <c r="AC43">
+        <v>3.1</v>
+      </c>
+      <c r="AD43">
         <v>1.36</v>
       </c>
-      <c r="T43">
-        <v>2.88</v>
-      </c>
-      <c r="U43">
-        <v>2.88</v>
-      </c>
-      <c r="V43">
-        <v>1.36</v>
-      </c>
-      <c r="W43">
-        <v>1.05</v>
-      </c>
-      <c r="X43">
-        <v>1.05</v>
-      </c>
-      <c r="Y43">
-        <v>1.3</v>
-      </c>
-      <c r="Z43">
-        <v>3.4</v>
-      </c>
-      <c r="AA43">
-        <v>2</v>
-      </c>
-      <c r="AB43">
+      <c r="AE43">
+        <v>1.1</v>
+      </c>
+      <c r="AF43">
+        <v>1.73</v>
+      </c>
+      <c r="AG43">
+        <v>2.1</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.27</v>
+      </c>
+      <c r="AK43">
         <v>1.8</v>
-      </c>
-      <c r="AC43">
-        <v>3.5</v>
-      </c>
-      <c r="AD43">
-        <v>1.29</v>
-      </c>
-      <c r="AE43">
-        <v>1.08</v>
-      </c>
-      <c r="AF43">
-        <v>1.8</v>
-      </c>
-      <c r="AG43">
-        <v>2</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.65</v>
-      </c>
-      <c r="AK43">
-        <v>1.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8637,16 +8637,16 @@
         <v>2.02</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U51">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V51">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
         <v>1.05</v>
@@ -8664,19 +8664,19 @@
         <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
         <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
         <v>1.9</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="O52">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P52">
         <v>2.33</v>
       </c>
       <c r="Q52">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="R52">
         <v>2</v>
@@ -8821,7 +8821,7 @@
         <v>1.35</v>
       </c>
       <c r="Z52">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="AA52">
         <v>2.2</v>
@@ -8833,13 +8833,13 @@
         <v>4.05</v>
       </c>
       <c r="AD52">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE52">
         <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG52">
         <v>1.9</v>
@@ -8858,7 +8858,7 @@
         <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>4.35</v>
       </c>
       <c r="P10">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>1.93</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.42</v>
+        <v>5.98</v>
       </c>
       <c r="O11">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>1.47</v>
       </c>
       <c r="Q11">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="R11">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T11">
         <v>4.5</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V11">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W11">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2138,28 +2138,28 @@
         <v>1.08</v>
       </c>
       <c r="Z11">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB11">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AC11">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AD11">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="O17">
         <v>3.8</v>
@@ -3092,7 +3092,7 @@
         <v>3.5</v>
       </c>
       <c r="R17">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
         <v>1.2</v>
@@ -3246,7 +3246,7 @@
         <v>1.4</v>
       </c>
       <c r="O18">
-        <v>4.8</v>
+        <v>5.19</v>
       </c>
       <c r="P18">
         <v>6.72</v>
@@ -3279,7 +3279,7 @@
         <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>1.42</v>
@@ -3288,7 +3288,7 @@
         <v>2.49</v>
       </c>
       <c r="AC18">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AD18">
         <v>1.61</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK18">
         <v>2.78</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O19">
         <v>3.3</v>
@@ -3427,10 +3427,10 @@
         <v>2.64</v>
       </c>
       <c r="U19">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3590,7 +3590,7 @@
         <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -3614,7 +3614,7 @@
         <v>1.85</v>
       </c>
       <c r="AC20">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD20">
         <v>1.3</v>
@@ -3735,10 +3735,10 @@
         <v>1.5</v>
       </c>
       <c r="O21">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="P21">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q21">
         <v>1.93</v>
@@ -3753,13 +3753,13 @@
         <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="V21">
         <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3901,7 +3901,7 @@
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3922,7 +3922,7 @@
         <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.06</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="O23">
         <v>4</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="R24">
+        <v>2.16</v>
+      </c>
+      <c r="S24">
+        <v>1.29</v>
+      </c>
+      <c r="T24">
+        <v>3.3</v>
+      </c>
+      <c r="U24">
+        <v>2.55</v>
+      </c>
+      <c r="V24">
+        <v>1.45</v>
+      </c>
+      <c r="W24">
+        <v>1.08</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.22</v>
+      </c>
+      <c r="Z24">
+        <v>4.22</v>
+      </c>
+      <c r="AA24">
+        <v>1.71</v>
+      </c>
+      <c r="AB24">
+        <v>2.05</v>
+      </c>
+      <c r="AC24">
+        <v>2.6</v>
+      </c>
+      <c r="AD24">
+        <v>1.42</v>
+      </c>
+      <c r="AE24">
+        <v>1.14</v>
+      </c>
+      <c r="AF24">
+        <v>1.57</v>
+      </c>
+      <c r="AG24">
         <v>2.25</v>
       </c>
-      <c r="S24">
-        <v>1.37</v>
-      </c>
-      <c r="T24">
-        <v>3.04</v>
-      </c>
-      <c r="U24">
-        <v>2.62</v>
-      </c>
-      <c r="V24">
-        <v>1.41</v>
-      </c>
-      <c r="W24">
-        <v>1.06</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.29</v>
-      </c>
-      <c r="Z24">
-        <v>3.5</v>
-      </c>
-      <c r="AA24">
-        <v>1.92</v>
-      </c>
-      <c r="AB24">
-        <v>1.84</v>
-      </c>
-      <c r="AC24">
-        <v>3.4</v>
-      </c>
-      <c r="AD24">
-        <v>1.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.12</v>
-      </c>
-      <c r="AF24">
-        <v>1.75</v>
-      </c>
-      <c r="AG24">
-        <v>2</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="Q25">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="R25">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T25">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>3.13</v>
+        <v>2.42</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y25">
+        <v>1.22</v>
+      </c>
+      <c r="Z25">
+        <v>3.8</v>
+      </c>
+      <c r="AA25">
+        <v>1.75</v>
+      </c>
+      <c r="AB25">
+        <v>1.92</v>
+      </c>
+      <c r="AC25">
+        <v>3.21</v>
+      </c>
+      <c r="AD25">
         <v>1.33</v>
       </c>
-      <c r="Z25">
-        <v>3.25</v>
-      </c>
-      <c r="AA25">
-        <v>1.98</v>
-      </c>
-      <c r="AB25">
-        <v>1.71</v>
-      </c>
-      <c r="AC25">
-        <v>3.7</v>
-      </c>
-      <c r="AD25">
-        <v>1.27</v>
-      </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
+        <v>3.1</v>
+      </c>
+      <c r="O26">
+        <v>3.35</v>
+      </c>
+      <c r="P26">
+        <v>2.2</v>
+      </c>
+      <c r="Q26">
+        <v>3.5</v>
+      </c>
+      <c r="R26">
+        <v>2.2</v>
+      </c>
+      <c r="S26">
+        <v>1.3</v>
+      </c>
+      <c r="T26">
         <v>3.2</v>
       </c>
-      <c r="O26">
-        <v>3.4</v>
-      </c>
-      <c r="P26">
-        <v>2.08</v>
-      </c>
-      <c r="Q26">
-        <v>3.18</v>
-      </c>
-      <c r="R26">
-        <v>2.16</v>
-      </c>
-      <c r="S26">
-        <v>1.29</v>
-      </c>
-      <c r="T26">
-        <v>3.3</v>
-      </c>
       <c r="U26">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
+        <v>1.07</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.21</v>
+      </c>
+      <c r="Z26">
+        <v>3.8</v>
+      </c>
+      <c r="AA26">
+        <v>1.79</v>
+      </c>
+      <c r="AB26">
+        <v>1.95</v>
+      </c>
+      <c r="AC26">
+        <v>3.04</v>
+      </c>
+      <c r="AD26">
+        <v>1.36</v>
+      </c>
+      <c r="AE26">
         <v>1.08</v>
       </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>1.22</v>
-      </c>
-      <c r="Z26">
-        <v>4.22</v>
-      </c>
-      <c r="AA26">
-        <v>1.7</v>
-      </c>
-      <c r="AB26">
-        <v>2.05</v>
-      </c>
-      <c r="AC26">
-        <v>2.6</v>
-      </c>
-      <c r="AD26">
-        <v>1.42</v>
-      </c>
-      <c r="AE26">
-        <v>1.14</v>
-      </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AK26">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O27">
+        <v>4.05</v>
+      </c>
+      <c r="P27">
+        <v>4.75</v>
+      </c>
+      <c r="Q27">
+        <v>2.03</v>
+      </c>
+      <c r="R27">
+        <v>2.26</v>
+      </c>
+      <c r="S27">
+        <v>1.29</v>
+      </c>
+      <c r="T27">
         <v>3.3</v>
       </c>
-      <c r="P27">
-        <v>2.5</v>
-      </c>
-      <c r="Q27">
-        <v>2.83</v>
-      </c>
-      <c r="R27">
-        <v>2.15</v>
-      </c>
-      <c r="S27">
-        <v>1.3</v>
-      </c>
-      <c r="T27">
-        <v>3.2</v>
-      </c>
       <c r="U27">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>4.1</v>
+        <v>4.49</v>
       </c>
       <c r="AA27">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB27">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
         <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="R28">
         <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK28">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q29">
-        <v>3.07</v>
+        <v>2.65</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="U29">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="V29">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="AA29">
+        <v>1.98</v>
+      </c>
+      <c r="AB29">
+        <v>1.71</v>
+      </c>
+      <c r="AC29">
+        <v>3.7</v>
+      </c>
+      <c r="AD29">
+        <v>1.27</v>
+      </c>
+      <c r="AE29">
+        <v>1.05</v>
+      </c>
+      <c r="AF29">
         <v>1.8</v>
       </c>
-      <c r="AB29">
-        <v>1.96</v>
-      </c>
-      <c r="AC29">
-        <v>3.06</v>
-      </c>
-      <c r="AD29">
-        <v>1.36</v>
-      </c>
-      <c r="AE29">
-        <v>1.14</v>
-      </c>
-      <c r="AF29">
-        <v>1.65</v>
-      </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="Q30">
-        <v>2.03</v>
+        <v>2.51</v>
       </c>
       <c r="R30">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U30">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>4.49</v>
+        <v>3.34</v>
       </c>
       <c r="AA30">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AB30">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
+        <v>1.75</v>
+      </c>
+      <c r="AG30">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.28</v>
+      </c>
+      <c r="AK30">
         <v>1.65</v>
-      </c>
-      <c r="AG30">
-        <v>2.15</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.17</v>
-      </c>
-      <c r="AK30">
-        <v>2.14</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>2.75</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
         <v>2.45</v>
@@ -5380,7 +5380,7 @@
         <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U31">
         <v>2.75</v>
@@ -5407,7 +5407,7 @@
         <v>1.93</v>
       </c>
       <c r="AC31">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AD31">
         <v>1.33</v>
@@ -5528,10 +5528,10 @@
         <v>1.48</v>
       </c>
       <c r="O32">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="Q32">
         <v>2.11</v>
@@ -5552,7 +5552,7 @@
         <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.03</v>
@@ -5579,7 +5579,7 @@
         <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG32">
         <v>1.94</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,37 +6503,37 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.19</v>
+        <v>2.54</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="Q38">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="R38">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.25</v>
@@ -6542,25 +6542,25 @@
         <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AB38">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
         <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AK38">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
+        <v>3.6</v>
+      </c>
+      <c r="P39">
         <v>3.7</v>
       </c>
-      <c r="P39">
-        <v>2.93</v>
-      </c>
       <c r="Q39">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V39">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.54</v>
+        <v>3.7</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="Q40">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U40">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
+        <v>1.2</v>
+      </c>
+      <c r="Z40">
+        <v>3.9</v>
+      </c>
+      <c r="AA40">
+        <v>1.68</v>
+      </c>
+      <c r="AB40">
+        <v>2.11</v>
+      </c>
+      <c r="AC40">
+        <v>2.59</v>
+      </c>
+      <c r="AD40">
+        <v>1.42</v>
+      </c>
+      <c r="AE40">
+        <v>1.12</v>
+      </c>
+      <c r="AF40">
+        <v>1.6</v>
+      </c>
+      <c r="AG40">
+        <v>2.16</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.22</v>
+      </c>
+      <c r="AK40">
         <v>1.25</v>
-      </c>
-      <c r="Z40">
-        <v>3.8</v>
-      </c>
-      <c r="AA40">
-        <v>1.87</v>
-      </c>
-      <c r="AB40">
-        <v>1.9</v>
-      </c>
-      <c r="AC40">
-        <v>3.1</v>
-      </c>
-      <c r="AD40">
-        <v>1.36</v>
-      </c>
-      <c r="AE40">
-        <v>1.1</v>
-      </c>
-      <c r="AF40">
-        <v>1.67</v>
-      </c>
-      <c r="AG40">
-        <v>2.08</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.39</v>
-      </c>
-      <c r="AK40">
-        <v>1.39</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>3.2</v>
+      </c>
+      <c r="O41">
+        <v>3.44</v>
+      </c>
+      <c r="P41">
+        <v>2.12</v>
+      </c>
+      <c r="Q41">
         <v>3.7</v>
       </c>
-      <c r="O41">
-        <v>3.8</v>
-      </c>
-      <c r="P41">
-        <v>1.82</v>
-      </c>
-      <c r="Q41">
-        <v>3.75</v>
-      </c>
       <c r="R41">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA41">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AB41">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AC41">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="AD41">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="O42">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.12</v>
+        <v>2.93</v>
       </c>
       <c r="Q42">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
         <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA42">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AD42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,37 +7318,37 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>3.19</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="Q43">
-        <v>2.55</v>
+        <v>3.84</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U43">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y43">
         <v>1.25</v>
@@ -7357,25 +7357,25 @@
         <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
         <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8625,10 +8625,10 @@
         <v>2.73</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P51">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q51">
         <v>3.13</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="O2">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -961,37 +961,37 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
         <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.18</v>
@@ -1000,25 +1000,25 @@
         <v>4.4</v>
       </c>
       <c r="AA4">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC4">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="AD4">
         <v>1.47</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.08</v>
       </c>
       <c r="AK4">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="O5">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="P5">
-        <v>8.869999999999999</v>
+        <v>11</v>
       </c>
       <c r="Q5">
         <v>1.5</v>
       </c>
       <c r="R5">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="U5">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
+        <v>1.15</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>5.01</v>
+      </c>
+      <c r="AA5">
+        <v>1.53</v>
+      </c>
+      <c r="AB5">
+        <v>2.5</v>
+      </c>
+      <c r="AC5">
+        <v>2.31</v>
+      </c>
+      <c r="AD5">
+        <v>1.57</v>
+      </c>
+      <c r="AE5">
         <v>1.18</v>
       </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>1.13</v>
-      </c>
-      <c r="Z5">
-        <v>6</v>
-      </c>
-      <c r="AA5">
-        <v>1.44</v>
-      </c>
-      <c r="AB5">
-        <v>2.6</v>
-      </c>
-      <c r="AC5">
-        <v>2.08</v>
-      </c>
-      <c r="AD5">
-        <v>1.65</v>
-      </c>
-      <c r="AE5">
-        <v>1.25</v>
-      </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK5">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>7.39</v>
+        <v>2.35</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="P8">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
-        <v>2.61</v>
+        <v>2.21</v>
       </c>
       <c r="U8">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
         <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
+        <v>1.5</v>
+      </c>
+      <c r="Z8">
+        <v>2.55</v>
+      </c>
+      <c r="AA8">
+        <v>2.52</v>
+      </c>
+      <c r="AB8">
         <v>1.44</v>
       </c>
-      <c r="Z8">
-        <v>2.75</v>
-      </c>
-      <c r="AA8">
-        <v>2.3</v>
-      </c>
-      <c r="AB8">
-        <v>1.6</v>
-      </c>
       <c r="AC8">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="O9">
-        <v>2.87</v>
+        <v>4.25</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>6.09</v>
       </c>
       <c r="R9">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z9">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="AB9">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AC9">
-        <v>4.95</v>
+        <v>3.96</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AG9">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="O10">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="Q10">
         <v>1.93</v>
       </c>
       <c r="R10">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S10">
         <v>1.29</v>
@@ -1975,7 +1975,7 @@
         <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
         <v>1.66</v>
@@ -1984,10 +1984,10 @@
         <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AD10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
         <v>1.17</v>
@@ -2108,13 +2108,13 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="Q11">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="R11">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="S11">
         <v>1.18</v>
@@ -2175,7 +2175,7 @@
         <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O14">
         <v>3.05</v>
@@ -2600,16 +2600,16 @@
         <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R14">
         <v>1.92</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="U14">
         <v>2.92</v>
@@ -2621,19 +2621,19 @@
         <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
         <v>2.88</v>
       </c>
       <c r="AA14">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC14">
         <v>3.98</v>
@@ -2642,7 +2642,7 @@
         <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>1.9</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>6.04</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q15">
-        <v>6.5</v>
+        <v>5.51</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="U15">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2787,31 +2787,31 @@
         <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z15">
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
         <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>2.63</v>
       </c>
       <c r="AK15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.73</v>
+        <v>1.37</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>5.19</v>
       </c>
       <c r="P17">
-        <v>2.05</v>
+        <v>6.72</v>
       </c>
       <c r="Q17">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S17">
         <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U17">
         <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB17">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AC17">
+        <v>2.31</v>
+      </c>
+      <c r="AD17">
+        <v>1.61</v>
+      </c>
+      <c r="AE17">
+        <v>1.22</v>
+      </c>
+      <c r="AF17">
+        <v>1.67</v>
+      </c>
+      <c r="AG17">
         <v>2.05</v>
       </c>
-      <c r="AD17">
-        <v>1.65</v>
-      </c>
-      <c r="AE17">
-        <v>1.28</v>
-      </c>
-      <c r="AF17">
-        <v>1.36</v>
-      </c>
-      <c r="AG17">
-        <v>2.8</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>2.78</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>5.19</v>
+        <v>3.85</v>
       </c>
       <c r="P18">
-        <v>6.72</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AC18">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE18">
+        <v>1.28</v>
+      </c>
+      <c r="AF18">
+        <v>1.36</v>
+      </c>
+      <c r="AG18">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.22</v>
       </c>
-      <c r="AF18">
-        <v>1.65</v>
-      </c>
-      <c r="AG18">
-        <v>2.1</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.09</v>
-      </c>
       <c r="AK18">
-        <v>2.78</v>
+        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>1.91</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
         <v>3.4</v>
@@ -3427,10 +3427,10 @@
         <v>2.64</v>
       </c>
       <c r="U19">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3572,10 +3572,10 @@
         <v>2.85</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P21">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q21">
         <v>1.93</v>
@@ -3771,16 +3771,16 @@
         <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC21">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AD21">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE21">
         <v>1.25</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="O22">
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
         <v>4</v>
       </c>
       <c r="P23">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="Q23">
         <v>2.2</v>
@@ -4079,10 +4079,10 @@
         <v>3.32</v>
       </c>
       <c r="U23">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
         <v>1.1</v>
@@ -4100,7 +4100,7 @@
         <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC23">
         <v>2.59</v>
@@ -4224,10 +4224,10 @@
         <v>3.2</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q24">
         <v>3.18</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S25">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA25">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AC25">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG25">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>2.51</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC26">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.61</v>
+        <v>2.88</v>
       </c>
       <c r="O27">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>4.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q27">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>4.49</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AB27">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>2.64</v>
+        <v>3.04</v>
       </c>
       <c r="AD27">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AK27">
-        <v>2.14</v>
+        <v>1.32</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q28">
-        <v>3.32</v>
+        <v>2.71</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
+        <v>3.08</v>
+      </c>
+      <c r="U28">
+        <v>2.42</v>
+      </c>
+      <c r="V28">
+        <v>1.48</v>
+      </c>
+      <c r="W28">
+        <v>1.09</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>1.22</v>
+      </c>
+      <c r="Z28">
+        <v>3.8</v>
+      </c>
+      <c r="AA28">
+        <v>1.75</v>
+      </c>
+      <c r="AB28">
+        <v>1.92</v>
+      </c>
+      <c r="AC28">
         <v>3.2</v>
       </c>
-      <c r="U28">
-        <v>2.36</v>
-      </c>
-      <c r="V28">
-        <v>1.45</v>
-      </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.24</v>
-      </c>
-      <c r="Z28">
-        <v>4.1</v>
-      </c>
-      <c r="AA28">
-        <v>1.72</v>
-      </c>
-      <c r="AB28">
-        <v>2.07</v>
-      </c>
-      <c r="AC28">
-        <v>2.88</v>
-      </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
+        <v>1.63</v>
+      </c>
+      <c r="AG28">
+        <v>2.14</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.38</v>
+      </c>
+      <c r="AK28">
         <v>1.53</v>
-      </c>
-      <c r="AG28">
-        <v>2.45</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.4</v>
-      </c>
-      <c r="AK28">
-        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
-        <v>2.65</v>
+        <v>3.32</v>
       </c>
       <c r="R29">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AB29">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AC29">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.8</v>
+      </c>
+      <c r="O30">
+        <v>3.5</v>
+      </c>
+      <c r="P30">
+        <v>2.3</v>
+      </c>
+      <c r="Q30">
+        <v>3</v>
+      </c>
+      <c r="R30">
+        <v>2.09</v>
+      </c>
+      <c r="S30">
+        <v>1.33</v>
+      </c>
+      <c r="T30">
+        <v>3.05</v>
+      </c>
+      <c r="U30">
+        <v>2.75</v>
+      </c>
+      <c r="V30">
+        <v>1.44</v>
+      </c>
+      <c r="W30">
+        <v>1.07</v>
+      </c>
+      <c r="X30">
+        <v>1.04</v>
+      </c>
+      <c r="Y30">
+        <v>1.25</v>
+      </c>
+      <c r="Z30">
+        <v>3.8</v>
+      </c>
+      <c r="AA30">
+        <v>1.85</v>
+      </c>
+      <c r="AB30">
+        <v>1.93</v>
+      </c>
+      <c r="AC30">
+        <v>3.29</v>
+      </c>
+      <c r="AD30">
+        <v>1.33</v>
+      </c>
+      <c r="AE30">
+        <v>1.1</v>
+      </c>
+      <c r="AF30">
+        <v>1.67</v>
+      </c>
+      <c r="AG30">
         <v>2.15</v>
       </c>
-      <c r="O30">
-        <v>3.4</v>
-      </c>
-      <c r="P30">
-        <v>3.3</v>
-      </c>
-      <c r="Q30">
-        <v>2.51</v>
-      </c>
-      <c r="R30">
-        <v>2.25</v>
-      </c>
-      <c r="S30">
-        <v>1.37</v>
-      </c>
-      <c r="T30">
-        <v>3.04</v>
-      </c>
-      <c r="U30">
-        <v>2.62</v>
-      </c>
-      <c r="V30">
-        <v>1.41</v>
-      </c>
-      <c r="W30">
-        <v>1.06</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.24</v>
       </c>
-      <c r="Z30">
-        <v>3.34</v>
-      </c>
-      <c r="AA30">
-        <v>1.88</v>
-      </c>
-      <c r="AB30">
-        <v>1.85</v>
-      </c>
-      <c r="AC30">
-        <v>3.08</v>
-      </c>
-      <c r="AD30">
-        <v>1.28</v>
-      </c>
-      <c r="AE30">
-        <v>1.06</v>
-      </c>
-      <c r="AF30">
-        <v>1.75</v>
-      </c>
-      <c r="AG30">
-        <v>2</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.28</v>
-      </c>
       <c r="AK30">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="R31">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>3.8</v>
+        <v>4.49</v>
       </c>
       <c r="AA31">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.48</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q32">
         <v>2.11</v>
@@ -5549,7 +5549,7 @@
         <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5561,13 +5561,13 @@
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>2.88</v>
@@ -5576,10 +5576,10 @@
         <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
         <v>1.94</v>
@@ -5854,7 +5854,7 @@
         <v>1.5</v>
       </c>
       <c r="O34">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P34">
         <v>4.92</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P36">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q37">
         <v>3.8</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,34 +6503,34 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P38">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="Q38">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="R38">
         <v>2.1</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1.04</v>
@@ -6539,28 +6539,28 @@
         <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA38">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,37 +6666,37 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P39">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="Q39">
-        <v>2.55</v>
+        <v>3.84</v>
       </c>
       <c r="R39">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U39">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y39">
         <v>1.25</v>
@@ -6705,25 +6705,25 @@
         <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
         <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O40">
+        <v>3.43</v>
+      </c>
+      <c r="P40">
+        <v>2.38</v>
+      </c>
+      <c r="Q40">
+        <v>3.14</v>
+      </c>
+      <c r="R40">
+        <v>2.1</v>
+      </c>
+      <c r="S40">
+        <v>1.33</v>
+      </c>
+      <c r="T40">
+        <v>3</v>
+      </c>
+      <c r="U40">
+        <v>2.67</v>
+      </c>
+      <c r="V40">
+        <v>1.4</v>
+      </c>
+      <c r="W40">
+        <v>1.07</v>
+      </c>
+      <c r="X40">
+        <v>1.04</v>
+      </c>
+      <c r="Y40">
+        <v>1.25</v>
+      </c>
+      <c r="Z40">
         <v>3.8</v>
       </c>
-      <c r="P40">
-        <v>1.82</v>
-      </c>
-      <c r="Q40">
-        <v>3.75</v>
-      </c>
-      <c r="R40">
-        <v>2.39</v>
-      </c>
-      <c r="S40">
-        <v>1.29</v>
-      </c>
-      <c r="T40">
-        <v>3.18</v>
-      </c>
-      <c r="U40">
-        <v>2.42</v>
-      </c>
-      <c r="V40">
-        <v>1.48</v>
-      </c>
-      <c r="W40">
-        <v>1.08</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.2</v>
-      </c>
-      <c r="Z40">
-        <v>3.9</v>
-      </c>
       <c r="AA40">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AB40">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AD40">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AK40">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O41">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="P41">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="Q41">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U41">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
+        <v>1.2</v>
+      </c>
+      <c r="Z41">
+        <v>3.9</v>
+      </c>
+      <c r="AA41">
+        <v>1.68</v>
+      </c>
+      <c r="AB41">
+        <v>2.11</v>
+      </c>
+      <c r="AC41">
+        <v>2.59</v>
+      </c>
+      <c r="AD41">
+        <v>1.42</v>
+      </c>
+      <c r="AE41">
+        <v>1.12</v>
+      </c>
+      <c r="AF41">
+        <v>1.6</v>
+      </c>
+      <c r="AG41">
+        <v>2.16</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.22</v>
+      </c>
+      <c r="AK41">
         <v>1.25</v>
-      </c>
-      <c r="Z41">
-        <v>3.7</v>
-      </c>
-      <c r="AA41">
-        <v>1.76</v>
-      </c>
-      <c r="AB41">
-        <v>1.99</v>
-      </c>
-      <c r="AC41">
-        <v>2.78</v>
-      </c>
-      <c r="AD41">
-        <v>1.36</v>
-      </c>
-      <c r="AE41">
-        <v>1.11</v>
-      </c>
-      <c r="AF41">
-        <v>1.65</v>
-      </c>
-      <c r="AG41">
-        <v>2.2</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.23</v>
-      </c>
-      <c r="AK41">
-        <v>1.27</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
         <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="Q42">
         <v>2.54</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,37 +7318,37 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P43">
+        <v>3.62</v>
+      </c>
+      <c r="Q43">
+        <v>2.45</v>
+      </c>
+      <c r="R43">
         <v>2.12</v>
       </c>
-      <c r="Q43">
-        <v>3.84</v>
-      </c>
-      <c r="R43">
-        <v>2.11</v>
-      </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U43">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
         <v>1.25</v>
@@ -7357,25 +7357,25 @@
         <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
         <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="O51">
         <v>3.15</v>
       </c>
       <c r="P51">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q51">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="R51">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U51">
         <v>3.18</v>
@@ -8649,16 +8649,16 @@
         <v>1.37</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA51">
         <v>2.1</v>
@@ -8667,19 +8667,19 @@
         <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,24 +624,24 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="O2">
-        <v>3.87</v>
+        <v>4.25</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="P3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R3">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="S3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="T3">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y3">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Z3">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AA3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE3">
         <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O4">
         <v>3.4</v>
@@ -1000,16 +1000,16 @@
         <v>4.4</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
         <v>2.14</v>
       </c>
       <c r="AC4">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE4">
         <v>1.12</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="O5">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
       <c r="P5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q5">
         <v>1.5</v>
@@ -1145,10 +1145,10 @@
         <v>3.24</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
         <v>1.15</v>
@@ -1157,19 +1157,19 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>5.01</v>
+        <v>4.84</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC5">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD5">
         <v>1.57</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O6">
+        <v>2.43</v>
+      </c>
+      <c r="P6">
         <v>2.45</v>
-      </c>
-      <c r="P6">
-        <v>2.55</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>2.05</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1945,52 +1945,52 @@
         <v>4.25</v>
       </c>
       <c r="P10">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Q11">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="S11">
         <v>1.18</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O12">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P12">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
       <c r="Q12">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA12">
+        <v>1.48</v>
+      </c>
+      <c r="AB12">
+        <v>2.62</v>
+      </c>
+      <c r="AC12">
+        <v>2.3</v>
+      </c>
+      <c r="AD12">
         <v>1.69</v>
       </c>
-      <c r="AB12">
-        <v>2.41</v>
-      </c>
-      <c r="AC12">
-        <v>2.5</v>
-      </c>
-      <c r="AD12">
-        <v>1.5</v>
-      </c>
       <c r="AE12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
         <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>9.220000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="O13">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="P13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q13">
         <v>5.61</v>
@@ -2443,49 +2443,49 @@
         <v>2.63</v>
       </c>
       <c r="S13">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T13">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U13">
         <v>2.08</v>
       </c>
       <c r="V13">
+        <v>1.75</v>
+      </c>
+      <c r="W13">
+        <v>1.14</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.11</v>
+      </c>
+      <c r="Z13">
+        <v>5.5</v>
+      </c>
+      <c r="AA13">
+        <v>1.44</v>
+      </c>
+      <c r="AB13">
+        <v>2.62</v>
+      </c>
+      <c r="AC13">
+        <v>2.25</v>
+      </c>
+      <c r="AD13">
+        <v>1.69</v>
+      </c>
+      <c r="AE13">
+        <v>1.22</v>
+      </c>
+      <c r="AF13">
         <v>1.78</v>
       </c>
-      <c r="W13">
-        <v>1.18</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.06</v>
-      </c>
-      <c r="Z13">
-        <v>7</v>
-      </c>
-      <c r="AA13">
-        <v>1.37</v>
-      </c>
-      <c r="AB13">
-        <v>3.05</v>
-      </c>
-      <c r="AC13">
-        <v>2.01</v>
-      </c>
-      <c r="AD13">
-        <v>1.8</v>
-      </c>
-      <c r="AE13">
-        <v>1.33</v>
-      </c>
-      <c r="AF13">
-        <v>1.67</v>
-      </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>3.6</v>
       </c>
       <c r="AK13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2926,71 +2926,71 @@
         <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="R16">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
         <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA16">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB16">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC16">
         <v>2.38</v>
       </c>
       <c r="AD16">
+        <v>1.57</v>
+      </c>
+      <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
         <v>1.53</v>
       </c>
-      <c r="AE16">
+      <c r="AG16">
+        <v>2.3</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.2</v>
       </c>
-      <c r="AF16">
-        <v>1.57</v>
-      </c>
-      <c r="AG16">
-        <v>2.24</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.21</v>
-      </c>
       <c r="AK16">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O17">
-        <v>5.19</v>
+        <v>4.99</v>
       </c>
       <c r="P17">
         <v>6.72</v>
@@ -3101,10 +3101,10 @@
         <v>4</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3113,25 +3113,25 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="AA17">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="AC17">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
         <v>1.67</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -3409,10 +3409,10 @@
         <v>1.91</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q19">
         <v>2.54</v>
@@ -3439,10 +3439,10 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA19">
         <v>1.99</v>
@@ -3460,7 +3460,7 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
         <v>1.84</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P21">
         <v>5.5</v>
@@ -3756,10 +3756,10 @@
         <v>2.08</v>
       </c>
       <c r="V21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3771,19 +3771,19 @@
         <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD21">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE21">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF21">
         <v>1.57</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P22">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3910,16 +3910,16 @@
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
         <v>2.75</v>
       </c>
       <c r="U22">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
         <v>1.04</v>
@@ -3934,19 +3934,19 @@
         <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB22">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AC22">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD22">
         <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
         <v>1.9</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P23">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="Q23">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
+        <v>1.29</v>
+      </c>
+      <c r="T23">
+        <v>3.3</v>
+      </c>
+      <c r="U23">
+        <v>2.55</v>
+      </c>
+      <c r="V23">
+        <v>1.45</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>4.26</v>
+      </c>
+      <c r="AA23">
+        <v>1.75</v>
+      </c>
+      <c r="AB23">
+        <v>2.05</v>
+      </c>
+      <c r="AC23">
+        <v>2.88</v>
+      </c>
+      <c r="AD23">
+        <v>1.4</v>
+      </c>
+      <c r="AE23">
+        <v>1.14</v>
+      </c>
+      <c r="AF23">
+        <v>1.57</v>
+      </c>
+      <c r="AG23">
+        <v>2.25</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.22</v>
+      </c>
+      <c r="AK23">
         <v>1.27</v>
-      </c>
-      <c r="T23">
-        <v>3.32</v>
-      </c>
-      <c r="U23">
-        <v>2.34</v>
-      </c>
-      <c r="V23">
-        <v>1.49</v>
-      </c>
-      <c r="W23">
-        <v>1.1</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.16</v>
-      </c>
-      <c r="Z23">
-        <v>4.15</v>
-      </c>
-      <c r="AA23">
-        <v>1.65</v>
-      </c>
-      <c r="AB23">
-        <v>2.09</v>
-      </c>
-      <c r="AC23">
-        <v>2.59</v>
-      </c>
-      <c r="AD23">
-        <v>1.39</v>
-      </c>
-      <c r="AE23">
-        <v>1.12</v>
-      </c>
-      <c r="AF23">
-        <v>1.64</v>
-      </c>
-      <c r="AG23">
-        <v>2.13</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.21</v>
-      </c>
-      <c r="AK23">
-        <v>1.97</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>3.1</v>
+      </c>
+      <c r="O24">
+        <v>3.35</v>
+      </c>
+      <c r="P24">
+        <v>2.2</v>
+      </c>
+      <c r="Q24">
+        <v>3.5</v>
+      </c>
+      <c r="R24">
+        <v>2.2</v>
+      </c>
+      <c r="S24">
+        <v>1.3</v>
+      </c>
+      <c r="T24">
         <v>3.2</v>
       </c>
-      <c r="O24">
-        <v>3.7</v>
-      </c>
-      <c r="P24">
-        <v>2.05</v>
-      </c>
-      <c r="Q24">
-        <v>3.18</v>
-      </c>
-      <c r="R24">
-        <v>2.16</v>
-      </c>
-      <c r="S24">
-        <v>1.29</v>
-      </c>
-      <c r="T24">
-        <v>3.3</v>
-      </c>
       <c r="U24">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
+        <v>1.07</v>
+      </c>
+      <c r="X24">
+        <v>1.03</v>
+      </c>
+      <c r="Y24">
+        <v>1.21</v>
+      </c>
+      <c r="Z24">
+        <v>3.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.79</v>
+      </c>
+      <c r="AB24">
+        <v>1.95</v>
+      </c>
+      <c r="AC24">
+        <v>3.06</v>
+      </c>
+      <c r="AD24">
+        <v>1.36</v>
+      </c>
+      <c r="AE24">
         <v>1.08</v>
       </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1.22</v>
-      </c>
-      <c r="Z24">
-        <v>4.22</v>
-      </c>
-      <c r="AA24">
-        <v>1.71</v>
-      </c>
-      <c r="AB24">
-        <v>2.05</v>
-      </c>
-      <c r="AC24">
-        <v>2.6</v>
-      </c>
-      <c r="AD24">
-        <v>1.42</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AK24">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R25">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T25">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="V25">
+        <v>1.48</v>
+      </c>
+      <c r="W25">
+        <v>1.09</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1.22</v>
+      </c>
+      <c r="Z25">
+        <v>3.8</v>
+      </c>
+      <c r="AA25">
+        <v>1.85</v>
+      </c>
+      <c r="AB25">
+        <v>1.91</v>
+      </c>
+      <c r="AC25">
+        <v>3.22</v>
+      </c>
+      <c r="AD25">
+        <v>1.33</v>
+      </c>
+      <c r="AE25">
+        <v>1.1</v>
+      </c>
+      <c r="AF25">
+        <v>1.63</v>
+      </c>
+      <c r="AG25">
+        <v>2.14</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.38</v>
       </c>
-      <c r="W25">
-        <v>1.05</v>
-      </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>1.33</v>
-      </c>
-      <c r="Z25">
-        <v>3.25</v>
-      </c>
-      <c r="AA25">
-        <v>1.99</v>
-      </c>
-      <c r="AB25">
-        <v>1.71</v>
-      </c>
-      <c r="AC25">
-        <v>3.7</v>
-      </c>
-      <c r="AD25">
-        <v>1.27</v>
-      </c>
-      <c r="AE25">
-        <v>1.05</v>
-      </c>
-      <c r="AF25">
-        <v>1.8</v>
-      </c>
-      <c r="AG25">
-        <v>2</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.25</v>
-      </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q26">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
+        <v>1.25</v>
+      </c>
+      <c r="Z26">
+        <v>3.8</v>
+      </c>
+      <c r="AA26">
+        <v>1.85</v>
+      </c>
+      <c r="AB26">
+        <v>1.93</v>
+      </c>
+      <c r="AC26">
+        <v>3.32</v>
+      </c>
+      <c r="AD26">
+        <v>1.33</v>
+      </c>
+      <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
+        <v>1.65</v>
+      </c>
+      <c r="AG26">
+        <v>2.2</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.24</v>
       </c>
-      <c r="Z26">
-        <v>3.34</v>
-      </c>
-      <c r="AA26">
-        <v>1.88</v>
-      </c>
-      <c r="AB26">
-        <v>1.85</v>
-      </c>
-      <c r="AC26">
-        <v>3.08</v>
-      </c>
-      <c r="AD26">
-        <v>1.28</v>
-      </c>
-      <c r="AE26">
-        <v>1.06</v>
-      </c>
-      <c r="AF26">
-        <v>1.75</v>
-      </c>
-      <c r="AG26">
-        <v>2</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.28</v>
-      </c>
       <c r="AK26">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.88</v>
+        <v>1.61</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q27">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>3.8</v>
+        <v>4.54</v>
       </c>
       <c r="AA27">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AC27">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>1.32</v>
+        <v>2.14</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
+        <v>1.75</v>
+      </c>
+      <c r="O28">
+        <v>4</v>
+      </c>
+      <c r="P28">
+        <v>4.4</v>
+      </c>
+      <c r="Q28">
         <v>2.2</v>
       </c>
-      <c r="O28">
-        <v>3.25</v>
-      </c>
-      <c r="P28">
-        <v>2.88</v>
-      </c>
-      <c r="Q28">
-        <v>2.71</v>
-      </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB28">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG28">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q29">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA29">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AB29">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AG29">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
         <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="U30">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="V30">
         <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB30">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC30">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AK30">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>4.49</v>
+        <v>3.34</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
+        <v>1.75</v>
+      </c>
+      <c r="AG31">
+        <v>2</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.28</v>
+      </c>
+      <c r="AK31">
         <v>1.65</v>
-      </c>
-      <c r="AG31">
-        <v>2.1</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.17</v>
-      </c>
-      <c r="AK31">
-        <v>2.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>4.1</v>
       </c>
       <c r="P32">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="Q32">
         <v>2.11</v>
@@ -5543,13 +5543,13 @@
         <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="U32">
         <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5564,7 +5564,7 @@
         <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
         <v>2.1</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="Q33">
         <v>2.88</v>
@@ -5727,10 +5727,10 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
         <v>2.34</v>
@@ -5857,7 +5857,7 @@
         <v>4.55</v>
       </c>
       <c r="P34">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -5872,7 +5872,7 @@
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V34">
         <v>1.65</v>
@@ -6180,10 +6180,10 @@
         <v>4.1</v>
       </c>
       <c r="O36">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="O37">
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q37">
         <v>3.8</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U37">
         <v>3</v>
@@ -6370,28 +6370,28 @@
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA37">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AB37">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC37">
         <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
         <v>1.87</v>
@@ -6413,7 +6413,7 @@
         <v>1.65</v>
       </c>
       <c r="AK37">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="O38">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA38">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC38">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="AD38">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="O39">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="P39">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="Q39">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="R39">
+        <v>2.4</v>
+      </c>
+      <c r="S39">
+        <v>1.29</v>
+      </c>
+      <c r="T39">
+        <v>3.18</v>
+      </c>
+      <c r="U39">
+        <v>2.42</v>
+      </c>
+      <c r="V39">
+        <v>1.48</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.2</v>
+      </c>
+      <c r="Z39">
+        <v>3.9</v>
+      </c>
+      <c r="AA39">
+        <v>1.68</v>
+      </c>
+      <c r="AB39">
         <v>2.11</v>
       </c>
-      <c r="S39">
-        <v>1.32</v>
-      </c>
-      <c r="T39">
-        <v>3.02</v>
-      </c>
-      <c r="U39">
-        <v>2.48</v>
-      </c>
-      <c r="V39">
-        <v>1.46</v>
-      </c>
-      <c r="W39">
-        <v>1.07</v>
-      </c>
-      <c r="X39">
-        <v>1</v>
-      </c>
-      <c r="Y39">
-        <v>1.25</v>
-      </c>
-      <c r="Z39">
-        <v>3.8</v>
-      </c>
-      <c r="AA39">
-        <v>1.78</v>
-      </c>
-      <c r="AB39">
-        <v>1.93</v>
-      </c>
       <c r="AC39">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
         <v>2.16</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
+        <v>1.22</v>
+      </c>
+      <c r="AK39">
         <v>1.25</v>
-      </c>
-      <c r="AK39">
-        <v>1.32</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O40">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="P40">
-        <v>2.38</v>
+        <v>3.62</v>
       </c>
       <c r="Q40">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>1.04</v>
@@ -6883,10 +6883,10 @@
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="P41">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R41">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AB41">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AK41">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q42">
-        <v>2.54</v>
+        <v>3.99</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="U42">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
         <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,31 +7318,31 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O43">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="P43">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q43">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
         <v>1.08</v>
@@ -7354,16 +7354,16 @@
         <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD43">
         <v>1.36</v>
@@ -7372,10 +7372,10 @@
         <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
+        <v>1.23</v>
+      </c>
+      <c r="AK43">
         <v>1.27</v>
-      </c>
-      <c r="AK43">
-        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="P44">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q44">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R44">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="S44">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
         <v>2.26</v>
@@ -7508,37 +7508,37 @@
         <v>1.65</v>
       </c>
       <c r="W44">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA44">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB44">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AC44">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AD44">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O45">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="P45">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="Q45">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R45">
         <v>2.75</v>
       </c>
       <c r="S45">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T45">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="U45">
         <v>1.68</v>
       </c>
       <c r="V45">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="W45">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X45">
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z45">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA45">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB45">
         <v>4.4</v>
       </c>
       <c r="AC45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AD45">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AE45">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AF45">
         <v>1.18</v>
       </c>
       <c r="AG45">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK45">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="O46">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="P46">
-        <v>22.61</v>
+        <v>20</v>
       </c>
       <c r="Q46">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R46">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="S46">
         <v>1.14</v>
@@ -7828,10 +7828,10 @@
         <v>5.75</v>
       </c>
       <c r="U46">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="V46">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="W46">
         <v>1.25</v>
@@ -7840,31 +7840,31 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z46">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB46">
         <v>3.7</v>
       </c>
       <c r="AC46">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AD46">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF46">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1</v>
       </c>
       <c r="AK46">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.13</v>
+        <v>3.29</v>
       </c>
       <c r="O47">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="P47">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R47">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T47">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="U47">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z47">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA47">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB47">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AC47">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD47">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG47">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="O48">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="P48">
-        <v>13</v>
+        <v>19.25</v>
       </c>
       <c r="Q48">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R48">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="S48">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T48">
-        <v>4.45</v>
+        <v>6</v>
       </c>
       <c r="U48">
         <v>1.9</v>
       </c>
       <c r="V48">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="W48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z48">
         <v>8</v>
       </c>
       <c r="AA48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AB48">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC48">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD48">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AE48">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF48">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG48">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O49">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="P49">
-        <v>5.96</v>
+        <v>6.21</v>
       </c>
       <c r="Q49">
         <v>1.96</v>
       </c>
       <c r="R49">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="U49">
         <v>2.17</v>
       </c>
       <c r="V49">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8338,22 +8338,22 @@
         <v>1.43</v>
       </c>
       <c r="AB49">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AC49">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD49">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE49">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK49">
         <v>2.5</v>
@@ -8459,40 +8459,40 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q50">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
         <v>3.35</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="V50">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W50">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
         <v>5.5</v>
@@ -8501,22 +8501,22 @@
         <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AC50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,19 +8631,19 @@
         <v>2.24</v>
       </c>
       <c r="Q51">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T51">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="V51">
         <v>1.37</v>
@@ -8652,25 +8652,25 @@
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC51">
-        <v>3.87</v>
+        <v>3.68</v>
       </c>
       <c r="AD51">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
@@ -8679,7 +8679,7 @@
         <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P52">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Q52">
         <v>3.68</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -2926,25 +2926,25 @@
         <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
         <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2959,7 +2959,7 @@
         <v>1.5</v>
       </c>
       <c r="AB16">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC16">
         <v>2.38</v>
@@ -2971,7 +2971,7 @@
         <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
         <v>2.3</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
         <v>3.4</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,58 +4221,58 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P24">
+        <v>4.4</v>
+      </c>
+      <c r="Q24">
         <v>2.2</v>
       </c>
-      <c r="Q24">
-        <v>3.5</v>
-      </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V24">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB24">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>3.06</v>
+        <v>2.59</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
         <v>1.64</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="S25">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z25">
+        <v>3.25</v>
+      </c>
+      <c r="AA25">
+        <v>2.02</v>
+      </c>
+      <c r="AB25">
+        <v>1.67</v>
+      </c>
+      <c r="AC25">
         <v>3.8</v>
       </c>
-      <c r="AA25">
-        <v>1.85</v>
-      </c>
-      <c r="AB25">
-        <v>1.91</v>
-      </c>
-      <c r="AC25">
-        <v>3.22</v>
-      </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AG25">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O26">
         <v>3.35</v>
       </c>
       <c r="P26">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
         <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
         <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>3.32</v>
+        <v>3.06</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q27">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>4.54</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB27">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
+        <v>1.75</v>
+      </c>
+      <c r="AG27">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.28</v>
+      </c>
+      <c r="AK27">
         <v>1.65</v>
-      </c>
-      <c r="AG27">
-        <v>2.1</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.17</v>
-      </c>
-      <c r="AK27">
-        <v>2.14</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>3.36</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.32</v>
+        <v>2.86</v>
       </c>
       <c r="U28">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB28">
         <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
+        <v>1.4</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
+        <v>1.57</v>
+      </c>
+      <c r="AG28">
+        <v>2.38</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.4</v>
+      </c>
+      <c r="AK28">
         <v>1.39</v>
-      </c>
-      <c r="AE28">
-        <v>1.12</v>
-      </c>
-      <c r="AF28">
-        <v>1.64</v>
-      </c>
-      <c r="AG28">
-        <v>2.13</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.21</v>
-      </c>
-      <c r="AK28">
-        <v>1.97</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
+        <v>2.32</v>
+      </c>
+      <c r="Q29">
         <v>3</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
+        <v>2.09</v>
+      </c>
+      <c r="S29">
+        <v>1.3</v>
+      </c>
+      <c r="T29">
+        <v>3.05</v>
+      </c>
+      <c r="U29">
         <v>2.75</v>
       </c>
-      <c r="R29">
-        <v>2.01</v>
-      </c>
-      <c r="S29">
-        <v>1.36</v>
-      </c>
-      <c r="T29">
-        <v>2.85</v>
-      </c>
-      <c r="U29">
-        <v>3.1</v>
-      </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.04</v>
       </c>
       <c r="Y29">
+        <v>1.25</v>
+      </c>
+      <c r="Z29">
+        <v>3.8</v>
+      </c>
+      <c r="AA29">
+        <v>1.85</v>
+      </c>
+      <c r="AB29">
+        <v>1.93</v>
+      </c>
+      <c r="AC29">
+        <v>3.32</v>
+      </c>
+      <c r="AD29">
         <v>1.33</v>
       </c>
-      <c r="Z29">
-        <v>3.25</v>
-      </c>
-      <c r="AA29">
-        <v>2.02</v>
-      </c>
-      <c r="AB29">
-        <v>1.67</v>
-      </c>
-      <c r="AC29">
-        <v>3.8</v>
-      </c>
-      <c r="AD29">
-        <v>1.26</v>
-      </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q30">
-        <v>3.36</v>
+        <v>2.71</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T30">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U30">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA30">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB30">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK30">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
+        <v>1.61</v>
+      </c>
+      <c r="O31">
+        <v>4</v>
+      </c>
+      <c r="P31">
+        <v>4.6</v>
+      </c>
+      <c r="Q31">
         <v>2.05</v>
       </c>
-      <c r="O31">
-        <v>3.4</v>
-      </c>
-      <c r="P31">
-        <v>3.25</v>
-      </c>
-      <c r="Q31">
-        <v>2.51</v>
-      </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>3.34</v>
+        <v>4.54</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AC31">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O33">
         <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q33">
         <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5712,7 +5712,7 @@
         <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5733,7 +5733,7 @@
         <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD33">
         <v>1.5</v>
@@ -5857,13 +5857,13 @@
         <v>4.55</v>
       </c>
       <c r="P34">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="Q34">
         <v>2</v>
       </c>
       <c r="R34">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
         <v>1.2</v>
@@ -5872,13 +5872,13 @@
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="V34">
         <v>1.65</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK34">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O35">
         <v>4.5</v>
@@ -6023,7 +6023,7 @@
         <v>5.47</v>
       </c>
       <c r="Q35">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R35">
         <v>2.59</v>
@@ -6032,16 +6032,16 @@
         <v>1.17</v>
       </c>
       <c r="T35">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="U35">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="V35">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W35">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6068,7 +6068,7 @@
         <v>1.33</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG35">
         <v>2.38</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W36">
         <v>1.12</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P37">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="Q37">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="R37">
         <v>2.07</v>
       </c>
       <c r="S37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="U37">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
+        <v>1.26</v>
+      </c>
+      <c r="Z37">
+        <v>3.2</v>
+      </c>
+      <c r="AA37">
+        <v>1.91</v>
+      </c>
+      <c r="AB37">
+        <v>1.83</v>
+      </c>
+      <c r="AC37">
+        <v>3.08</v>
+      </c>
+      <c r="AD37">
         <v>1.28</v>
       </c>
-      <c r="Z37">
-        <v>3.05</v>
-      </c>
-      <c r="AA37">
-        <v>1.99</v>
-      </c>
-      <c r="AB37">
+      <c r="AE37">
+        <v>1.07</v>
+      </c>
+      <c r="AF37">
         <v>1.76</v>
       </c>
-      <c r="AC37">
-        <v>3.34</v>
-      </c>
-      <c r="AD37">
-        <v>1.24</v>
-      </c>
-      <c r="AE37">
-        <v>1.06</v>
-      </c>
-      <c r="AF37">
-        <v>1.87</v>
-      </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>2.75</v>
+        <v>3.62</v>
       </c>
       <c r="Q38">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="R38">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S38">
         <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB38">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG38">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.48</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
-        <v>3.95</v>
+        <v>3.43</v>
       </c>
       <c r="P39">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AB39">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="O40">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="P40">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q40">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="R40">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U40">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="V40">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
         <v>1.08</v>
@@ -6862,31 +6862,31 @@
         <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA40">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="O41">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="P41">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="Q41">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="R41">
+        <v>2.33</v>
+      </c>
+      <c r="S41">
+        <v>1.28</v>
+      </c>
+      <c r="T41">
+        <v>3.22</v>
+      </c>
+      <c r="U41">
+        <v>2.42</v>
+      </c>
+      <c r="V41">
+        <v>1.48</v>
+      </c>
+      <c r="W41">
+        <v>1.08</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>1.2</v>
+      </c>
+      <c r="Z41">
+        <v>3.92</v>
+      </c>
+      <c r="AA41">
+        <v>1.68</v>
+      </c>
+      <c r="AB41">
+        <v>2.11</v>
+      </c>
+      <c r="AC41">
+        <v>2.59</v>
+      </c>
+      <c r="AD41">
+        <v>1.42</v>
+      </c>
+      <c r="AE41">
+        <v>1.12</v>
+      </c>
+      <c r="AF41">
+        <v>1.64</v>
+      </c>
+      <c r="AG41">
         <v>2.1</v>
       </c>
-      <c r="S41">
-        <v>1.33</v>
-      </c>
-      <c r="T41">
-        <v>3</v>
-      </c>
-      <c r="U41">
-        <v>2.67</v>
-      </c>
-      <c r="V41">
-        <v>1.4</v>
-      </c>
-      <c r="W41">
-        <v>1.07</v>
-      </c>
-      <c r="X41">
-        <v>1.04</v>
-      </c>
-      <c r="Y41">
-        <v>1.25</v>
-      </c>
-      <c r="Z41">
-        <v>3.8</v>
-      </c>
-      <c r="AA41">
-        <v>1.87</v>
-      </c>
-      <c r="AB41">
-        <v>1.9</v>
-      </c>
-      <c r="AC41">
-        <v>3.1</v>
-      </c>
-      <c r="AD41">
-        <v>1.36</v>
-      </c>
-      <c r="AE41">
-        <v>1.1</v>
-      </c>
-      <c r="AF41">
-        <v>1.67</v>
-      </c>
-      <c r="AG41">
-        <v>2.08</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
-        <v>3.99</v>
+        <v>2.64</v>
       </c>
       <c r="R42">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V42">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
         <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AA42">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7321,61 +7321,61 @@
         <v>3.25</v>
       </c>
       <c r="O43">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q43">
-        <v>3.7</v>
+        <v>3.99</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
         <v>1.31</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="U43">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
         <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
         <v>1.99</v>
       </c>
       <c r="AC43">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
         <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.45</v>
+        <v>1.11</v>
       </c>
       <c r="O45">
-        <v>4.33</v>
+        <v>10</v>
       </c>
       <c r="P45">
-        <v>2.44</v>
+        <v>20</v>
       </c>
       <c r="Q45">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="R45">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="S45">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U45">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="V45">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="W45">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.05</v>
       </c>
       <c r="Z45">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA45">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AB45">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AC45">
+        <v>1.71</v>
+      </c>
+      <c r="AD45">
+        <v>2.05</v>
+      </c>
+      <c r="AE45">
         <v>1.44</v>
       </c>
-      <c r="AD45">
-        <v>2.63</v>
-      </c>
-      <c r="AE45">
-        <v>1.76</v>
-      </c>
       <c r="AF45">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AG45">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>7.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="O46">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="P46">
-        <v>20</v>
+        <v>19.25</v>
       </c>
       <c r="Q46">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="R46">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="S46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T46">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V46">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="W46">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z46">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA46">
         <v>1.22</v>
       </c>
       <c r="AB46">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AC46">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD46">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF46">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AG46">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK46">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.29</v>
+        <v>1.54</v>
       </c>
       <c r="O47">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="P47">
-        <v>2.1</v>
+        <v>6.21</v>
       </c>
       <c r="Q47">
-        <v>3.54</v>
+        <v>1.96</v>
       </c>
       <c r="R47">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="S47">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="U47">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V47">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W47">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z47">
         <v>6</v>
       </c>
       <c r="AA47">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB47">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AC47">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD47">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AE47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF47">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.12</v>
+        <v>3.29</v>
       </c>
       <c r="O48">
-        <v>9.5</v>
+        <v>3.95</v>
       </c>
       <c r="P48">
-        <v>19.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q48">
-        <v>1.42</v>
+        <v>3.54</v>
       </c>
       <c r="R48">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="S48">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="T48">
+        <v>4.05</v>
+      </c>
+      <c r="U48">
+        <v>2.1</v>
+      </c>
+      <c r="V48">
+        <v>1.77</v>
+      </c>
+      <c r="W48">
+        <v>1.21</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.08</v>
+      </c>
+      <c r="Z48">
         <v>6</v>
       </c>
-      <c r="U48">
-        <v>1.9</v>
-      </c>
-      <c r="V48">
-        <v>2.04</v>
-      </c>
-      <c r="W48">
-        <v>1.3</v>
-      </c>
-      <c r="X48">
-        <v>1</v>
-      </c>
-      <c r="Y48">
-        <v>1.02</v>
-      </c>
-      <c r="Z48">
-        <v>8</v>
-      </c>
       <c r="AA48">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AB48">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="AC48">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AD48">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AE48">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AF48">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="AG48">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>6</v>
+        <v>1.36</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,77 +8296,77 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O49">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P49">
-        <v>6.21</v>
+        <v>5.75</v>
       </c>
       <c r="Q49">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="R49">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="S49">
         <v>1.22</v>
       </c>
       <c r="T49">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="U49">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="V49">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W49">
+        <v>1.18</v>
+      </c>
+      <c r="X49">
+        <v>1.02</v>
+      </c>
+      <c r="Y49">
+        <v>1.12</v>
+      </c>
+      <c r="Z49">
+        <v>5.5</v>
+      </c>
+      <c r="AA49">
+        <v>1.5</v>
+      </c>
+      <c r="AB49">
+        <v>2.49</v>
+      </c>
+      <c r="AC49">
+        <v>2.25</v>
+      </c>
+      <c r="AD49">
+        <v>1.6</v>
+      </c>
+      <c r="AE49">
+        <v>1.22</v>
+      </c>
+      <c r="AF49">
+        <v>1.58</v>
+      </c>
+      <c r="AG49">
+        <v>2.38</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.17</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.11</v>
-      </c>
-      <c r="Z49">
-        <v>6</v>
-      </c>
-      <c r="AA49">
-        <v>1.43</v>
-      </c>
-      <c r="AB49">
-        <v>2.75</v>
-      </c>
-      <c r="AC49">
-        <v>2.04</v>
-      </c>
-      <c r="AD49">
-        <v>1.73</v>
-      </c>
-      <c r="AE49">
-        <v>1.28</v>
-      </c>
-      <c r="AF49">
-        <v>1.55</v>
-      </c>
-      <c r="AG49">
-        <v>2.4</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.1</v>
       </c>
       <c r="AK49">
         <v>2.5</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="O50">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P50">
-        <v>5.75</v>
+        <v>2.44</v>
       </c>
       <c r="Q50">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="R50">
+        <v>2.75</v>
+      </c>
+      <c r="S50">
+        <v>1.12</v>
+      </c>
+      <c r="T50">
+        <v>6</v>
+      </c>
+      <c r="U50">
+        <v>1.68</v>
+      </c>
+      <c r="V50">
+        <v>2.26</v>
+      </c>
+      <c r="W50">
+        <v>1.43</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
+        <v>1.05</v>
+      </c>
+      <c r="Z50">
+        <v>11</v>
+      </c>
+      <c r="AA50">
+        <v>1.18</v>
+      </c>
+      <c r="AB50">
+        <v>4.4</v>
+      </c>
+      <c r="AC50">
+        <v>1.44</v>
+      </c>
+      <c r="AD50">
         <v>2.63</v>
       </c>
-      <c r="S50">
-        <v>1.22</v>
-      </c>
-      <c r="T50">
-        <v>3.35</v>
-      </c>
-      <c r="U50">
-        <v>2.11</v>
-      </c>
-      <c r="V50">
-        <v>1.71</v>
-      </c>
-      <c r="W50">
+      <c r="AE50">
+        <v>1.76</v>
+      </c>
+      <c r="AF50">
         <v>1.18</v>
       </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
-        <v>1.12</v>
-      </c>
-      <c r="Z50">
-        <v>5.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.5</v>
-      </c>
-      <c r="AB50">
-        <v>2.49</v>
-      </c>
-      <c r="AC50">
-        <v>2.25</v>
-      </c>
-      <c r="AD50">
-        <v>1.6</v>
-      </c>
-      <c r="AE50">
-        <v>1.22</v>
-      </c>
-      <c r="AF50">
-        <v>1.58</v>
-      </c>
       <c r="AG50">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1113,14 +1113,14 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79", "90+2"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "43"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,130 +1590,130 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
         <v>2.35</v>
       </c>
       <c r="O8">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P8">
         <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="R8">
         <v>1.79</v>
       </c>
       <c r="S8">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T8">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="U8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="V8">
         <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y8">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z8">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AA8">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AB8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8">
         <v>5.5</v>
       </c>
       <c r="AD8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
         <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "40", "90+5"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "85"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1756,13 +1756,13 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1772,68 +1772,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="O9">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="P9">
         <v>1.37</v>
       </c>
       <c r="Q9">
-        <v>6.09</v>
+        <v>6.47</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="U9">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
+        <v>1.34</v>
+      </c>
+      <c r="Z9">
+        <v>3.25</v>
+      </c>
+      <c r="AA9">
+        <v>2</v>
+      </c>
+      <c r="AB9">
+        <v>1.82</v>
+      </c>
+      <c r="AC9">
+        <v>3.34</v>
+      </c>
+      <c r="AD9">
+        <v>1.27</v>
+      </c>
+      <c r="AE9">
         <v>1.07</v>
       </c>
-      <c r="Y9">
-        <v>1.45</v>
-      </c>
-      <c r="Z9">
-        <v>2.74</v>
-      </c>
-      <c r="AA9">
-        <v>2.17</v>
-      </c>
-      <c r="AB9">
-        <v>1.59</v>
-      </c>
-      <c r="AC9">
-        <v>3.96</v>
-      </c>
-      <c r="AD9">
-        <v>1.17</v>
-      </c>
-      <c r="AE9">
-        <v>1.02</v>
-      </c>
       <c r="AF9">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG9">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1842,11 +1842,11 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
         <v>1.06</v>
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1935,23 +1935,23 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O10">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="R10">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1972,35 +1972,35 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA10">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="AD10">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2012,34 +2012,34 @@
         <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.98</v>
+        <v>6.24</v>
       </c>
       <c r="O11">
         <v>5</v>
@@ -2111,55 +2111,55 @@
         <v>1.35</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="R11">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="S11">
+        <v>1.2</v>
+      </c>
+      <c r="T11">
+        <v>4</v>
+      </c>
+      <c r="U11">
+        <v>2.3</v>
+      </c>
+      <c r="V11">
+        <v>1.6</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.12</v>
+      </c>
+      <c r="Z11">
+        <v>5.18</v>
+      </c>
+      <c r="AA11">
+        <v>1.52</v>
+      </c>
+      <c r="AB11">
+        <v>2.5</v>
+      </c>
+      <c r="AC11">
+        <v>2.4</v>
+      </c>
+      <c r="AD11">
+        <v>1.57</v>
+      </c>
+      <c r="AE11">
         <v>1.18</v>
       </c>
-      <c r="T11">
-        <v>4.5</v>
-      </c>
-      <c r="U11">
-        <v>2.02</v>
-      </c>
-      <c r="V11">
-        <v>1.68</v>
-      </c>
-      <c r="W11">
-        <v>1.15</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>1.08</v>
-      </c>
-      <c r="Z11">
-        <v>5.7</v>
-      </c>
-      <c r="AA11">
-        <v>1.36</v>
-      </c>
-      <c r="AB11">
-        <v>2.7</v>
-      </c>
-      <c r="AC11">
-        <v>2.03</v>
-      </c>
-      <c r="AD11">
-        <v>1.73</v>
-      </c>
-      <c r="AE11">
-        <v>1.27</v>
-      </c>
       <c r="AF11">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O12">
         <v>4.5</v>
@@ -2277,46 +2277,46 @@
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="U12">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V12">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z12">
         <v>5.4</v>
       </c>
       <c r="AA12">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
         <v>2.62</v>
       </c>
       <c r="AC12">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD12">
         <v>1.69</v>
       </c>
       <c r="AE12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
         <v>1.57</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,16 +2431,16 @@
         <v>9.17</v>
       </c>
       <c r="O13">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="P13">
         <v>1.3</v>
       </c>
       <c r="Q13">
-        <v>5.61</v>
+        <v>6.47</v>
       </c>
       <c r="R13">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S13">
         <v>1.23</v>
@@ -2449,7 +2449,7 @@
         <v>4.33</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="V13">
         <v>1.75</v>
@@ -2473,19 +2473,19 @@
         <v>2.62</v>
       </c>
       <c r="AC13">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AD13">
         <v>1.69</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
         <v>1.78</v>
       </c>
       <c r="AG13">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P14">
+        <v>2.12</v>
+      </c>
+      <c r="Q14">
+        <v>4.2</v>
+      </c>
+      <c r="R14">
+        <v>1.82</v>
+      </c>
+      <c r="S14">
+        <v>1.5</v>
+      </c>
+      <c r="T14">
+        <v>2.27</v>
+      </c>
+      <c r="U14">
+        <v>3.6</v>
+      </c>
+      <c r="V14">
+        <v>1.25</v>
+      </c>
+      <c r="W14">
+        <v>1.02</v>
+      </c>
+      <c r="X14">
+        <v>1.07</v>
+      </c>
+      <c r="Y14">
+        <v>1.5</v>
+      </c>
+      <c r="Z14">
         <v>2.4</v>
       </c>
-      <c r="Q14">
-        <v>3.24</v>
-      </c>
-      <c r="R14">
-        <v>1.92</v>
-      </c>
-      <c r="S14">
-        <v>1.42</v>
-      </c>
-      <c r="T14">
-        <v>2.51</v>
-      </c>
-      <c r="U14">
-        <v>2.92</v>
-      </c>
-      <c r="V14">
-        <v>1.34</v>
-      </c>
-      <c r="W14">
-        <v>1.04</v>
-      </c>
-      <c r="X14">
-        <v>1.06</v>
-      </c>
-      <c r="Y14">
-        <v>1.4</v>
-      </c>
-      <c r="Z14">
-        <v>2.88</v>
-      </c>
       <c r="AA14">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="AB14">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AC14">
-        <v>3.98</v>
+        <v>4.85</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG14">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>6.04</v>
+        <v>6.75</v>
       </c>
       <c r="O15">
         <v>3.9</v>
       </c>
       <c r="P15">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q15">
-        <v>5.51</v>
+        <v>8.35</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T15">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U15">
         <v>3</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
+        <v>1.07</v>
+      </c>
+      <c r="X15">
         <v>1.03</v>
       </c>
-      <c r="X15">
-        <v>1.06</v>
-      </c>
       <c r="Y15">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA15">
+        <v>2</v>
+      </c>
+      <c r="AB15">
+        <v>1.73</v>
+      </c>
+      <c r="AC15">
+        <v>3.78</v>
+      </c>
+      <c r="AD15">
+        <v>1.27</v>
+      </c>
+      <c r="AE15">
+        <v>1.05</v>
+      </c>
+      <c r="AF15">
         <v>2.2</v>
       </c>
-      <c r="AB15">
-        <v>1.65</v>
-      </c>
-      <c r="AC15">
-        <v>3.82</v>
-      </c>
-      <c r="AD15">
-        <v>1.25</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>2.38</v>
-      </c>
       <c r="AG15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AK15">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,49 +2926,49 @@
         <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="R16">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T16">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="V16">
         <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA16">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB16">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC16">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AD16">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O17">
-        <v>4.99</v>
+        <v>4.71</v>
       </c>
       <c r="P17">
-        <v>6.72</v>
+        <v>5.86</v>
       </c>
       <c r="Q17">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="R17">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
         <v>1.2</v>
@@ -3101,43 +3101,43 @@
         <v>4</v>
       </c>
       <c r="U17">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="AA17">
         <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AC17">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AD17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
         <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="P18">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="Q18">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R18">
         <v>2.5</v>
@@ -3261,40 +3261,40 @@
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB18">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AC18">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD18">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AE18">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF18">
         <v>1.36</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
+        <v>1.15</v>
+      </c>
+      <c r="AK18">
         <v>1.22</v>
-      </c>
-      <c r="AK18">
-        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,22 +3409,22 @@
         <v>1.91</v>
       </c>
       <c r="O19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
         <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="U19">
         <v>2.8</v>
@@ -3436,7 +3436,7 @@
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19">
         <v>1.22</v>
@@ -3445,25 +3445,25 @@
         <v>2.63</v>
       </c>
       <c r="AA19">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC19">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
         <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -3578,10 +3578,10 @@
         <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R20">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
         <v>1.36</v>
@@ -3611,10 +3611,10 @@
         <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD20">
         <v>1.3</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
         <v>5.5</v>
       </c>
       <c r="Q21">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="S21">
         <v>1.22</v>
@@ -3759,16 +3759,16 @@
         <v>1.66</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>1.5</v>
@@ -3777,7 +3777,7 @@
         <v>2.5</v>
       </c>
       <c r="AC21">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AD21">
         <v>1.61</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK21">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="P22">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="Q22">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="R22">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
         <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="U22">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA22">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AB22">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC22">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
         <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG22">
         <v>1.9</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O23">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>3.18</v>
+        <v>3.83</v>
       </c>
       <c r="R23">
+        <v>2.24</v>
+      </c>
+      <c r="S23">
+        <v>1.25</v>
+      </c>
+      <c r="T23">
+        <v>3.6</v>
+      </c>
+      <c r="U23">
+        <v>2.4</v>
+      </c>
+      <c r="V23">
+        <v>1.53</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.2</v>
+      </c>
+      <c r="Z23">
+        <v>4.56</v>
+      </c>
+      <c r="AA23">
+        <v>1.64</v>
+      </c>
+      <c r="AB23">
         <v>2.16</v>
       </c>
-      <c r="S23">
-        <v>1.29</v>
-      </c>
-      <c r="T23">
-        <v>3.3</v>
-      </c>
-      <c r="U23">
-        <v>2.55</v>
-      </c>
-      <c r="V23">
-        <v>1.45</v>
-      </c>
-      <c r="W23">
-        <v>1.08</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1.22</v>
-      </c>
-      <c r="Z23">
-        <v>4.26</v>
-      </c>
-      <c r="AA23">
-        <v>1.75</v>
-      </c>
-      <c r="AB23">
-        <v>2.05</v>
-      </c>
       <c r="AC23">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AK23">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="U24">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
+        <v>2.04</v>
+      </c>
+      <c r="AB24">
         <v>1.67</v>
       </c>
-      <c r="AB24">
-        <v>2.05</v>
-      </c>
       <c r="AC24">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="AD24">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="R25">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1.04</v>
       </c>
       <c r="Y25">
+        <v>1.2</v>
+      </c>
+      <c r="Z25">
+        <v>3.8</v>
+      </c>
+      <c r="AA25">
+        <v>1.9</v>
+      </c>
+      <c r="AB25">
+        <v>1.95</v>
+      </c>
+      <c r="AC25">
+        <v>3</v>
+      </c>
+      <c r="AD25">
         <v>1.33</v>
       </c>
-      <c r="Z25">
-        <v>3.25</v>
-      </c>
-      <c r="AA25">
-        <v>2.02</v>
-      </c>
-      <c r="AB25">
-        <v>1.67</v>
-      </c>
-      <c r="AC25">
-        <v>3.8</v>
-      </c>
-      <c r="AD25">
-        <v>1.26</v>
-      </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
+        <v>2.72</v>
+      </c>
+      <c r="O26">
+        <v>3.28</v>
+      </c>
+      <c r="P26">
+        <v>2.42</v>
+      </c>
+      <c r="Q26">
         <v>3.1</v>
       </c>
-      <c r="O26">
-        <v>3.35</v>
-      </c>
-      <c r="P26">
-        <v>2.2</v>
-      </c>
-      <c r="Q26">
-        <v>3.5</v>
-      </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U26">
         <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
         <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
         <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="AD26">
+        <v>1.33</v>
+      </c>
+      <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
+        <v>1.65</v>
+      </c>
+      <c r="AG26">
+        <v>2.2</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.27</v>
+      </c>
+      <c r="AK26">
         <v>1.36</v>
-      </c>
-      <c r="AE26">
-        <v>1.08</v>
-      </c>
-      <c r="AF26">
-        <v>1.64</v>
-      </c>
-      <c r="AG26">
-        <v>2.13</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.6</v>
-      </c>
-      <c r="AK26">
-        <v>1.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P27">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>2.51</v>
+        <v>2.85</v>
       </c>
       <c r="R27">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
+        <v>1.31</v>
+      </c>
+      <c r="T27">
+        <v>3.08</v>
+      </c>
+      <c r="U27">
+        <v>2.42</v>
+      </c>
+      <c r="V27">
+        <v>1.48</v>
+      </c>
+      <c r="W27">
+        <v>1.09</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1.22</v>
+      </c>
+      <c r="Z27">
+        <v>3.6</v>
+      </c>
+      <c r="AA27">
+        <v>1.85</v>
+      </c>
+      <c r="AB27">
+        <v>1.89</v>
+      </c>
+      <c r="AC27">
+        <v>3.22</v>
+      </c>
+      <c r="AD27">
         <v>1.33</v>
       </c>
-      <c r="T27">
-        <v>3.01</v>
-      </c>
-      <c r="U27">
-        <v>2.62</v>
-      </c>
-      <c r="V27">
-        <v>1.4</v>
-      </c>
-      <c r="W27">
-        <v>1.06</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>1.24</v>
-      </c>
-      <c r="Z27">
-        <v>3.34</v>
-      </c>
-      <c r="AA27">
-        <v>1.88</v>
-      </c>
-      <c r="AB27">
-        <v>1.85</v>
-      </c>
-      <c r="AC27">
-        <v>3.08</v>
-      </c>
-      <c r="AD27">
-        <v>1.28</v>
-      </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q28">
-        <v>3.36</v>
+        <v>1.99</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T28">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W28">
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>3.9</v>
+        <v>4.65</v>
       </c>
       <c r="AA28">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG28">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P29">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="R29">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA29">
+        <v>1.88</v>
+      </c>
+      <c r="AB29">
         <v>1.85</v>
       </c>
-      <c r="AB29">
-        <v>1.93</v>
-      </c>
       <c r="AC29">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
+        <v>1.67</v>
+      </c>
+      <c r="AG29">
+        <v>2</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.28</v>
+      </c>
+      <c r="AK29">
         <v>1.65</v>
-      </c>
-      <c r="AG29">
-        <v>2.2</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.24</v>
-      </c>
-      <c r="AK29">
-        <v>1.35</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>2.71</v>
+        <v>3.38</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S30">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="U30">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
         <v>3.8</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB30">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AC30">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AK30">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
         <v>4</v>
@@ -5395,7 +5395,7 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
         <v>4.54</v>
@@ -5410,13 +5410,13 @@
         <v>2.65</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE31">
         <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
         <v>2.1</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK31">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,22 +5525,22 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O32">
         <v>4.1</v>
       </c>
       <c r="P32">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q32">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
         <v>3.26</v>
@@ -5555,13 +5555,13 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
         <v>1.83</v>
@@ -5570,19 +5570,19 @@
         <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5709,7 +5709,7 @@
         <v>3.6</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V33">
         <v>1.58</v>
@@ -5727,25 +5727,25 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
+        <v>2.27</v>
+      </c>
+      <c r="AC33">
         <v>2.38</v>
-      </c>
-      <c r="AC33">
-        <v>2.35</v>
       </c>
       <c r="AD33">
         <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG33">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O34">
         <v>4.55</v>
       </c>
       <c r="P34">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U34">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="V34">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="W34">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z34">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA34">
+        <v>1.36</v>
+      </c>
+      <c r="AB34">
+        <v>3.1</v>
+      </c>
+      <c r="AC34">
+        <v>1.93</v>
+      </c>
+      <c r="AD34">
+        <v>1.87</v>
+      </c>
+      <c r="AE34">
+        <v>1.36</v>
+      </c>
+      <c r="AF34">
         <v>1.44</v>
       </c>
-      <c r="AB34">
-        <v>2.7</v>
-      </c>
-      <c r="AC34">
-        <v>2.15</v>
-      </c>
-      <c r="AD34">
-        <v>1.67</v>
-      </c>
-      <c r="AE34">
-        <v>1.29</v>
-      </c>
-      <c r="AF34">
-        <v>1.53</v>
-      </c>
       <c r="AG34">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.13</v>
       </c>
       <c r="AK34">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O35">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P35">
-        <v>5.47</v>
+        <v>6.05</v>
       </c>
       <c r="Q35">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R35">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="S35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T35">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="U35">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="V35">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W35">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z35">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA35">
+        <v>1.32</v>
+      </c>
+      <c r="AB35">
+        <v>2.92</v>
+      </c>
+      <c r="AC35">
+        <v>1.87</v>
+      </c>
+      <c r="AD35">
+        <v>1.88</v>
+      </c>
+      <c r="AE35">
         <v>1.4</v>
-      </c>
-      <c r="AB35">
-        <v>2.88</v>
-      </c>
-      <c r="AC35">
-        <v>2</v>
-      </c>
-      <c r="AD35">
-        <v>1.8</v>
-      </c>
-      <c r="AE35">
-        <v>1.33</v>
       </c>
       <c r="AF35">
         <v>1.47</v>
       </c>
       <c r="AG35">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK35">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
+        <v>4.4</v>
+      </c>
+      <c r="O36">
         <v>4.1</v>
       </c>
-      <c r="O36">
-        <v>3.9</v>
-      </c>
       <c r="P36">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="Q36">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
         <v>1.23</v>
@@ -6198,28 +6198,28 @@
         <v>3.48</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V36">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W36">
         <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB36">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
         <v>2.27</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O37">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q37">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="R37">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="S37">
         <v>1.36</v>
@@ -6367,37 +6367,37 @@
         <v>1.41</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA37">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB37">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD37">
         <v>1.28</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="P38">
-        <v>3.62</v>
+        <v>2.05</v>
       </c>
       <c r="Q38">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="R38">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
         <v>1.08</v>
@@ -6539,28 +6539,28 @@
         <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA38">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE38">
         <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="P39">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q39">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S39">
         <v>1.33</v>
@@ -6687,7 +6687,7 @@
         <v>3</v>
       </c>
       <c r="U39">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="V39">
         <v>1.4</v>
@@ -6711,13 +6711,13 @@
         <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
         <v>1.67</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="O40">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R40">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S40">
+        <v>1.4</v>
+      </c>
+      <c r="T40">
+        <v>2.67</v>
+      </c>
+      <c r="U40">
+        <v>3</v>
+      </c>
+      <c r="V40">
+        <v>1.33</v>
+      </c>
+      <c r="W40">
+        <v>1.05</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.35</v>
+      </c>
+      <c r="Z40">
+        <v>2.87</v>
+      </c>
+      <c r="AA40">
+        <v>1.98</v>
+      </c>
+      <c r="AB40">
+        <v>1.7</v>
+      </c>
+      <c r="AC40">
+        <v>3.34</v>
+      </c>
+      <c r="AD40">
+        <v>1.29</v>
+      </c>
+      <c r="AE40">
+        <v>1.08</v>
+      </c>
+      <c r="AF40">
+        <v>1.74</v>
+      </c>
+      <c r="AG40">
+        <v>1.95</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.31</v>
       </c>
-      <c r="T40">
-        <v>3.08</v>
-      </c>
-      <c r="U40">
-        <v>2.76</v>
-      </c>
-      <c r="V40">
-        <v>1.45</v>
-      </c>
-      <c r="W40">
-        <v>1.08</v>
-      </c>
-      <c r="X40">
-        <v>1.04</v>
-      </c>
-      <c r="Y40">
-        <v>1.22</v>
-      </c>
-      <c r="Z40">
-        <v>3.7</v>
-      </c>
-      <c r="AA40">
-        <v>1.76</v>
-      </c>
-      <c r="AB40">
-        <v>1.99</v>
-      </c>
-      <c r="AC40">
-        <v>2.78</v>
-      </c>
-      <c r="AD40">
-        <v>1.37</v>
-      </c>
-      <c r="AE40">
-        <v>1.1</v>
-      </c>
-      <c r="AF40">
-        <v>1.65</v>
-      </c>
-      <c r="AG40">
-        <v>2.2</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.23</v>
-      </c>
       <c r="AK40">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="O41">
         <v>4</v>
       </c>
       <c r="P41">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q41">
         <v>4.33</v>
       </c>
       <c r="R41">
+        <v>2.42</v>
+      </c>
+      <c r="S41">
+        <v>1.24</v>
+      </c>
+      <c r="T41">
+        <v>3.4</v>
+      </c>
+      <c r="U41">
+        <v>2.3</v>
+      </c>
+      <c r="V41">
+        <v>1.58</v>
+      </c>
+      <c r="W41">
+        <v>1.11</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.17</v>
+      </c>
+      <c r="Z41">
+        <v>4.4</v>
+      </c>
+      <c r="AA41">
+        <v>1.57</v>
+      </c>
+      <c r="AB41">
+        <v>2.31</v>
+      </c>
+      <c r="AC41">
         <v>2.33</v>
       </c>
-      <c r="S41">
-        <v>1.28</v>
-      </c>
-      <c r="T41">
-        <v>3.22</v>
-      </c>
-      <c r="U41">
-        <v>2.42</v>
-      </c>
-      <c r="V41">
-        <v>1.48</v>
-      </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
+      <c r="AD41">
+        <v>1.52</v>
+      </c>
+      <c r="AE41">
         <v>1.2</v>
       </c>
-      <c r="Z41">
-        <v>3.92</v>
-      </c>
-      <c r="AA41">
-        <v>1.68</v>
-      </c>
-      <c r="AB41">
-        <v>2.11</v>
-      </c>
-      <c r="AC41">
-        <v>2.59</v>
-      </c>
-      <c r="AD41">
-        <v>1.42</v>
-      </c>
-      <c r="AE41">
-        <v>1.12</v>
-      </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AK41">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q42">
-        <v>2.64</v>
+        <v>3.99</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="U42">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
         <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
         <v>3.45</v>
       </c>
       <c r="P43">
-        <v>2.12</v>
+        <v>3.62</v>
       </c>
       <c r="Q43">
-        <v>3.99</v>
+        <v>2.45</v>
       </c>
       <c r="R43">
         <v>2.12</v>
       </c>
       <c r="S43">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U43">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
         <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
         <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7496,49 +7496,49 @@
         <v>2.41</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U44">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="V44">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W44">
         <v>1.17</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z44">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA44">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB44">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC44">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD44">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE44">
         <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="O45">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="P45">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q45">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="R45">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="S45">
         <v>1.14</v>
       </c>
       <c r="T45">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="U45">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V45">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="W45">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7683,25 +7683,25 @@
         <v>8.5</v>
       </c>
       <c r="AA45">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AB45">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AC45">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD45">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AE45">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF45">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK45">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>19.25</v>
       </c>
       <c r="Q46">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R46">
         <v>3.4</v>
       </c>
       <c r="S46">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="U46">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="V46">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="W46">
         <v>1.3</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z46">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA46">
         <v>1.22</v>
       </c>
       <c r="AB46">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AC46">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD46">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE46">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF46">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG46">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7973,25 +7973,25 @@
         <v>1.54</v>
       </c>
       <c r="O47">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P47">
         <v>6.21</v>
       </c>
       <c r="Q47">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R47">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="S47">
         <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="U47">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="V47">
         <v>1.65</v>
@@ -8009,13 +8009,13 @@
         <v>6</v>
       </c>
       <c r="AA47">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB47">
         <v>2.75</v>
       </c>
       <c r="AC47">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AD47">
         <v>1.73</v>
@@ -8024,7 +8024,7 @@
         <v>1.28</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
         <v>2.4</v>
@@ -8142,10 +8142,10 @@
         <v>2.1</v>
       </c>
       <c r="Q48">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="R48">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="S48">
         <v>1.21</v>
@@ -8154,7 +8154,7 @@
         <v>4.05</v>
       </c>
       <c r="U48">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V48">
         <v>1.77</v>
@@ -8166,7 +8166,7 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
         <v>6</v>
@@ -8190,7 +8190,7 @@
         <v>1.39</v>
       </c>
       <c r="AG48">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8305,31 +8305,31 @@
         <v>5.75</v>
       </c>
       <c r="Q49">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="R49">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S49">
         <v>1.22</v>
       </c>
       <c r="T49">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="V49">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="W49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
         <v>5.5</v>
@@ -8338,22 +8338,22 @@
         <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AC49">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AD49">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE49">
         <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.17</v>
       </c>
       <c r="AK49">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>2.44</v>
       </c>
       <c r="Q50">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
         <v>2.75</v>
@@ -8480,16 +8480,16 @@
         <v>6</v>
       </c>
       <c r="U50">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="V50">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="W50">
         <v>1.43</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.05</v>
@@ -8504,10 +8504,10 @@
         <v>4.4</v>
       </c>
       <c r="AC50">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD50">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AE50">
         <v>1.76</v>
@@ -8640,19 +8640,19 @@
         <v>1.39</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="U51">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="V51">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
         <v>1.36</v>
@@ -8664,19 +8664,19 @@
         <v>2.15</v>
       </c>
       <c r="AB51">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC51">
         <v>3.68</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
         <v>1.85</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O52">
         <v>2.95</v>
       </c>
       <c r="P52">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q52">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="R52">
         <v>2</v>
@@ -8809,7 +8809,7 @@
         <v>3.1</v>
       </c>
       <c r="V52">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W52">
         <v>1.06</v>
@@ -8818,28 +8818,28 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z52">
-        <v>2.74</v>
+        <v>3.01</v>
       </c>
       <c r="AA52">
         <v>2.2</v>
       </c>
       <c r="AB52">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC52">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AD52">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
         <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
         <v>1.9</v>

--- a/jogos_2026-10-20.xlsx
+++ b/jogos_2026-10-20.xlsx
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2094,11 +2094,11 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,130 +2242,130 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O12">
-        <v>4.5</v>
+        <v>4.74</v>
       </c>
       <c r="P12">
         <v>4.9</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R12">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="S12">
         <v>1.2</v>
       </c>
       <c r="T12">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="U12">
         <v>2.28</v>
       </c>
       <c r="V12">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF12">
+        <v>1.53</v>
+      </c>
+      <c r="AG12">
+        <v>2.4</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>["4", "11"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>["15", "90"]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.14</v>
+      </c>
+      <c r="AK12">
+        <v>2.5</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>4</v>
+      </c>
+      <c r="AN12">
+        <v>4</v>
+      </c>
+      <c r="AO12">
+        <v>15</v>
+      </c>
+      <c r="AP12">
+        <v>15</v>
+      </c>
+      <c r="AQ12">
         <v>1.57</v>
       </c>
-      <c r="AG12">
-        <v>2.25</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.15</v>
-      </c>
-      <c r="AK12">
-        <v>2.38</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,130 +2405,130 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>9.17</v>
+        <v>8.5</v>
       </c>
       <c r="O13">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>6.47</v>
+        <v>6.66</v>
       </c>
       <c r="R13">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="S13">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
         <v>4.33</v>
       </c>
       <c r="U13">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V13">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB13">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AC13">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AD13">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE13">
         <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "53"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="AK13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2583,11 +2583,11 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "15", "77", "89"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "81"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "63"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,48 +3048,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>1.43</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>4.71</v>
+        <v>3.87</v>
       </c>
       <c r="P17">
-        <v>5.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
-        <v>1.88</v>
+        <v>3.04</v>
       </c>
       <c r="R17">
         <v>2.5</v>
@@ -3098,89 +3098,89 @@
         <v>1.2</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AB17">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="AC17">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="AD17">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "53", "80", "85"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>1.43</v>
       </c>
       <c r="O18">
-        <v>3.87</v>
+        <v>4.71</v>
       </c>
       <c r="P18">
-        <v>1.84</v>
+        <v>5.86</v>
       </c>
       <c r="Q18">
-        <v>3.04</v>
+        <v>1.88</v>
       </c>
       <c r="R18">
         <v>2.5</v>
@@ -3261,46 +3261,46 @@
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA18">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="AC18">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="AD18">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.22</v>
+        <v>2.55</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>1.99</v>
       </c>
       <c r="R24">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="AA24">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="AC24">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD24">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="Q25">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U25">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA25">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB25">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AK25">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,52 +4547,52 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="O26">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="P26">
+        <v>2.75</v>
+      </c>
+      <c r="Q26">
+        <v>2.85</v>
+      </c>
+      <c r="R26">
+        <v>2.25</v>
+      </c>
+      <c r="S26">
+        <v>1.31</v>
+      </c>
+      <c r="T26">
+        <v>3.08</v>
+      </c>
+      <c r="U26">
         <v>2.42</v>
       </c>
-      <c r="Q26">
-        <v>3.1</v>
-      </c>
-      <c r="R26">
-        <v>2.09</v>
-      </c>
-      <c r="S26">
-        <v>1.3</v>
-      </c>
-      <c r="T26">
-        <v>3.05</v>
-      </c>
-      <c r="U26">
-        <v>2.75</v>
-      </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC26">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="AD26">
         <v>1.33</v>
@@ -4601,10 +4601,10 @@
         <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,52 +4710,52 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="O27">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P27">
+        <v>2.42</v>
+      </c>
+      <c r="Q27">
+        <v>3.1</v>
+      </c>
+      <c r="R27">
+        <v>2.09</v>
+      </c>
+      <c r="S27">
+        <v>1.3</v>
+      </c>
+      <c r="T27">
+        <v>3.05</v>
+      </c>
+      <c r="U27">
         <v>2.75</v>
       </c>
-      <c r="Q27">
-        <v>2.85</v>
-      </c>
-      <c r="R27">
-        <v>2.25</v>
-      </c>
-      <c r="S27">
-        <v>1.31</v>
-      </c>
-      <c r="T27">
-        <v>3.08</v>
-      </c>
-      <c r="U27">
-        <v>2.42</v>
-      </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
         <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="AD27">
         <v>1.33</v>
@@ -4764,10 +4764,10 @@
         <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>5.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q28">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="R28">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
+        <v>3.2</v>
+      </c>
+      <c r="U28">
+        <v>2.71</v>
+      </c>
+      <c r="V28">
+        <v>1.43</v>
+      </c>
+      <c r="W28">
+        <v>1.07</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>1.2</v>
+      </c>
+      <c r="Z28">
         <v>3.8</v>
       </c>
-      <c r="U28">
-        <v>2.24</v>
-      </c>
-      <c r="V28">
-        <v>1.56</v>
-      </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.12</v>
-      </c>
-      <c r="Z28">
-        <v>4.65</v>
-      </c>
       <c r="AA28">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AD28">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AK28">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q30">
-        <v>3.38</v>
+        <v>2.05</v>
       </c>
       <c r="R30">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
+        <v>1.53</v>
+      </c>
+      <c r="W30">
+        <v>1.11</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.16</v>
+      </c>
+      <c r="Z30">
+        <v>4.54</v>
+      </c>
+      <c r="AA30">
+        <v>1.6</v>
+      </c>
+      <c r="AB30">
+        <v>2.26</v>
+      </c>
+      <c r="AC30">
+        <v>2.65</v>
+      </c>
+      <c r="AD30">
         <v>1.44</v>
       </c>
-      <c r="W30">
-        <v>1.1</v>
-      </c>
-      <c r="X30">
-        <v>1.03</v>
-      </c>
-      <c r="Y30">
-        <v>1.25</v>
-      </c>
-      <c r="Z30">
-        <v>3.8</v>
-      </c>
-      <c r="AA30">
-        <v>1.81</v>
-      </c>
-      <c r="AB30">
-        <v>2.03</v>
-      </c>
-      <c r="AC30">
-        <v>3.1</v>
-      </c>
-      <c r="AD30">
-        <v>1.39</v>
-      </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AK30">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="P31">
-        <v>4.6</v>
+        <v>3.12</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>4.54</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AB31">
-        <v>2.26</v>
+        <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="AD31">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="O39">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="P39">
-        <v>2.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q39">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="R39">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.04</v>
@@ -6711,19 +6711,19 @@
         <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="Q40">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R40">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="S40">
+        <v>1.33</v>
+      </c>
+      <c r="T40">
+        <v>3</v>
+      </c>
+      <c r="U40">
+        <v>2.63</v>
+      </c>
+      <c r="V40">
         <v>1.4</v>
       </c>
-      <c r="T40">
-        <v>2.67</v>
-      </c>
-      <c r="U40">
-        <v>3</v>
-      </c>
-      <c r="V40">
+      <c r="W40">
+        <v>1.07</v>
+      </c>
+      <c r="X40">
+        <v>1.04</v>
+      </c>
+      <c r="Y40">
+        <v>1.25</v>
+      </c>
+      <c r="Z40">
+        <v>3.8</v>
+      </c>
+      <c r="AA40">
+        <v>1.87</v>
+      </c>
+      <c r="AB40">
+        <v>1.9</v>
+      </c>
+      <c r="AC40">
+        <v>3.25</v>
+      </c>
+      <c r="AD40">
         <v>1.33</v>
       </c>
-      <c r="W40">
-        <v>1.05</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.35</v>
-      </c>
-      <c r="Z40">
-        <v>2.87</v>
-      </c>
-      <c r="AA40">
-        <v>1.98</v>
-      </c>
-      <c r="AB40">
-        <v>1.7</v>
-      </c>
-      <c r="AC40">
-        <v>3.34</v>
-      </c>
-      <c r="AD40">
-        <v>1.29</v>
-      </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S42">
+        <v>1.4</v>
+      </c>
+      <c r="T42">
+        <v>2.67</v>
+      </c>
+      <c r="U42">
+        <v>3</v>
+      </c>
+      <c r="V42">
+        <v>1.33</v>
+      </c>
+      <c r="W42">
+        <v>1.05</v>
+      </c>
+      <c r="X42">
+        <v>1.01</v>
+      </c>
+      <c r="Y42">
+        <v>1.35</v>
+      </c>
+      <c r="Z42">
+        <v>2.87</v>
+      </c>
+      <c r="AA42">
+        <v>1.98</v>
+      </c>
+      <c r="AB42">
+        <v>1.7</v>
+      </c>
+      <c r="AC42">
+        <v>3.34</v>
+      </c>
+      <c r="AD42">
+        <v>1.29</v>
+      </c>
+      <c r="AE42">
+        <v>1.08</v>
+      </c>
+      <c r="AF42">
+        <v>1.74</v>
+      </c>
+      <c r="AG42">
+        <v>1.95</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.31</v>
       </c>
-      <c r="T42">
-        <v>3.22</v>
-      </c>
-      <c r="U42">
-        <v>2.48</v>
-      </c>
-      <c r="V42">
-        <v>1.46</v>
-      </c>
-      <c r="W42">
-        <v>1.08</v>
-      </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
-      <c r="Y42">
-        <v>1.22</v>
-      </c>
-      <c r="Z42">
-        <v>4.1</v>
-      </c>
-      <c r="AA42">
-        <v>1.85</v>
-      </c>
-      <c r="AB42">
-        <v>1.99</v>
-      </c>
-      <c r="AC42">
-        <v>2.83</v>
-      </c>
-      <c r="AD42">
-        <v>1.33</v>
-      </c>
-      <c r="AE42">
-        <v>1.1</v>
-      </c>
-      <c r="AF42">
-        <v>1.62</v>
-      </c>
-      <c r="AG42">
-        <v>2.16</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.25</v>
-      </c>
       <c r="AK42">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.98</v>
+        <v>3.35</v>
       </c>
       <c r="O43">
         <v>3.45</v>
       </c>
       <c r="P43">
-        <v>3.62</v>
+        <v>2.12</v>
       </c>
       <c r="Q43">
-        <v>2.45</v>
+        <v>3.99</v>
       </c>
       <c r="R43">
         <v>2.12</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U43">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
         <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
         <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,7 +7484,7 @@
         <v>1.75</v>
       </c>
       <c r="O44">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P44">
         <v>4.4</v>
@@ -7496,16 +7496,16 @@
         <v>2.41</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
         <v>3.8</v>
       </c>
       <c r="U44">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W44">
         <v>1.17</v>
@@ -7520,13 +7520,13 @@
         <v>5.5</v>
       </c>
       <c r="AA44">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC44">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AD44">
         <v>1.57</v>
@@ -7653,55 +7653,55 @@
         <v>19</v>
       </c>
       <c r="Q45">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R45">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="S45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="U45">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V45">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="W45">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z45">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA45">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AB45">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AC45">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD45">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AE45">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF45">
         <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK45">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,7 +7810,7 @@
         <v>1.12</v>
       </c>
       <c r="O46">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="P46">
         <v>19.25</v>
@@ -7831,7 +7831,7 @@
         <v>1.81</v>
       </c>
       <c r="V46">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="W46">
         <v>1.3</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="O47">
         <v>4.8</v>
@@ -7982,7 +7982,7 @@
         <v>1.92</v>
       </c>
       <c r="R47">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="S47">
         <v>1.22</v>
@@ -7994,13 +7994,13 @@
         <v>2.16</v>
       </c>
       <c r="V47">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W47">
         <v>1.17</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
         <v>1.11</v>
@@ -8015,7 +8015,7 @@
         <v>2.75</v>
       </c>
       <c r="AC47">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD47">
         <v>1.73</v>
@@ -8027,7 +8027,7 @@
         <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.1</v>
       </c>
       <c r="AK47">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.29</v>
+        <v>2.45</v>
       </c>
       <c r="O48">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="P48">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q48">
-        <v>3.62</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="S48">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="T48">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="U48">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="V48">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="W48">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Z48">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA48">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AB48">
-        <v>2.64</v>
+        <v>4.4</v>
       </c>
       <c r="AC48">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AD48">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="AE48">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="AF48">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AG48">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="O49">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P49">
-        <v>5.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q49">
-        <v>1.97</v>
+        <v>3.65</v>
       </c>
       <c r="R49">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="U49">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="V49">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="W49">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB49">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="AC49">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="AD49">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AE49">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF49">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>2.58</v>
+        <v>1.36</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="O50">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P50">
-        <v>2.44</v>
+        <v>5.75</v>
       </c>
       <c r="Q50">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="R50">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="S50">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>1.62</v>
+        <v>2.36</v>
       </c>
       <c r="V50">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
       <c r="W50">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC50">
-        <v>1.5</v>
+        <v>2.47</v>
       </c>
       <c r="AD50">
+        <v>1.56</v>
+      </c>
+      <c r="AE50">
+        <v>1.22</v>
+      </c>
+      <c r="AF50">
+        <v>1.65</v>
+      </c>
+      <c r="AG50">
+        <v>2.3</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.14</v>
+      </c>
+      <c r="AK50">
         <v>2.5</v>
-      </c>
-      <c r="AE50">
-        <v>1.76</v>
-      </c>
-      <c r="AF50">
-        <v>1.18</v>
-      </c>
-      <c r="AG50">
-        <v>4</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.18</v>
-      </c>
-      <c r="AK50">
-        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="O51">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q51">
         <v>3.7</v>
@@ -8637,49 +8637,49 @@
         <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T51">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
         <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AA51">
         <v>2.15</v>
       </c>
       <c r="AB51">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC51">
         <v>3.68</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
         <v>1.3</v>
